--- a/ESERCIZIO_M2-1-1_dati.xlsx
+++ b/ESERCIZIO_M2-1-1_dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giancarloortolani/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{2DB87580-355D-1A4E-86C4-8EFCF6DAAB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E3E98A4-C39D-CC4D-9307-8424883A9E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="38400" windowHeight="20040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assoluti_Iva" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,6 @@
     <definedName name="VIDEO_B">Assoluti_Iva!$A$37:$C$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1797,11 +1796,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-[$€]\ * #,##0.00_-;\-[$€]\ * #,##0.00_-;_-[$€]\ * &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="165" formatCode="_-[$€-410]\ * #,##0.00_-;\-[$€-410]\ * #,##0.00_-;_-[$€-410]\ * &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ [$€-803]_-;\-* #,##0.00\ [$€-803]_-;_-* &quot;-&quot;??\ [$€-803]_-;_-@_-"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -1928,7 +1928,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1950,6 +1950,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2227,8 +2228,10 @@
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="107.19921875" customWidth="1"/>
     <col min="6" max="6" width="5.59765625" customWidth="1"/>
-    <col min="7" max="7" width="12.19921875" customWidth="1"/>
-    <col min="8" max="26" width="8.796875" customWidth="1"/>
+    <col min="7" max="7" width="13.59765625" customWidth="1"/>
+    <col min="8" max="10" width="8.796875" customWidth="1"/>
+    <col min="11" max="11" width="22.59765625" customWidth="1"/>
+    <col min="12" max="26" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2280,8 +2283,8 @@
         <v>281000</v>
       </c>
       <c r="D2" s="4">
-        <f>C2*$G$2</f>
-        <v>56200</v>
+        <f>C2-(C2/(1+($G$2)))</f>
+        <v>46833.333333333314</v>
       </c>
       <c r="E2" s="3" t="str">
         <f>_xlfn.CONCAT(A2," ",B2)</f>
@@ -2291,10 +2294,16 @@
       <c r="G2" s="14">
         <v>0.2</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="14">
+        <f>1+G2</f>
+        <v>1.2</v>
+      </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="K2" s="21">
+        <f>(C2*$G$2)/$H$2</f>
+        <v>46833.333333333336</v>
+      </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -2322,8 +2331,8 @@
         <v>323000</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" ref="D3:D66" si="0">C3*$G$2</f>
-        <v>64600</v>
+        <f t="shared" ref="D3:D66" si="0">C3-(C3/(1+($G$2)))</f>
+        <v>53833.333333333314</v>
       </c>
       <c r="E3" s="3" t="str">
         <f t="shared" ref="E3:E66" si="1">_xlfn.CONCAT(A3," ",B3)</f>
@@ -2334,7 +2343,10 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="K3" s="21">
+        <f t="shared" ref="K3:K66" si="2">(C3*$G$2)/$H$2</f>
+        <v>53833.333333333336</v>
+      </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -2363,7 +2375,7 @@
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>68800</v>
+        <v>57333.333333333314</v>
       </c>
       <c r="E4" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2374,7 +2386,10 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="K4" s="21">
+        <f t="shared" si="2"/>
+        <v>57333.333333333336</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -2403,18 +2418,24 @@
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>72200</v>
+        <v>60166.666666666628</v>
       </c>
       <c r="E5" s="3" t="str">
         <f t="shared" si="1"/>
         <v>MON.SVGA 0,28 15" AOC 5GLR+ OSD 1280 x 1024, MPR II,TCO'92 N.I., Energy Star Digit 69KHz</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="G5" s="21">
+        <f>C2/H2</f>
+        <v>234166.66666666669</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="K5" s="21">
+        <f t="shared" si="2"/>
+        <v>60166.666666666672</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -2443,7 +2464,7 @@
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>104200</v>
+        <v>86833.333333333314</v>
       </c>
       <c r="E6" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2454,7 +2475,10 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="K6" s="21">
+        <f t="shared" si="2"/>
+        <v>86833.333333333343</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -2483,7 +2507,7 @@
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>105400</v>
+        <v>87833.333333333314</v>
       </c>
       <c r="E7" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2494,7 +2518,10 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="21">
+        <f t="shared" si="2"/>
+        <v>87833.333333333343</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -2523,7 +2550,7 @@
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>125200</v>
+        <v>104333.33333333331</v>
       </c>
       <c r="E8" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2534,7 +2561,10 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="K8" s="21">
+        <f t="shared" si="2"/>
+        <v>104333.33333333334</v>
+      </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -2563,7 +2593,7 @@
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>131200</v>
+        <v>109333.33333333326</v>
       </c>
       <c r="E9" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2574,7 +2604,10 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="21">
+        <f t="shared" si="2"/>
+        <v>109333.33333333334</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -2603,7 +2636,7 @@
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>133200</v>
+        <v>111000</v>
       </c>
       <c r="E10" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2614,7 +2647,10 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="21">
+        <f t="shared" si="2"/>
+        <v>111000</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -2643,7 +2679,7 @@
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>176400</v>
+        <v>147000</v>
       </c>
       <c r="E11" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2654,7 +2690,10 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="21">
+        <f t="shared" si="2"/>
+        <v>147000</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -2683,7 +2722,7 @@
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>221600</v>
+        <v>184666.66666666663</v>
       </c>
       <c r="E12" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2694,7 +2733,10 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="21">
+        <f t="shared" si="2"/>
+        <v>184666.66666666669</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
@@ -2723,7 +2765,7 @@
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>263200</v>
+        <v>219333.33333333326</v>
       </c>
       <c r="E13" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2734,7 +2776,10 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="K13" s="21">
+        <f t="shared" si="2"/>
+        <v>219333.33333333334</v>
+      </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
@@ -2763,7 +2808,7 @@
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>318800</v>
+        <v>265666.66666666651</v>
       </c>
       <c r="E14" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2774,7 +2819,10 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="K14" s="21">
+        <f t="shared" si="2"/>
+        <v>265666.66666666669</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
@@ -2803,7 +2851,7 @@
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>543800</v>
+        <v>453166.66666666651</v>
       </c>
       <c r="E15" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2814,7 +2862,10 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="K15" s="21">
+        <f t="shared" si="2"/>
+        <v>453166.66666666669</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
@@ -2850,7 +2901,10 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="K16" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -2879,7 +2933,7 @@
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>818400</v>
+        <v>682000</v>
       </c>
       <c r="E17" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2890,7 +2944,10 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="K17" s="21">
+        <f t="shared" si="2"/>
+        <v>682000</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
@@ -2919,7 +2976,7 @@
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>2771800</v>
+        <v>2309833.3333333321</v>
       </c>
       <c r="E18" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2930,7 +2987,10 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="K18" s="21">
+        <f t="shared" si="2"/>
+        <v>2309833.3333333335</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -2966,7 +3026,10 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="K19" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
@@ -2995,7 +3058,7 @@
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>33400</v>
+        <v>27833.333333333314</v>
       </c>
       <c r="E20" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3006,7 +3069,10 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+      <c r="K20" s="21">
+        <f t="shared" si="2"/>
+        <v>27833.333333333336</v>
+      </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
@@ -3035,7 +3101,7 @@
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>40400</v>
+        <v>33666.666666666657</v>
       </c>
       <c r="E21" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3046,7 +3112,10 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="K21" s="21">
+        <f t="shared" si="2"/>
+        <v>33666.666666666672</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
@@ -3075,7 +3144,7 @@
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>40600</v>
+        <v>33833.333333333314</v>
       </c>
       <c r="E22" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3086,7 +3155,10 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
+      <c r="K22" s="21">
+        <f t="shared" si="2"/>
+        <v>33833.333333333336</v>
+      </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
@@ -3115,7 +3187,7 @@
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>46800</v>
+        <v>39000</v>
       </c>
       <c r="E23" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3126,7 +3198,10 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="K23" s="21">
+        <f t="shared" si="2"/>
+        <v>39000</v>
+      </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -3155,7 +3230,7 @@
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>50400</v>
+        <v>42000</v>
       </c>
       <c r="E24" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3166,7 +3241,10 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="K24" s="21">
+        <f t="shared" si="2"/>
+        <v>42000</v>
+      </c>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
@@ -3195,7 +3273,7 @@
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>51800</v>
+        <v>43166.666666666657</v>
       </c>
       <c r="E25" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3206,7 +3284,10 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
+      <c r="K25" s="21">
+        <f t="shared" si="2"/>
+        <v>43166.666666666672</v>
+      </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3235,7 +3316,7 @@
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>53800</v>
+        <v>44833.333333333314</v>
       </c>
       <c r="E26" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3246,7 +3327,10 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
+      <c r="K26" s="21">
+        <f t="shared" si="2"/>
+        <v>44833.333333333336</v>
+      </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
@@ -3275,7 +3359,7 @@
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>54200</v>
+        <v>45166.666666666657</v>
       </c>
       <c r="E27" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3286,7 +3370,10 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
+      <c r="K27" s="21">
+        <f t="shared" si="2"/>
+        <v>45166.666666666672</v>
+      </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
@@ -3315,7 +3402,7 @@
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>58400</v>
+        <v>48666.666666666657</v>
       </c>
       <c r="E28" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3326,7 +3413,10 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
+      <c r="K28" s="21">
+        <f t="shared" si="2"/>
+        <v>48666.666666666672</v>
+      </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3355,7 +3445,7 @@
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>58600</v>
+        <v>48833.333333333314</v>
       </c>
       <c r="E29" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3366,7 +3456,10 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
+      <c r="K29" s="21">
+        <f t="shared" si="2"/>
+        <v>48833.333333333336</v>
+      </c>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
@@ -3395,7 +3488,7 @@
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>61400</v>
+        <v>51166.666666666657</v>
       </c>
       <c r="E30" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3406,7 +3499,10 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
+      <c r="K30" s="21">
+        <f t="shared" si="2"/>
+        <v>51166.666666666672</v>
+      </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
@@ -3435,7 +3531,7 @@
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>88000</v>
+        <v>73333.333333333314</v>
       </c>
       <c r="E31" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3446,7 +3542,10 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
+      <c r="K31" s="21">
+        <f t="shared" si="2"/>
+        <v>73333.333333333343</v>
+      </c>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
@@ -3475,7 +3574,7 @@
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>97400</v>
+        <v>81166.666666666628</v>
       </c>
       <c r="E32" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3486,7 +3585,10 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
+      <c r="K32" s="21">
+        <f t="shared" si="2"/>
+        <v>81166.666666666672</v>
+      </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
@@ -3515,7 +3617,7 @@
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>113200</v>
+        <v>94333.333333333314</v>
       </c>
       <c r="E33" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3526,7 +3628,10 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
+      <c r="K33" s="21">
+        <f t="shared" si="2"/>
+        <v>94333.333333333343</v>
+      </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
@@ -3555,7 +3660,7 @@
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>160400</v>
+        <v>133666.66666666663</v>
       </c>
       <c r="E34" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3566,7 +3671,10 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
+      <c r="K34" s="21">
+        <f t="shared" si="2"/>
+        <v>133666.66666666669</v>
+      </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -3595,7 +3703,7 @@
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>315800</v>
+        <v>263166.66666666651</v>
       </c>
       <c r="E35" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3606,7 +3714,10 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
+      <c r="K35" s="21">
+        <f t="shared" si="2"/>
+        <v>263166.66666666669</v>
+      </c>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
@@ -3642,7 +3753,10 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
+      <c r="K36" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
@@ -3671,7 +3785,7 @@
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>14000</v>
+        <v>11666.666666666664</v>
       </c>
       <c r="E37" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3682,7 +3796,10 @@
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
+      <c r="K37" s="21">
+        <f t="shared" si="2"/>
+        <v>11666.666666666668</v>
+      </c>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
@@ -3711,7 +3828,7 @@
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>20800</v>
+        <v>17333.333333333328</v>
       </c>
       <c r="E38" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3722,7 +3839,10 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
+      <c r="K38" s="21">
+        <f t="shared" si="2"/>
+        <v>17333.333333333336</v>
+      </c>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
@@ -3751,7 +3871,7 @@
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>25400</v>
+        <v>21166.666666666657</v>
       </c>
       <c r="E39" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3762,7 +3882,10 @@
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
+      <c r="K39" s="21">
+        <f t="shared" si="2"/>
+        <v>21166.666666666668</v>
+      </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
@@ -3791,7 +3914,7 @@
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>32400</v>
+        <v>27000</v>
       </c>
       <c r="E40" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3802,7 +3925,10 @@
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
+      <c r="K40" s="21">
+        <f t="shared" si="2"/>
+        <v>27000</v>
+      </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -3831,7 +3957,7 @@
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>35800</v>
+        <v>29833.333333333314</v>
       </c>
       <c r="E41" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3842,7 +3968,10 @@
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
+      <c r="K41" s="21">
+        <f t="shared" si="2"/>
+        <v>29833.333333333336</v>
+      </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
@@ -3871,7 +4000,7 @@
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>37200</v>
+        <v>31000</v>
       </c>
       <c r="E42" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3882,7 +4011,10 @@
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
+      <c r="K42" s="21">
+        <f t="shared" si="2"/>
+        <v>31000</v>
+      </c>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
@@ -3911,7 +4043,7 @@
       </c>
       <c r="D43" s="4">
         <f t="shared" si="0"/>
-        <v>37200</v>
+        <v>31000</v>
       </c>
       <c r="E43" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3922,7 +4054,10 @@
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
+      <c r="K43" s="21">
+        <f t="shared" si="2"/>
+        <v>31000</v>
+      </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
@@ -3951,7 +4086,7 @@
       </c>
       <c r="D44" s="4">
         <f t="shared" si="0"/>
-        <v>40600</v>
+        <v>33833.333333333314</v>
       </c>
       <c r="E44" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3962,7 +4097,10 @@
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
+      <c r="K44" s="21">
+        <f t="shared" si="2"/>
+        <v>33833.333333333336</v>
+      </c>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
@@ -3991,7 +4129,7 @@
       </c>
       <c r="D45" s="4">
         <f t="shared" si="0"/>
-        <v>42400</v>
+        <v>35333.333333333314</v>
       </c>
       <c r="E45" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4002,7 +4140,10 @@
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
+      <c r="K45" s="21">
+        <f t="shared" si="2"/>
+        <v>35333.333333333336</v>
+      </c>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
@@ -4031,7 +4172,7 @@
       </c>
       <c r="D46" s="4">
         <f t="shared" si="0"/>
-        <v>44400</v>
+        <v>37000</v>
       </c>
       <c r="E46" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4042,7 +4183,10 @@
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
+      <c r="K46" s="21">
+        <f t="shared" si="2"/>
+        <v>37000</v>
+      </c>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
@@ -4071,7 +4215,7 @@
       </c>
       <c r="D47" s="4">
         <f t="shared" si="0"/>
-        <v>49000</v>
+        <v>40833.333333333314</v>
       </c>
       <c r="E47" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4082,7 +4226,10 @@
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
+      <c r="K47" s="21">
+        <f t="shared" si="2"/>
+        <v>40833.333333333336</v>
+      </c>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
@@ -4111,7 +4258,7 @@
       </c>
       <c r="D48" s="4">
         <f t="shared" si="0"/>
-        <v>50200</v>
+        <v>41833.333333333314</v>
       </c>
       <c r="E48" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4122,7 +4269,10 @@
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
+      <c r="K48" s="21">
+        <f t="shared" si="2"/>
+        <v>41833.333333333336</v>
+      </c>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4151,7 +4301,7 @@
       </c>
       <c r="D49" s="4">
         <f t="shared" si="0"/>
-        <v>51400</v>
+        <v>42833.333333333314</v>
       </c>
       <c r="E49" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4162,7 +4312,10 @@
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
+      <c r="K49" s="21">
+        <f t="shared" si="2"/>
+        <v>42833.333333333336</v>
+      </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
@@ -4191,7 +4344,7 @@
       </c>
       <c r="D50" s="4">
         <f t="shared" si="0"/>
-        <v>53800</v>
+        <v>44833.333333333314</v>
       </c>
       <c r="E50" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4202,7 +4355,10 @@
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
+      <c r="K50" s="21">
+        <f t="shared" si="2"/>
+        <v>44833.333333333336</v>
+      </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
@@ -4231,7 +4387,7 @@
       </c>
       <c r="D51" s="4">
         <f t="shared" si="0"/>
-        <v>62800</v>
+        <v>52333.333333333314</v>
       </c>
       <c r="E51" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4242,7 +4398,10 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
+      <c r="K51" s="21">
+        <f t="shared" si="2"/>
+        <v>52333.333333333336</v>
+      </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
@@ -4271,7 +4430,7 @@
       </c>
       <c r="D52" s="4">
         <f t="shared" si="0"/>
-        <v>65000</v>
+        <v>54166.666666666628</v>
       </c>
       <c r="E52" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4282,7 +4441,10 @@
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
+      <c r="K52" s="21">
+        <f t="shared" si="2"/>
+        <v>54166.666666666672</v>
+      </c>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
@@ -4311,7 +4473,7 @@
       </c>
       <c r="D53" s="4">
         <f t="shared" si="0"/>
-        <v>69400</v>
+        <v>57833.333333333314</v>
       </c>
       <c r="E53" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4322,7 +4484,10 @@
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
+      <c r="K53" s="21">
+        <f t="shared" si="2"/>
+        <v>57833.333333333336</v>
+      </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
@@ -4351,7 +4516,7 @@
       </c>
       <c r="D54" s="4">
         <f t="shared" si="0"/>
-        <v>73800</v>
+        <v>61500</v>
       </c>
       <c r="E54" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4362,7 +4527,10 @@
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
+      <c r="K54" s="21">
+        <f t="shared" si="2"/>
+        <v>61500</v>
+      </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
@@ -4391,7 +4559,7 @@
       </c>
       <c r="D55" s="4">
         <f t="shared" si="0"/>
-        <v>80400</v>
+        <v>67000</v>
       </c>
       <c r="E55" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4402,7 +4570,10 @@
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
+      <c r="K55" s="21">
+        <f t="shared" si="2"/>
+        <v>67000</v>
+      </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
@@ -4431,7 +4602,7 @@
       </c>
       <c r="D56" s="4">
         <f t="shared" si="0"/>
-        <v>94200</v>
+        <v>78500</v>
       </c>
       <c r="E56" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4442,7 +4613,10 @@
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
+      <c r="K56" s="21">
+        <f t="shared" si="2"/>
+        <v>78500</v>
+      </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
@@ -4471,7 +4645,7 @@
       </c>
       <c r="D57" s="4">
         <f t="shared" si="0"/>
-        <v>95200</v>
+        <v>79333.333333333314</v>
       </c>
       <c r="E57" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4482,7 +4656,10 @@
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
+      <c r="K57" s="21">
+        <f t="shared" si="2"/>
+        <v>79333.333333333343</v>
+      </c>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
@@ -4511,7 +4688,7 @@
       </c>
       <c r="D58" s="4">
         <f t="shared" si="0"/>
-        <v>98400</v>
+        <v>82000</v>
       </c>
       <c r="E58" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4522,7 +4699,10 @@
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
+      <c r="K58" s="21">
+        <f t="shared" si="2"/>
+        <v>82000</v>
+      </c>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
@@ -4551,7 +4731,7 @@
       </c>
       <c r="D59" s="4">
         <f t="shared" si="0"/>
-        <v>106200</v>
+        <v>88500</v>
       </c>
       <c r="E59" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4562,7 +4742,10 @@
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
+      <c r="K59" s="21">
+        <f t="shared" si="2"/>
+        <v>88500</v>
+      </c>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
@@ -4591,7 +4774,7 @@
       </c>
       <c r="D60" s="4">
         <f t="shared" si="0"/>
-        <v>110400</v>
+        <v>92000</v>
       </c>
       <c r="E60" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4602,7 +4785,10 @@
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
+      <c r="K60" s="21">
+        <f t="shared" si="2"/>
+        <v>92000</v>
+      </c>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
@@ -4631,7 +4817,7 @@
       </c>
       <c r="D61" s="4">
         <f t="shared" si="0"/>
-        <v>297400</v>
+        <v>247833.33333333326</v>
       </c>
       <c r="E61" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4642,7 +4828,10 @@
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
+      <c r="K61" s="21">
+        <f t="shared" si="2"/>
+        <v>247833.33333333334</v>
+      </c>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
@@ -4678,7 +4867,10 @@
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
+      <c r="K62" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
@@ -4707,7 +4899,7 @@
       </c>
       <c r="D63" s="4">
         <f t="shared" si="0"/>
-        <v>20200</v>
+        <v>16833.333333333328</v>
       </c>
       <c r="E63" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4718,7 +4910,10 @@
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
+      <c r="K63" s="21">
+        <f t="shared" si="2"/>
+        <v>16833.333333333336</v>
+      </c>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
@@ -4747,7 +4942,7 @@
       </c>
       <c r="D64" s="4">
         <f t="shared" si="0"/>
-        <v>7600</v>
+        <v>6333.3333333333321</v>
       </c>
       <c r="E64" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4758,7 +4953,10 @@
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
+      <c r="K64" s="21">
+        <f t="shared" si="2"/>
+        <v>6333.3333333333339</v>
+      </c>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
@@ -4787,7 +4985,7 @@
       </c>
       <c r="D65" s="4">
         <f t="shared" si="0"/>
-        <v>27400</v>
+        <v>22833.333333333328</v>
       </c>
       <c r="E65" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4798,7 +4996,10 @@
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
+      <c r="K65" s="21">
+        <f t="shared" si="2"/>
+        <v>22833.333333333336</v>
+      </c>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
@@ -4827,7 +5028,7 @@
       </c>
       <c r="D66" s="4">
         <f t="shared" si="0"/>
-        <v>44400</v>
+        <v>37000</v>
       </c>
       <c r="E66" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4838,7 +5039,10 @@
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
+      <c r="K66" s="21">
+        <f t="shared" si="2"/>
+        <v>37000</v>
+      </c>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
@@ -4866,11 +5070,11 @@
         <v>501000</v>
       </c>
       <c r="D67" s="4">
-        <f t="shared" ref="D67:D130" si="2">C67*$G$2</f>
-        <v>100200</v>
+        <f t="shared" ref="D67:D130" si="3">C67-(C67/(1+($G$2)))</f>
+        <v>83500</v>
       </c>
       <c r="E67" s="3" t="str">
-        <f t="shared" ref="E67:E130" si="3">_xlfn.CONCAT(A67," ",B67)</f>
+        <f t="shared" ref="E67:E130" si="4">_xlfn.CONCAT(A67," ",B67)</f>
         <v>Contr. PCI AHA 2940AU SCSI-2 Adaptec 2940 Ultra Fast, SCSI-2, sw EZ SCSI 4.0</v>
       </c>
       <c r="F67" s="3"/>
@@ -4878,7 +5082,10 @@
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
+      <c r="K67" s="21">
+        <f t="shared" ref="K67:K130" si="5">(C67*$G$2)/$H$2</f>
+        <v>83500</v>
+      </c>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
@@ -4906,11 +5113,11 @@
         <v>428000</v>
       </c>
       <c r="D68" s="4">
-        <f t="shared" si="2"/>
-        <v>85600</v>
+        <f t="shared" si="3"/>
+        <v>71333.333333333314</v>
       </c>
       <c r="E68" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Contr. PCI AHA 2940UW Wide SCSI OEM Adaptec 2940 Ultra Fast, Wide SCSI e SCSI-2</v>
       </c>
       <c r="F68" s="3"/>
@@ -4918,7 +5125,10 @@
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
+      <c r="K68" s="21">
+        <f t="shared" si="5"/>
+        <v>71333.333333333343</v>
+      </c>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
@@ -4946,11 +5156,11 @@
         <v>561000</v>
       </c>
       <c r="D69" s="4">
-        <f t="shared" si="2"/>
-        <v>112200</v>
+        <f t="shared" si="3"/>
+        <v>93500</v>
       </c>
       <c r="E69" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Contr. PCI AHA 2940UW Wide SCSI Adaptec 2940 Ultra Fast, Wide SCSI e SCSI-2, sw EZ SCSI</v>
       </c>
       <c r="F69" s="3"/>
@@ -4958,7 +5168,10 @@
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
+      <c r="K69" s="21">
+        <f t="shared" si="5"/>
+        <v>93500</v>
+      </c>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
@@ -4986,11 +5199,11 @@
         <v>1578000</v>
       </c>
       <c r="D70" s="4">
-        <f t="shared" si="2"/>
-        <v>315600</v>
+        <f t="shared" si="3"/>
+        <v>263000</v>
       </c>
       <c r="E70" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Contr.PCI DA2100 Dual Wide SCSI ASUS Infotrend-500127 dual Ultra Fast, Wide SCSI, RAID</v>
       </c>
       <c r="F70" s="3"/>
@@ -4998,7 +5211,10 @@
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
+      <c r="K70" s="21">
+        <f t="shared" si="5"/>
+        <v>263000</v>
+      </c>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
@@ -5026,11 +5242,11 @@
         <v>34000</v>
       </c>
       <c r="D71" s="4">
-        <f t="shared" si="2"/>
-        <v>6800</v>
+        <f t="shared" si="3"/>
+        <v>5666.6666666666642</v>
       </c>
       <c r="E71" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Scheda 2 porte seriali, 1 porta parallela 16550 Fast UART</v>
       </c>
       <c r="F71" s="3"/>
@@ -5038,7 +5254,10 @@
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
+      <c r="K71" s="21">
+        <f t="shared" si="5"/>
+        <v>5666.666666666667</v>
+      </c>
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
@@ -5066,11 +5285,11 @@
         <v>20000</v>
       </c>
       <c r="D72" s="4">
-        <f t="shared" si="2"/>
-        <v>4000</v>
+        <f t="shared" si="3"/>
+        <v>3333.3333333333321</v>
       </c>
       <c r="E72" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">Scheda singola seriale  </v>
       </c>
       <c r="F72" s="3"/>
@@ -5078,7 +5297,10 @@
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
+      <c r="K72" s="21">
+        <f t="shared" si="5"/>
+        <v>3333.3333333333335</v>
+      </c>
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
@@ -5106,11 +5328,11 @@
         <v>23000</v>
       </c>
       <c r="D73" s="4">
-        <f t="shared" si="2"/>
-        <v>4600</v>
+        <f t="shared" si="3"/>
+        <v>3833.3333333333321</v>
       </c>
       <c r="E73" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">Scheda doppia seriale  </v>
       </c>
       <c r="F73" s="3"/>
@@ -5118,7 +5340,10 @@
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
+      <c r="K73" s="21">
+        <f t="shared" si="5"/>
+        <v>3833.3333333333335</v>
+      </c>
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
@@ -5144,11 +5369,11 @@
         <v>98000</v>
       </c>
       <c r="D74" s="4">
-        <f t="shared" si="2"/>
-        <v>19600</v>
+        <f t="shared" si="3"/>
+        <v>16333.333333333328</v>
       </c>
       <c r="E74" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">Scheda 4 porte seriali </v>
       </c>
       <c r="F74" s="3"/>
@@ -5156,7 +5381,10 @@
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
+      <c r="K74" s="21">
+        <f t="shared" si="5"/>
+        <v>16333.333333333334</v>
+      </c>
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
@@ -5182,11 +5410,11 @@
         <v>251000</v>
       </c>
       <c r="D75" s="4">
-        <f t="shared" si="2"/>
-        <v>50200</v>
+        <f t="shared" si="3"/>
+        <v>41833.333333333314</v>
       </c>
       <c r="E75" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">Scheda 8 porte seriali </v>
       </c>
       <c r="F75" s="3"/>
@@ -5194,7 +5422,10 @@
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
+      <c r="K75" s="21">
+        <f t="shared" si="5"/>
+        <v>41833.333333333336</v>
+      </c>
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
@@ -5220,11 +5451,11 @@
         <v>15000</v>
       </c>
       <c r="D76" s="4">
-        <f t="shared" si="2"/>
-        <v>3000</v>
+        <f t="shared" si="3"/>
+        <v>2500</v>
       </c>
       <c r="E76" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">Scheda singola parallela </v>
       </c>
       <c r="F76" s="3"/>
@@ -5232,7 +5463,10 @@
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
+      <c r="K76" s="21">
+        <f t="shared" si="5"/>
+        <v>2500</v>
+      </c>
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
@@ -5258,11 +5492,11 @@
         <v>14000</v>
       </c>
       <c r="D77" s="4">
-        <f t="shared" si="2"/>
-        <v>2800</v>
+        <f t="shared" si="3"/>
+        <v>2333.3333333333321</v>
       </c>
       <c r="E77" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">Scheda 2 porte joystick </v>
       </c>
       <c r="F77" s="3"/>
@@ -5270,7 +5504,10 @@
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
+      <c r="K77" s="21">
+        <f t="shared" si="5"/>
+        <v>2333.3333333333335</v>
+      </c>
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
@@ -5294,11 +5531,11 @@
       <c r="B78" s="3"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E78" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">HARD DISK </v>
       </c>
       <c r="F78" s="3"/>
@@ -5306,7 +5543,10 @@
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
+      <c r="K78" s="21">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
@@ -5334,11 +5574,11 @@
         <v>399000</v>
       </c>
       <c r="D79" s="4">
-        <f t="shared" si="2"/>
-        <v>79800</v>
+        <f t="shared" si="3"/>
+        <v>66500</v>
       </c>
       <c r="E79" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>HARD DISK 2.5"  2,1GB U.Dma 2,5" 12mm HITACHI - DK226A-21</v>
       </c>
       <c r="F79" s="3"/>
@@ -5346,7 +5586,10 @@
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
+      <c r="K79" s="21">
+        <f t="shared" si="5"/>
+        <v>66500</v>
+      </c>
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
@@ -5374,11 +5617,11 @@
         <v>259000</v>
       </c>
       <c r="D80" s="4">
-        <f t="shared" si="2"/>
-        <v>51800</v>
+        <f t="shared" si="3"/>
+        <v>43166.666666666657</v>
       </c>
       <c r="E80" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">HD 2,1 GB Ultra DMA 5400rpm 3,5" ULTRA DMA FUJITSU </v>
       </c>
       <c r="F80" s="3"/>
@@ -5386,7 +5629,10 @@
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
+      <c r="K80" s="21">
+        <f t="shared" si="5"/>
+        <v>43166.666666666672</v>
+      </c>
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
@@ -5414,11 +5660,11 @@
         <v>324000</v>
       </c>
       <c r="D81" s="4">
-        <f t="shared" si="2"/>
-        <v>64800</v>
+        <f t="shared" si="3"/>
+        <v>54000</v>
       </c>
       <c r="E81" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">HD 3,2 GB Ultra DMA 5400rpm 3,5" ULTRA DMA FUJITSU </v>
       </c>
       <c r="F81" s="3"/>
@@ -5426,7 +5672,10 @@
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
-      <c r="K81" s="3"/>
+      <c r="K81" s="21">
+        <f t="shared" si="5"/>
+        <v>54000</v>
+      </c>
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
@@ -5454,11 +5703,11 @@
         <v>378000</v>
       </c>
       <c r="D82" s="4">
-        <f t="shared" si="2"/>
-        <v>75600</v>
+        <f t="shared" si="3"/>
+        <v>63000</v>
       </c>
       <c r="E82" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">HD 4,3 GB Ultra DMA 5400rpm 3,5" ULTRA DMA FUJITSU </v>
       </c>
       <c r="F82" s="3"/>
@@ -5466,7 +5715,10 @@
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
-      <c r="K82" s="3"/>
+      <c r="K82" s="21">
+        <f t="shared" si="5"/>
+        <v>63000</v>
+      </c>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
@@ -5494,11 +5746,11 @@
         <v>469000</v>
       </c>
       <c r="D83" s="4">
-        <f t="shared" si="2"/>
-        <v>93800</v>
+        <f t="shared" si="3"/>
+        <v>78166.666666666628</v>
       </c>
       <c r="E83" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">HD 5,2 GB Ultra DMA 5400rpm 3,5" ULTRA DMA FUJITSU </v>
       </c>
       <c r="F83" s="3"/>
@@ -5506,7 +5758,10 @@
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
+      <c r="K83" s="21">
+        <f t="shared" si="5"/>
+        <v>78166.666666666672</v>
+      </c>
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
@@ -5534,11 +5789,11 @@
         <v>556000</v>
       </c>
       <c r="D84" s="4">
-        <f t="shared" si="2"/>
-        <v>111200</v>
+        <f t="shared" si="3"/>
+        <v>92666.666666666628</v>
       </c>
       <c r="E84" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">HD 6,4 GB Ultra DMA 5400rpm 3,5" ULTRA DMA FUJITSU </v>
       </c>
       <c r="F84" s="3"/>
@@ -5546,7 +5801,10 @@
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
+      <c r="K84" s="21">
+        <f t="shared" si="5"/>
+        <v>92666.666666666672</v>
+      </c>
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
@@ -5574,11 +5832,11 @@
         <v>476000</v>
       </c>
       <c r="D85" s="4">
-        <f t="shared" si="2"/>
-        <v>95200</v>
+        <f t="shared" si="3"/>
+        <v>79333.333333333314</v>
       </c>
       <c r="E85" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>HD 2 GB SCSI III 5400 rpm 3,5" SCSI QUANTUM FIREBALL ST</v>
       </c>
       <c r="F85" s="3"/>
@@ -5586,7 +5844,10 @@
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
-      <c r="K85" s="3"/>
+      <c r="K85" s="21">
+        <f t="shared" si="5"/>
+        <v>79333.333333333343</v>
+      </c>
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
@@ -5614,11 +5875,11 @@
         <v>477000</v>
       </c>
       <c r="D86" s="4">
-        <f t="shared" si="2"/>
-        <v>95400</v>
+        <f t="shared" si="3"/>
+        <v>79500</v>
       </c>
       <c r="E86" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>HD 3,2 GB SCSI III 5400rpm 3,5" SCSI QUANTUM FIREBALL ST</v>
       </c>
       <c r="F86" s="3"/>
@@ -5626,7 +5887,10 @@
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
+      <c r="K86" s="21">
+        <f t="shared" si="5"/>
+        <v>79500</v>
+      </c>
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
@@ -5654,11 +5918,11 @@
         <v>556000</v>
       </c>
       <c r="D87" s="4">
-        <f t="shared" si="2"/>
-        <v>111200</v>
+        <f t="shared" si="3"/>
+        <v>92666.666666666628</v>
       </c>
       <c r="E87" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>HD 4,3 GB SCSI 5400 rpm 3,5" SCSI QUANTUM FIREBALL ST</v>
       </c>
       <c r="F87" s="3"/>
@@ -5666,7 +5930,10 @@
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
+      <c r="K87" s="21">
+        <f t="shared" si="5"/>
+        <v>92666.666666666672</v>
+      </c>
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
@@ -5694,11 +5961,11 @@
         <v>695000</v>
       </c>
       <c r="D88" s="4">
-        <f t="shared" si="2"/>
-        <v>139000</v>
+        <f t="shared" si="3"/>
+        <v>115833.33333333326</v>
       </c>
       <c r="E88" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>HD 4,5 GB SCSI ULTRA WIDE 7200rpm 3,5" SCSI III, QUANTUM VIKING</v>
       </c>
       <c r="F88" s="3"/>
@@ -5706,7 +5973,10 @@
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
-      <c r="K88" s="3"/>
+      <c r="K88" s="21">
+        <f t="shared" si="5"/>
+        <v>115833.33333333334</v>
+      </c>
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
@@ -5734,11 +6004,11 @@
         <v>1279000</v>
       </c>
       <c r="D89" s="4">
-        <f t="shared" si="2"/>
-        <v>255800</v>
+        <f t="shared" si="3"/>
+        <v>213166.66666666651</v>
       </c>
       <c r="E89" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>HD 4,5 GB SCSI ULTRA WIDE 10.000rpm 3,5" SCSI U.W. SEAGATE CHEETAH</v>
       </c>
       <c r="F89" s="3"/>
@@ -5746,7 +6016,10 @@
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
-      <c r="K89" s="3"/>
+      <c r="K89" s="21">
+        <f t="shared" si="5"/>
+        <v>213166.66666666669</v>
+      </c>
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
       <c r="N89" s="3"/>
@@ -5774,11 +6047,11 @@
         <v>35000</v>
       </c>
       <c r="D90" s="4">
-        <f t="shared" si="2"/>
-        <v>7000</v>
+        <f t="shared" si="3"/>
+        <v>5833.3333333333321</v>
       </c>
       <c r="E90" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>FDD 1,44MB PANASONIC</v>
       </c>
       <c r="F90" s="3"/>
@@ -5786,7 +6059,10 @@
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
+      <c r="K90" s="21">
+        <f t="shared" si="5"/>
+        <v>5833.3333333333339</v>
+      </c>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
@@ -5814,11 +6090,11 @@
         <v>175000</v>
       </c>
       <c r="D91" s="4">
-        <f t="shared" si="2"/>
-        <v>35000</v>
+        <f t="shared" si="3"/>
+        <v>29166.666666666657</v>
       </c>
       <c r="E91" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>FLOPPY DRIVE 120MB PANASONIC LS-120</v>
       </c>
       <c r="F91" s="3"/>
@@ -5826,7 +6102,10 @@
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
+      <c r="K91" s="21">
+        <f t="shared" si="5"/>
+        <v>29166.666666666668</v>
+      </c>
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
@@ -5854,11 +6133,11 @@
         <v>272000</v>
       </c>
       <c r="D92" s="4">
-        <f t="shared" si="2"/>
-        <v>54400</v>
+        <f t="shared" si="3"/>
+        <v>45333.333333333314</v>
       </c>
       <c r="E92" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ZIP DRIVE 100MB PARALL. IOMEGA</v>
       </c>
       <c r="F92" s="3"/>
@@ -5866,7 +6145,10 @@
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
+      <c r="K92" s="21">
+        <f t="shared" si="5"/>
+        <v>45333.333333333336</v>
+      </c>
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
@@ -5894,11 +6176,11 @@
         <v>198000</v>
       </c>
       <c r="D93" s="4">
-        <f t="shared" si="2"/>
-        <v>39600</v>
+        <f t="shared" si="3"/>
+        <v>33000</v>
       </c>
       <c r="E93" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ZIP ATAPI 100MB INTERNO IOMEGA</v>
       </c>
       <c r="F93" s="3"/>
@@ -5906,7 +6188,10 @@
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
+      <c r="K93" s="21">
+        <f t="shared" si="5"/>
+        <v>33000</v>
+      </c>
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
       <c r="N93" s="3"/>
@@ -5934,11 +6219,11 @@
         <v>290000</v>
       </c>
       <c r="D94" s="4">
-        <f t="shared" si="2"/>
-        <v>58000</v>
+        <f t="shared" si="3"/>
+        <v>48333.333333333314</v>
       </c>
       <c r="E94" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ZIP DRIVE 100MB SCSI IOMEGA</v>
       </c>
       <c r="F94" s="3"/>
@@ -5946,7 +6231,10 @@
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
+      <c r="K94" s="21">
+        <f t="shared" si="5"/>
+        <v>48333.333333333336</v>
+      </c>
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
       <c r="N94" s="3"/>
@@ -5974,11 +6262,11 @@
         <v>589000</v>
       </c>
       <c r="D95" s="4">
-        <f t="shared" si="2"/>
-        <v>117800</v>
+        <f t="shared" si="3"/>
+        <v>98166.666666666628</v>
       </c>
       <c r="E95" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>JAZ DRIVE 1GB INT. IOMEGA</v>
       </c>
       <c r="F95" s="3"/>
@@ -5986,7 +6274,10 @@
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
+      <c r="K95" s="21">
+        <f t="shared" si="5"/>
+        <v>98166.666666666672</v>
+      </c>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
@@ -6014,11 +6305,11 @@
         <v>743000</v>
       </c>
       <c r="D96" s="4">
-        <f t="shared" si="2"/>
-        <v>148600</v>
+        <f t="shared" si="3"/>
+        <v>123833.33333333326</v>
       </c>
       <c r="E96" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>JAZ DRIVE 1GB EXT. IOMEGA</v>
       </c>
       <c r="F96" s="3"/>
@@ -6026,7 +6317,10 @@
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
+      <c r="K96" s="21">
+        <f t="shared" si="5"/>
+        <v>123833.33333333334</v>
+      </c>
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
@@ -6054,11 +6348,11 @@
         <v>271000</v>
       </c>
       <c r="D97" s="4">
-        <f t="shared" si="2"/>
-        <v>54200</v>
+        <f t="shared" si="3"/>
+        <v>45166.666666666657</v>
       </c>
       <c r="E97" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">KIT 10  CARTUCCE ZIP DRIVE  </v>
       </c>
       <c r="F97" s="3"/>
@@ -6066,7 +6360,10 @@
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
+      <c r="K97" s="21">
+        <f t="shared" si="5"/>
+        <v>45166.666666666672</v>
+      </c>
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
@@ -6094,11 +6391,11 @@
         <v>632000</v>
       </c>
       <c r="D98" s="4">
-        <f t="shared" si="2"/>
-        <v>126400</v>
+        <f t="shared" si="3"/>
+        <v>105333.33333333326</v>
       </c>
       <c r="E98" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">KIT 3 CARTUCCE JAZ DRIVE  </v>
       </c>
       <c r="F98" s="3"/>
@@ -6106,7 +6403,10 @@
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
+      <c r="K98" s="21">
+        <f t="shared" si="5"/>
+        <v>105333.33333333334</v>
+      </c>
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
@@ -6134,11 +6434,11 @@
         <v>90000</v>
       </c>
       <c r="D99" s="4">
-        <f t="shared" si="2"/>
-        <v>18000</v>
+        <f t="shared" si="3"/>
+        <v>15000</v>
       </c>
       <c r="E99" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>KIT 3 CARTUCCE 120MB 3M per LS-120</v>
       </c>
       <c r="F99" s="3"/>
@@ -6146,7 +6446,10 @@
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
-      <c r="K99" s="3"/>
+      <c r="K99" s="21">
+        <f t="shared" si="5"/>
+        <v>15000</v>
+      </c>
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
       <c r="N99" s="3"/>
@@ -6174,11 +6477,11 @@
         <v>4000</v>
       </c>
       <c r="D100" s="4">
-        <f t="shared" si="2"/>
-        <v>800</v>
+        <f t="shared" si="3"/>
+        <v>666.66666666666652</v>
       </c>
       <c r="E100" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>FRAME HDD  Kit montaggio Hard Disk 3,5"</v>
       </c>
       <c r="F100" s="3"/>
@@ -6186,7 +6489,10 @@
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
+      <c r="K100" s="21">
+        <f t="shared" si="5"/>
+        <v>666.66666666666674</v>
+      </c>
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
       <c r="N100" s="3"/>
@@ -6214,11 +6520,11 @@
         <v>5000</v>
       </c>
       <c r="D101" s="4">
-        <f t="shared" si="2"/>
-        <v>1000</v>
+        <f t="shared" si="3"/>
+        <v>833.33333333333303</v>
       </c>
       <c r="E101" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>FRAME FDD  Kit montaggio Floppy Disk Drive 3,5"</v>
       </c>
       <c r="F101" s="3"/>
@@ -6226,7 +6532,10 @@
       <c r="H101" s="3"/>
       <c r="I101" s="3"/>
       <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
+      <c r="K101" s="21">
+        <f t="shared" si="5"/>
+        <v>833.33333333333337</v>
+      </c>
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
       <c r="N101" s="3"/>
@@ -6254,11 +6563,11 @@
         <v>41000</v>
       </c>
       <c r="D102" s="4">
-        <f t="shared" si="2"/>
-        <v>8200</v>
+        <f t="shared" si="3"/>
+        <v>6833.3333333333285</v>
       </c>
       <c r="E102" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>FRAME REMOVIBILE 3.5" Kit FRAME REMOVIBILE per HDD 3,5"</v>
       </c>
       <c r="F102" s="3"/>
@@ -6266,7 +6575,10 @@
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
       <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
+      <c r="K102" s="21">
+        <f t="shared" si="5"/>
+        <v>6833.3333333333339</v>
+      </c>
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
@@ -6290,11 +6602,11 @@
       <c r="B103" s="3"/>
       <c r="C103" s="4"/>
       <c r="D103" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E103" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">MAGNETO-OTTICI </v>
       </c>
       <c r="F103" s="3"/>
@@ -6302,7 +6614,10 @@
       <c r="H103" s="3"/>
       <c r="I103" s="3"/>
       <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
+      <c r="K103" s="21">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
@@ -6330,11 +6645,11 @@
         <v>737000</v>
       </c>
       <c r="D104" s="4">
-        <f t="shared" si="2"/>
-        <v>147400</v>
+        <f t="shared" si="3"/>
+        <v>122833.33333333326</v>
       </c>
       <c r="E104" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>M.O. + CD 4X,  PD 2000 INT. 650 MB PLASMON PD2000I</v>
       </c>
       <c r="F104" s="3"/>
@@ -6342,7 +6657,10 @@
       <c r="H104" s="3"/>
       <c r="I104" s="3"/>
       <c r="J104" s="3"/>
-      <c r="K104" s="3"/>
+      <c r="K104" s="21">
+        <f t="shared" si="5"/>
+        <v>122833.33333333334</v>
+      </c>
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
@@ -6370,11 +6688,11 @@
         <v>910000</v>
       </c>
       <c r="D105" s="4">
-        <f t="shared" si="2"/>
-        <v>182000</v>
+        <f t="shared" si="3"/>
+        <v>151666.66666666663</v>
       </c>
       <c r="E105" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>M.O. + CD 4X,  PD 2000 EXT. 650 MB PLASMON PD2000E</v>
       </c>
       <c r="F105" s="3"/>
@@ -6382,7 +6700,10 @@
       <c r="H105" s="3"/>
       <c r="I105" s="3"/>
       <c r="J105" s="3"/>
-      <c r="K105" s="3"/>
+      <c r="K105" s="21">
+        <f t="shared" si="5"/>
+        <v>151666.66666666669</v>
+      </c>
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
@@ -6408,11 +6729,11 @@
         <v>241000</v>
       </c>
       <c r="D106" s="4">
-        <f t="shared" si="2"/>
-        <v>48200</v>
+        <f t="shared" si="3"/>
+        <v>40166.666666666657</v>
       </c>
       <c r="E106" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">KIT 5 CARTUCCE 650 MB </v>
       </c>
       <c r="F106" s="3"/>
@@ -6420,7 +6741,10 @@
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3"/>
-      <c r="K106" s="3"/>
+      <c r="K106" s="21">
+        <f t="shared" si="5"/>
+        <v>40166.666666666672</v>
+      </c>
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
       <c r="N106" s="3"/>
@@ -6444,11 +6768,11 @@
       <c r="B107" s="3"/>
       <c r="C107" s="4"/>
       <c r="D107" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E107" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">CD ROM </v>
       </c>
       <c r="F107" s="3"/>
@@ -6456,7 +6780,10 @@
       <c r="H107" s="3"/>
       <c r="I107" s="3"/>
       <c r="J107" s="3"/>
-      <c r="K107" s="3"/>
+      <c r="K107" s="21">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
       <c r="N107" s="3"/>
@@ -6484,11 +6811,11 @@
         <v>112000</v>
       </c>
       <c r="D108" s="4">
-        <f t="shared" si="2"/>
-        <v>22400</v>
+        <f t="shared" si="3"/>
+        <v>18666.666666666657</v>
       </c>
       <c r="E108" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CD ROM 24X HITACHI CDR 8330 24 velocita',EIDE</v>
       </c>
       <c r="F108" s="3"/>
@@ -6496,7 +6823,10 @@
       <c r="H108" s="3"/>
       <c r="I108" s="3"/>
       <c r="J108" s="3"/>
-      <c r="K108" s="3"/>
+      <c r="K108" s="21">
+        <f t="shared" si="5"/>
+        <v>18666.666666666668</v>
+      </c>
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
       <c r="N108" s="3"/>
@@ -6524,11 +6854,11 @@
         <v>113000</v>
       </c>
       <c r="D109" s="4">
-        <f t="shared" si="2"/>
-        <v>22600</v>
+        <f t="shared" si="3"/>
+        <v>18833.333333333328</v>
       </c>
       <c r="E109" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CD ROM 24X CREATIVE 24 velocita',EIDE</v>
       </c>
       <c r="F109" s="3"/>
@@ -6536,7 +6866,10 @@
       <c r="H109" s="3"/>
       <c r="I109" s="3"/>
       <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
+      <c r="K109" s="21">
+        <f t="shared" si="5"/>
+        <v>18833.333333333336</v>
+      </c>
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
       <c r="N109" s="3"/>
@@ -6564,11 +6897,11 @@
         <v>121000</v>
       </c>
       <c r="D110" s="4">
-        <f t="shared" si="2"/>
-        <v>24200</v>
+        <f t="shared" si="3"/>
+        <v>20166.666666666657</v>
       </c>
       <c r="E110" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CD ROM 24X PIONEER 502-S Bulk 24 velocita',EIDE,SLOT-IN</v>
       </c>
       <c r="F110" s="3"/>
@@ -6576,7 +6909,10 @@
       <c r="H110" s="3"/>
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
+      <c r="K110" s="21">
+        <f t="shared" si="5"/>
+        <v>20166.666666666668</v>
+      </c>
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
@@ -6604,11 +6940,11 @@
         <v>160000</v>
       </c>
       <c r="D111" s="4">
-        <f t="shared" si="2"/>
-        <v>32000</v>
+        <f t="shared" si="3"/>
+        <v>26666.666666666657</v>
       </c>
       <c r="E111" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CD ROM 34X ASUS 34 velocita',EIDE</v>
       </c>
       <c r="F111" s="3"/>
@@ -6616,7 +6952,10 @@
       <c r="H111" s="3"/>
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
-      <c r="K111" s="3"/>
+      <c r="K111" s="21">
+        <f t="shared" si="5"/>
+        <v>26666.666666666668</v>
+      </c>
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
       <c r="N111" s="3"/>
@@ -6644,11 +6983,11 @@
         <v>195000</v>
       </c>
       <c r="D112" s="4">
-        <f t="shared" si="2"/>
-        <v>39000</v>
+        <f t="shared" si="3"/>
+        <v>32500</v>
       </c>
       <c r="E112" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CD ROM 24X SCSI NEC 24 velocita',SCSI</v>
       </c>
       <c r="F112" s="3"/>
@@ -6656,7 +6995,10 @@
       <c r="H112" s="3"/>
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
-      <c r="K112" s="3"/>
+      <c r="K112" s="21">
+        <f t="shared" si="5"/>
+        <v>32500</v>
+      </c>
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
       <c r="N112" s="3"/>
@@ -6684,11 +7026,11 @@
         <v>215000</v>
       </c>
       <c r="D113" s="4">
-        <f t="shared" si="2"/>
-        <v>43000</v>
+        <f t="shared" si="3"/>
+        <v>35833.333333333314</v>
       </c>
       <c r="E113" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CD ROM 32X SCSI WAITEC 32 velocita',SCSI</v>
       </c>
       <c r="F113" s="3"/>
@@ -6696,7 +7038,10 @@
       <c r="H113" s="3"/>
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
-      <c r="K113" s="3"/>
+      <c r="K113" s="21">
+        <f t="shared" si="5"/>
+        <v>35833.333333333336</v>
+      </c>
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
       <c r="N113" s="3"/>
@@ -6724,11 +7069,11 @@
         <v>321000</v>
       </c>
       <c r="D114" s="4">
-        <f t="shared" si="2"/>
-        <v>64200</v>
+        <f t="shared" si="3"/>
+        <v>53500</v>
       </c>
       <c r="E114" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CD ROM PLEXTOR PX-32TSI 32 velocita',SCSI</v>
       </c>
       <c r="F114" s="3"/>
@@ -6736,7 +7081,10 @@
       <c r="H114" s="3"/>
       <c r="I114" s="3"/>
       <c r="J114" s="3"/>
-      <c r="K114" s="3"/>
+      <c r="K114" s="21">
+        <f t="shared" si="5"/>
+        <v>53500</v>
+      </c>
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
       <c r="N114" s="3"/>
@@ -6764,11 +7112,11 @@
         <v>614000</v>
       </c>
       <c r="D115" s="4">
-        <f t="shared" si="2"/>
-        <v>122800</v>
+        <f t="shared" si="3"/>
+        <v>102333.33333333331</v>
       </c>
       <c r="E115" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>DVD CREATIVE KIT ENCORE DXR2 CREATIVE</v>
       </c>
       <c r="F115" s="3"/>
@@ -6776,7 +7124,10 @@
       <c r="H115" s="3"/>
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
-      <c r="K115" s="3"/>
+      <c r="K115" s="21">
+        <f t="shared" si="5"/>
+        <v>102333.33333333334</v>
+      </c>
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
       <c r="N115" s="3"/>
@@ -6800,11 +7151,11 @@
       <c r="B116" s="3"/>
       <c r="C116" s="4"/>
       <c r="D116" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E116" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">MASTERIZZATORI </v>
       </c>
       <c r="F116" s="3"/>
@@ -6812,7 +7163,10 @@
       <c r="H116" s="3"/>
       <c r="I116" s="3"/>
       <c r="J116" s="3"/>
-      <c r="K116" s="3"/>
+      <c r="K116" s="21">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
       <c r="N116" s="3"/>
@@ -6840,11 +7194,11 @@
         <v>30000</v>
       </c>
       <c r="D117" s="4">
-        <f t="shared" si="2"/>
-        <v>6000</v>
+        <f t="shared" si="3"/>
+        <v>5000</v>
       </c>
       <c r="E117" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CONFEZIONE 10 CDR 74' Kit 10 pz.</v>
       </c>
       <c r="F117" s="3"/>
@@ -6852,7 +7206,10 @@
       <c r="H117" s="3"/>
       <c r="I117" s="3"/>
       <c r="J117" s="3"/>
-      <c r="K117" s="3"/>
+      <c r="K117" s="21">
+        <f t="shared" si="5"/>
+        <v>5000</v>
+      </c>
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
       <c r="N117" s="3"/>
@@ -6880,11 +7237,11 @@
         <v>34000</v>
       </c>
       <c r="D118" s="4">
-        <f t="shared" si="2"/>
-        <v>6800</v>
+        <f t="shared" si="3"/>
+        <v>5666.6666666666642</v>
       </c>
       <c r="E118" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CD RISCRIVIBILE 74' VERBATIM</v>
       </c>
       <c r="F118" s="3"/>
@@ -6892,7 +7249,10 @@
       <c r="H118" s="3"/>
       <c r="I118" s="3"/>
       <c r="J118" s="3"/>
-      <c r="K118" s="3"/>
+      <c r="K118" s="21">
+        <f t="shared" si="5"/>
+        <v>5666.666666666667</v>
+      </c>
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
       <c r="N118" s="3"/>
@@ -6920,11 +7280,11 @@
         <v>35000</v>
       </c>
       <c r="D119" s="4">
-        <f t="shared" si="2"/>
-        <v>7000</v>
+        <f t="shared" si="3"/>
+        <v>5833.3333333333321</v>
       </c>
       <c r="E119" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CONFEZIONE 10 CDR 74' KODAK Kit 10 pz.</v>
       </c>
       <c r="F119" s="3"/>
@@ -6932,7 +7292,10 @@
       <c r="H119" s="3"/>
       <c r="I119" s="3"/>
       <c r="J119" s="3"/>
-      <c r="K119" s="3"/>
+      <c r="K119" s="21">
+        <f t="shared" si="5"/>
+        <v>5833.3333333333339</v>
+      </c>
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
       <c r="N119" s="3"/>
@@ -6960,11 +7323,11 @@
         <v>77000</v>
       </c>
       <c r="D120" s="4">
-        <f t="shared" si="2"/>
-        <v>15400</v>
+        <f t="shared" si="3"/>
+        <v>12833.333333333328</v>
       </c>
       <c r="E120" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>SOFTWARE LABELLER CD KIT Software per creazione etichette CD</v>
       </c>
       <c r="F120" s="3"/>
@@ -6972,7 +7335,10 @@
       <c r="H120" s="3"/>
       <c r="I120" s="3"/>
       <c r="J120" s="3"/>
-      <c r="K120" s="3"/>
+      <c r="K120" s="21">
+        <f t="shared" si="5"/>
+        <v>12833.333333333334</v>
+      </c>
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
       <c r="N120" s="3"/>
@@ -7000,11 +7366,11 @@
         <v>723000</v>
       </c>
       <c r="D121" s="4">
-        <f t="shared" si="2"/>
-        <v>144600</v>
+        <f t="shared" si="3"/>
+        <v>120500</v>
       </c>
       <c r="E121" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>WAITEC WT48/1 - GEAR - int. 4 WRITE 8 READ</v>
       </c>
       <c r="F121" s="3"/>
@@ -7012,7 +7378,10 @@
       <c r="H121" s="3"/>
       <c r="I121" s="3"/>
       <c r="J121" s="3"/>
-      <c r="K121" s="3"/>
+      <c r="K121" s="21">
+        <f t="shared" si="5"/>
+        <v>120500</v>
+      </c>
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
       <c r="N121" s="3"/>
@@ -7040,11 +7409,11 @@
         <v>742000</v>
       </c>
       <c r="D122" s="4">
-        <f t="shared" si="2"/>
-        <v>148400</v>
+        <f t="shared" si="3"/>
+        <v>123666.66666666663</v>
       </c>
       <c r="E122" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>WAITEC 2036EI/1 - SOFTWARE  CD RISCRIVIBILE 2REW,2WRI,6READ, EIDE</v>
       </c>
       <c r="F122" s="3"/>
@@ -7052,7 +7421,10 @@
       <c r="H122" s="3"/>
       <c r="I122" s="3"/>
       <c r="J122" s="3"/>
-      <c r="K122" s="3"/>
+      <c r="K122" s="21">
+        <f t="shared" si="5"/>
+        <v>123666.66666666667</v>
+      </c>
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
       <c r="N122" s="3"/>
@@ -7080,11 +7452,11 @@
         <v>778000</v>
       </c>
       <c r="D123" s="4">
-        <f t="shared" si="2"/>
-        <v>155600</v>
+        <f t="shared" si="3"/>
+        <v>129666.66666666663</v>
       </c>
       <c r="E123" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>RICOH MP6200ADP + SOFT.+5 CDR CD RISCRIVIBILE 2REW,2WRI,6R E-IDE</v>
       </c>
       <c r="F123" s="3"/>
@@ -7092,7 +7464,10 @@
       <c r="H123" s="3"/>
       <c r="I123" s="3"/>
       <c r="J123" s="3"/>
-      <c r="K123" s="3"/>
+      <c r="K123" s="21">
+        <f t="shared" si="5"/>
+        <v>129666.66666666667</v>
+      </c>
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
       <c r="N123" s="3"/>
@@ -7120,11 +7495,11 @@
         <v>878000</v>
       </c>
       <c r="D124" s="4">
-        <f t="shared" si="2"/>
-        <v>175600</v>
+        <f t="shared" si="3"/>
+        <v>146333.33333333326</v>
       </c>
       <c r="E124" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>RICOH MP6200SR - SOFTWARE SCSI CD RISCRIVIBILE 2REW,2WRI,6READ, SCSI</v>
       </c>
       <c r="F124" s="3"/>
@@ -7132,7 +7507,10 @@
       <c r="H124" s="3"/>
       <c r="I124" s="3"/>
       <c r="J124" s="3"/>
-      <c r="K124" s="3"/>
+      <c r="K124" s="21">
+        <f t="shared" si="5"/>
+        <v>146333.33333333334</v>
+      </c>
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
       <c r="N124" s="3"/>
@@ -7160,11 +7538,11 @@
         <v>883000</v>
       </c>
       <c r="D125" s="4">
-        <f t="shared" si="2"/>
-        <v>176600</v>
+        <f t="shared" si="3"/>
+        <v>147166.66666666663</v>
       </c>
       <c r="E125" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>WAITEC 2026/1 - SOFTWARE SCSI CD RISCRIVIBILE 2REW,2WRI,6READ, SCSI</v>
       </c>
       <c r="F125" s="3"/>
@@ -7172,7 +7550,10 @@
       <c r="H125" s="3"/>
       <c r="I125" s="3"/>
       <c r="J125" s="3"/>
-      <c r="K125" s="3"/>
+      <c r="K125" s="21">
+        <f t="shared" si="5"/>
+        <v>147166.66666666669</v>
+      </c>
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
       <c r="N125" s="3"/>
@@ -7200,11 +7581,11 @@
         <v>913000</v>
       </c>
       <c r="D126" s="4">
-        <f t="shared" si="2"/>
-        <v>182600</v>
+        <f t="shared" si="3"/>
+        <v>152166.66666666663</v>
       </c>
       <c r="E126" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CDR 480i PLASMON EASY CD int. 4 WRITE 8 READ</v>
       </c>
       <c r="F126" s="3"/>
@@ -7212,7 +7593,10 @@
       <c r="H126" s="3"/>
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
-      <c r="K126" s="3"/>
+      <c r="K126" s="21">
+        <f t="shared" si="5"/>
+        <v>152166.66666666669</v>
+      </c>
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
       <c r="N126" s="3"/>
@@ -7240,11 +7624,11 @@
         <v>1125000</v>
       </c>
       <c r="D127" s="4">
-        <f t="shared" si="2"/>
-        <v>225000</v>
+        <f t="shared" si="3"/>
+        <v>187500</v>
       </c>
       <c r="E127" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CDR 480e PLASMON EASY CD ext. 4 WRITE 8 READ</v>
       </c>
       <c r="F127" s="3"/>
@@ -7252,7 +7636,10 @@
       <c r="H127" s="3"/>
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
-      <c r="K127" s="3"/>
+      <c r="K127" s="21">
+        <f t="shared" si="5"/>
+        <v>187500</v>
+      </c>
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
       <c r="N127" s="3"/>
@@ -7276,11 +7663,11 @@
       <c r="B128" s="3"/>
       <c r="C128" s="4"/>
       <c r="D128" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E128" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">MEMORIE </v>
       </c>
       <c r="F128" s="3"/>
@@ -7288,7 +7675,10 @@
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
-      <c r="K128" s="3"/>
+      <c r="K128" s="21">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
       <c r="N128" s="3"/>
@@ -7314,11 +7704,11 @@
         <v>33000</v>
       </c>
       <c r="D129" s="4">
-        <f t="shared" si="2"/>
-        <v>6600</v>
+        <f t="shared" si="3"/>
+        <v>5500</v>
       </c>
       <c r="E129" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">SIMM 8MB 72 PIN (EDO) </v>
       </c>
       <c r="F129" s="3"/>
@@ -7326,7 +7716,10 @@
       <c r="H129" s="3"/>
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
-      <c r="K129" s="3"/>
+      <c r="K129" s="21">
+        <f t="shared" si="5"/>
+        <v>5500</v>
+      </c>
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
       <c r="N129" s="3"/>
@@ -7352,11 +7745,11 @@
         <v>52000</v>
       </c>
       <c r="D130" s="4">
-        <f t="shared" si="2"/>
-        <v>10400</v>
+        <f t="shared" si="3"/>
+        <v>8666.6666666666642</v>
       </c>
       <c r="E130" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">SIMM 16MB 72 PIN (EDO) </v>
       </c>
       <c r="F130" s="3"/>
@@ -7364,7 +7757,10 @@
       <c r="H130" s="3"/>
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
-      <c r="K130" s="3"/>
+      <c r="K130" s="21">
+        <f t="shared" si="5"/>
+        <v>8666.6666666666679</v>
+      </c>
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
       <c r="N130" s="3"/>
@@ -7390,11 +7786,11 @@
         <v>97000</v>
       </c>
       <c r="D131" s="4">
-        <f t="shared" ref="D131:D194" si="4">C131*$G$2</f>
-        <v>19400</v>
+        <f t="shared" ref="D131:D194" si="6">C131-(C131/(1+($G$2)))</f>
+        <v>16166.666666666657</v>
       </c>
       <c r="E131" s="3" t="str">
-        <f t="shared" ref="E131:E194" si="5">_xlfn.CONCAT(A131," ",B131)</f>
+        <f t="shared" ref="E131:E194" si="7">_xlfn.CONCAT(A131," ",B131)</f>
         <v xml:space="preserve">SIMM 32MB 72 PIN (EDO) </v>
       </c>
       <c r="F131" s="3"/>
@@ -7402,7 +7798,10 @@
       <c r="H131" s="3"/>
       <c r="I131" s="3"/>
       <c r="J131" s="3"/>
-      <c r="K131" s="3"/>
+      <c r="K131" s="21">
+        <f t="shared" ref="K131:K194" si="8">(C131*$G$2)/$H$2</f>
+        <v>16166.666666666668</v>
+      </c>
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
@@ -7428,11 +7827,11 @@
       </c>
       <c r="C132" s="4"/>
       <c r="D132" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E132" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">MODEM FAX - VIDEOCAMERA  </v>
       </c>
       <c r="F132" s="3"/>
@@ -7440,7 +7839,10 @@
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
-      <c r="K132" s="3"/>
+      <c r="K132" s="21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
       <c r="N132" s="3"/>
@@ -7468,11 +7870,11 @@
         <v>131000</v>
       </c>
       <c r="D133" s="4">
-        <f t="shared" si="4"/>
-        <v>26200</v>
+        <f t="shared" si="6"/>
+        <v>21833.333333333328</v>
       </c>
       <c r="E133" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F MOTOROLA 3400PRO 28800 EXT MOTOROLA</v>
       </c>
       <c r="F133" s="3"/>
@@ -7480,7 +7882,10 @@
       <c r="H133" s="3"/>
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
-      <c r="K133" s="3"/>
+      <c r="K133" s="21">
+        <f t="shared" si="8"/>
+        <v>21833.333333333336</v>
+      </c>
       <c r="L133" s="3"/>
       <c r="M133" s="3"/>
       <c r="N133" s="3"/>
@@ -7508,11 +7913,11 @@
         <v>169000</v>
       </c>
       <c r="D134" s="4">
-        <f t="shared" si="4"/>
-        <v>33800</v>
+        <f t="shared" si="6"/>
+        <v>28166.666666666657</v>
       </c>
       <c r="E134" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F LEONARDO PC 33600 INT OEM DIGICOM</v>
       </c>
       <c r="F134" s="3"/>
@@ -7520,7 +7925,10 @@
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
-      <c r="K134" s="3"/>
+      <c r="K134" s="21">
+        <f t="shared" si="8"/>
+        <v>28166.666666666668</v>
+      </c>
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
       <c r="N134" s="3"/>
@@ -7548,11 +7956,11 @@
         <v>190000</v>
       </c>
       <c r="D135" s="4">
-        <f t="shared" si="4"/>
-        <v>38000</v>
+        <f t="shared" si="6"/>
+        <v>31666.666666666657</v>
       </c>
       <c r="E135" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F LEONARDO PC 33600 EXT DIGICOM</v>
       </c>
       <c r="F135" s="3"/>
@@ -7560,7 +7968,10 @@
       <c r="H135" s="3"/>
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
-      <c r="K135" s="3"/>
+      <c r="K135" s="21">
+        <f t="shared" si="8"/>
+        <v>31666.666666666668</v>
+      </c>
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
       <c r="N135" s="3"/>
@@ -7588,11 +7999,11 @@
         <v>191000</v>
       </c>
       <c r="D136" s="4">
-        <f t="shared" si="4"/>
-        <v>38200</v>
+        <f t="shared" si="6"/>
+        <v>31833.333333333314</v>
       </c>
       <c r="E136" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F MOTOROLA 56K  EXT BULK MOTOROLA</v>
       </c>
       <c r="F136" s="3"/>
@@ -7600,7 +8011,10 @@
       <c r="H136" s="3"/>
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
-      <c r="K136" s="3"/>
+      <c r="K136" s="21">
+        <f t="shared" si="8"/>
+        <v>31833.333333333336</v>
+      </c>
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
       <c r="N136" s="3"/>
@@ -7628,11 +8042,11 @@
         <v>197000</v>
       </c>
       <c r="D137" s="4">
-        <f t="shared" si="4"/>
-        <v>39400</v>
+        <f t="shared" si="6"/>
+        <v>32833.333333333314</v>
       </c>
       <c r="E137" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F LEONARDO PC 33600 INT DIGICOM</v>
       </c>
       <c r="F137" s="3"/>
@@ -7640,7 +8054,10 @@
       <c r="H137" s="3"/>
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
-      <c r="K137" s="3"/>
+      <c r="K137" s="21">
+        <f t="shared" si="8"/>
+        <v>32833.333333333336</v>
+      </c>
       <c r="L137" s="3"/>
       <c r="M137" s="3"/>
       <c r="N137" s="3"/>
@@ -7668,11 +8085,11 @@
         <v>201000</v>
       </c>
       <c r="D138" s="4">
-        <f t="shared" si="4"/>
-        <v>40200</v>
+        <f t="shared" si="6"/>
+        <v>33500</v>
       </c>
       <c r="E138" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F TIZIANO 33600 EXT DIGICOM</v>
       </c>
       <c r="F138" s="3"/>
@@ -7680,7 +8097,10 @@
       <c r="H138" s="3"/>
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
-      <c r="K138" s="3"/>
+      <c r="K138" s="21">
+        <f t="shared" si="8"/>
+        <v>33500</v>
+      </c>
       <c r="L138" s="3"/>
       <c r="M138" s="3"/>
       <c r="N138" s="3"/>
@@ -7708,11 +8128,11 @@
         <v>220000</v>
       </c>
       <c r="D139" s="4">
-        <f t="shared" si="4"/>
-        <v>44000</v>
+        <f t="shared" si="6"/>
+        <v>36666.666666666657</v>
       </c>
       <c r="E139" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F SPORTSTER FLASH 33600 EXT ITA  US ROBOTICS</v>
       </c>
       <c r="F139" s="3"/>
@@ -7720,7 +8140,10 @@
       <c r="H139" s="3"/>
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
-      <c r="K139" s="3"/>
+      <c r="K139" s="21">
+        <f t="shared" si="8"/>
+        <v>36666.666666666672</v>
+      </c>
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
       <c r="N139" s="3"/>
@@ -7748,11 +8171,11 @@
         <v>250000</v>
       </c>
       <c r="D140" s="4">
-        <f t="shared" si="4"/>
-        <v>50000</v>
+        <f t="shared" si="6"/>
+        <v>41666.666666666657</v>
       </c>
       <c r="E140" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F MOTOROLA 56K  EXT MOTOROLA</v>
       </c>
       <c r="F140" s="3"/>
@@ -7760,7 +8183,10 @@
       <c r="H140" s="3"/>
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
-      <c r="K140" s="3"/>
+      <c r="K140" s="21">
+        <f t="shared" si="8"/>
+        <v>41666.666666666672</v>
+      </c>
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
       <c r="N140" s="3"/>
@@ -7788,11 +8214,11 @@
         <v>257000</v>
       </c>
       <c r="D141" s="4">
-        <f t="shared" si="4"/>
-        <v>51400</v>
+        <f t="shared" si="6"/>
+        <v>42833.333333333314</v>
       </c>
       <c r="E141" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F LEONARDO  56K  EXT DIGICOM</v>
       </c>
       <c r="F141" s="3"/>
@@ -7800,7 +8226,10 @@
       <c r="H141" s="3"/>
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
-      <c r="K141" s="3"/>
+      <c r="K141" s="21">
+        <f t="shared" si="8"/>
+        <v>42833.333333333336</v>
+      </c>
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
       <c r="N141" s="3"/>
@@ -7828,11 +8257,11 @@
         <v>278000</v>
       </c>
       <c r="D142" s="4">
-        <f t="shared" si="4"/>
-        <v>55600</v>
+        <f t="shared" si="6"/>
+        <v>46333.333333333314</v>
       </c>
       <c r="E142" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F TIZIANO 56K EXT DIGICOM</v>
       </c>
       <c r="F142" s="3"/>
@@ -7840,7 +8269,10 @@
       <c r="H142" s="3"/>
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
-      <c r="K142" s="3"/>
+      <c r="K142" s="21">
+        <f t="shared" si="8"/>
+        <v>46333.333333333336</v>
+      </c>
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3"/>
@@ -7868,11 +8300,11 @@
         <v>280000</v>
       </c>
       <c r="D143" s="4">
-        <f t="shared" si="4"/>
-        <v>56000</v>
+        <f t="shared" si="6"/>
+        <v>46666.666666666657</v>
       </c>
       <c r="E143" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F SPORTSTER MESSAGE PLUS US ROBOTICS</v>
       </c>
       <c r="F143" s="3"/>
@@ -7880,7 +8312,10 @@
       <c r="H143" s="3"/>
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
-      <c r="K143" s="3"/>
+      <c r="K143" s="21">
+        <f t="shared" si="8"/>
+        <v>46666.666666666672</v>
+      </c>
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
       <c r="N143" s="3"/>
@@ -7908,11 +8343,11 @@
         <v>300000</v>
       </c>
       <c r="D144" s="4">
-        <f t="shared" si="4"/>
-        <v>60000</v>
+        <f t="shared" si="6"/>
+        <v>50000</v>
       </c>
       <c r="E144" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F LEONARDO PCMCIA 33600 DIGICOM</v>
       </c>
       <c r="F144" s="3"/>
@@ -7920,7 +8355,10 @@
       <c r="H144" s="3"/>
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
-      <c r="K144" s="3"/>
+      <c r="K144" s="21">
+        <f t="shared" si="8"/>
+        <v>50000</v>
+      </c>
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
@@ -7948,11 +8386,11 @@
         <v>305000</v>
       </c>
       <c r="D145" s="4">
-        <f t="shared" si="4"/>
-        <v>61000</v>
+        <f t="shared" si="6"/>
+        <v>50833.333333333314</v>
       </c>
       <c r="E145" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>KIT VIDEOCONFERENZA "GALILEO" DIGICOM / H.324</v>
       </c>
       <c r="F145" s="3"/>
@@ -7960,7 +8398,10 @@
       <c r="H145" s="3"/>
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
-      <c r="K145" s="3"/>
+      <c r="K145" s="21">
+        <f t="shared" si="8"/>
+        <v>50833.333333333336</v>
+      </c>
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
       <c r="N145" s="3"/>
@@ -7988,11 +8429,11 @@
         <v>335000</v>
       </c>
       <c r="D146" s="4">
-        <f t="shared" si="4"/>
-        <v>67000</v>
+        <f t="shared" si="6"/>
+        <v>55833.333333333314</v>
       </c>
       <c r="E146" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>MODEM ISDN TINTORETTO EXT. DIGICOM</v>
       </c>
       <c r="F146" s="3"/>
@@ -8000,7 +8441,10 @@
       <c r="H146" s="3"/>
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
-      <c r="K146" s="3"/>
+      <c r="K146" s="21">
+        <f t="shared" si="8"/>
+        <v>55833.333333333336</v>
+      </c>
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
       <c r="N146" s="3"/>
@@ -8028,11 +8472,11 @@
         <v>360000</v>
       </c>
       <c r="D147" s="4">
-        <f t="shared" si="4"/>
-        <v>72000</v>
+        <f t="shared" si="6"/>
+        <v>60000</v>
       </c>
       <c r="E147" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F LEONARDO PCMCIA 56K DIGICOM</v>
       </c>
       <c r="F147" s="3"/>
@@ -8040,7 +8484,10 @@
       <c r="H147" s="3"/>
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
-      <c r="K147" s="3"/>
+      <c r="K147" s="21">
+        <f t="shared" si="8"/>
+        <v>60000</v>
+      </c>
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
       <c r="N147" s="3"/>
@@ -8068,11 +8515,11 @@
         <v>429000</v>
       </c>
       <c r="D148" s="4">
-        <f t="shared" si="4"/>
-        <v>85800</v>
+        <f t="shared" si="6"/>
+        <v>71500</v>
       </c>
       <c r="E148" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>MODEM MOTOROLA ISDN  EXT.64/128K MOTOROLA</v>
       </c>
       <c r="F148" s="3"/>
@@ -8080,7 +8527,10 @@
       <c r="H148" s="3"/>
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
-      <c r="K148" s="3"/>
+      <c r="K148" s="21">
+        <f t="shared" si="8"/>
+        <v>71500</v>
+      </c>
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
       <c r="N148" s="3"/>
@@ -8108,11 +8558,11 @@
         <v>701000</v>
       </c>
       <c r="D149" s="4">
-        <f t="shared" si="4"/>
-        <v>140200</v>
+        <f t="shared" si="6"/>
+        <v>116833.33333333326</v>
       </c>
       <c r="E149" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>M/F ISDN DONATELLO EXT. DIGICOM</v>
       </c>
       <c r="F149" s="3"/>
@@ -8120,7 +8570,10 @@
       <c r="H149" s="3"/>
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
-      <c r="K149" s="3"/>
+      <c r="K149" s="21">
+        <f t="shared" si="8"/>
+        <v>116833.33333333334</v>
+      </c>
       <c r="L149" s="3"/>
       <c r="M149" s="3"/>
       <c r="N149" s="3"/>
@@ -8144,11 +8597,11 @@
       <c r="B150" s="3"/>
       <c r="C150" s="4"/>
       <c r="D150" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E150" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">MULTIMEDIA </v>
       </c>
       <c r="F150" s="3"/>
@@ -8156,7 +8609,10 @@
       <c r="H150" s="3"/>
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
-      <c r="K150" s="3"/>
+      <c r="K150" s="21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
       <c r="N150" s="3"/>
@@ -8184,11 +8640,11 @@
         <v>90000</v>
       </c>
       <c r="D151" s="4">
-        <f t="shared" si="4"/>
-        <v>18000</v>
+        <f t="shared" si="6"/>
+        <v>15000</v>
       </c>
       <c r="E151" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>SOUND AXP201/U PCI 64 Asus - ESS Maestro-1 Audio accellerator</v>
       </c>
       <c r="F151" s="3"/>
@@ -8196,7 +8652,10 @@
       <c r="H151" s="3"/>
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
-      <c r="K151" s="3"/>
+      <c r="K151" s="21">
+        <f t="shared" si="8"/>
+        <v>15000</v>
+      </c>
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
       <c r="N151" s="3"/>
@@ -8224,11 +8683,11 @@
         <v>69000</v>
       </c>
       <c r="D152" s="4">
-        <f t="shared" si="4"/>
-        <v>13800</v>
+        <f t="shared" si="6"/>
+        <v>11500</v>
       </c>
       <c r="E152" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>SOUND BLASTER 16 PnP  O.E.M. Creative</v>
       </c>
       <c r="F152" s="3"/>
@@ -8236,7 +8695,10 @@
       <c r="H152" s="3"/>
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
-      <c r="K152" s="3"/>
+      <c r="K152" s="21">
+        <f t="shared" si="8"/>
+        <v>11500</v>
+      </c>
       <c r="L152" s="3"/>
       <c r="M152" s="3"/>
       <c r="N152" s="3"/>
@@ -8264,11 +8726,11 @@
         <v>89000</v>
       </c>
       <c r="D153" s="4">
-        <f t="shared" si="4"/>
-        <v>17800</v>
+        <f t="shared" si="6"/>
+        <v>14833.333333333328</v>
       </c>
       <c r="E153" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>SOUND BLASTER 16 PnP NO IDE Creative</v>
       </c>
       <c r="F153" s="3"/>
@@ -8276,7 +8738,10 @@
       <c r="H153" s="3"/>
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
-      <c r="K153" s="3"/>
+      <c r="K153" s="21">
+        <f t="shared" si="8"/>
+        <v>14833.333333333334</v>
+      </c>
       <c r="L153" s="3"/>
       <c r="M153" s="3"/>
       <c r="N153" s="3"/>
@@ -8304,11 +8769,11 @@
         <v>138000</v>
       </c>
       <c r="D154" s="4">
-        <f t="shared" si="4"/>
-        <v>27600</v>
+        <f t="shared" si="6"/>
+        <v>23000</v>
       </c>
       <c r="E154" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>SOUND BLASTER AWE64 STD OEM Creative</v>
       </c>
       <c r="F154" s="3"/>
@@ -8316,7 +8781,10 @@
       <c r="H154" s="3"/>
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
-      <c r="K154" s="3"/>
+      <c r="K154" s="21">
+        <f t="shared" si="8"/>
+        <v>23000</v>
+      </c>
       <c r="L154" s="3"/>
       <c r="M154" s="3"/>
       <c r="N154" s="3"/>
@@ -8344,11 +8812,11 @@
         <v>196000</v>
       </c>
       <c r="D155" s="4">
-        <f t="shared" si="4"/>
-        <v>39200</v>
+        <f t="shared" si="6"/>
+        <v>32666.666666666657</v>
       </c>
       <c r="E155" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>SOUND BLASTER AWE64 STANDARD Creative</v>
       </c>
       <c r="F155" s="3"/>
@@ -8356,7 +8824,10 @@
       <c r="H155" s="3"/>
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
-      <c r="K155" s="3"/>
+      <c r="K155" s="21">
+        <f t="shared" si="8"/>
+        <v>32666.666666666668</v>
+      </c>
       <c r="L155" s="3"/>
       <c r="M155" s="3"/>
       <c r="N155" s="3"/>
@@ -8384,11 +8855,11 @@
         <v>329000</v>
       </c>
       <c r="D156" s="4">
-        <f t="shared" si="4"/>
-        <v>65800</v>
+        <f t="shared" si="6"/>
+        <v>54833.333333333314</v>
       </c>
       <c r="E156" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>SOUND BLASTER AWE64 GOLD PNP  Creative</v>
       </c>
       <c r="F156" s="3"/>
@@ -8396,7 +8867,10 @@
       <c r="H156" s="3"/>
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
-      <c r="K156" s="3"/>
+      <c r="K156" s="21">
+        <f t="shared" si="8"/>
+        <v>54833.333333333336</v>
+      </c>
       <c r="L156" s="3"/>
       <c r="M156" s="3"/>
       <c r="N156" s="3"/>
@@ -8424,11 +8898,11 @@
         <v>295000</v>
       </c>
       <c r="D157" s="4">
-        <f t="shared" si="4"/>
-        <v>59000</v>
+        <f t="shared" si="6"/>
+        <v>49166.666666666657</v>
       </c>
       <c r="E157" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>KIT "DISCOVERY AWE64" 24X PNP Creative</v>
       </c>
       <c r="F157" s="3"/>
@@ -8436,7 +8910,10 @@
       <c r="H157" s="3"/>
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
-      <c r="K157" s="3"/>
+      <c r="K157" s="21">
+        <f t="shared" si="8"/>
+        <v>49166.666666666672</v>
+      </c>
       <c r="L157" s="3"/>
       <c r="M157" s="3"/>
       <c r="N157" s="3"/>
@@ -8464,11 +8941,11 @@
         <v>19000</v>
       </c>
       <c r="D158" s="4">
-        <f t="shared" si="4"/>
-        <v>3800</v>
+        <f t="shared" si="6"/>
+        <v>3166.6666666666661</v>
       </c>
       <c r="E158" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>SPEAKERS MLI-699 MLI-60</v>
       </c>
       <c r="F158" s="3"/>
@@ -8476,7 +8953,10 @@
       <c r="H158" s="3"/>
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
-      <c r="K158" s="3"/>
+      <c r="K158" s="21">
+        <f t="shared" si="8"/>
+        <v>3166.666666666667</v>
+      </c>
       <c r="L158" s="3"/>
       <c r="M158" s="3"/>
       <c r="N158" s="3"/>
@@ -8504,11 +8984,11 @@
         <v>26000</v>
       </c>
       <c r="D159" s="4">
-        <f t="shared" si="4"/>
-        <v>5200</v>
+        <f t="shared" si="6"/>
+        <v>4333.3333333333321</v>
       </c>
       <c r="E159" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>SPEAKER 25 W FS-60</v>
       </c>
       <c r="F159" s="3"/>
@@ -8516,7 +8996,10 @@
       <c r="H159" s="3"/>
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
-      <c r="K159" s="3"/>
+      <c r="K159" s="21">
+        <f t="shared" si="8"/>
+        <v>4333.3333333333339</v>
+      </c>
       <c r="L159" s="3"/>
       <c r="M159" s="3"/>
       <c r="N159" s="3"/>
@@ -8544,11 +9027,11 @@
         <v>28000</v>
       </c>
       <c r="D160" s="4">
-        <f t="shared" si="4"/>
-        <v>5600</v>
+        <f t="shared" si="6"/>
+        <v>4666.6666666666642</v>
       </c>
       <c r="E160" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>SPEAKER PROFESSIONAL 70 W FS-70</v>
       </c>
       <c r="F160" s="3"/>
@@ -8556,7 +9039,10 @@
       <c r="H160" s="3"/>
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
-      <c r="K160" s="3"/>
+      <c r="K160" s="21">
+        <f t="shared" si="8"/>
+        <v>4666.666666666667</v>
+      </c>
       <c r="L160" s="3"/>
       <c r="M160" s="3"/>
       <c r="N160" s="3"/>
@@ -8584,11 +9070,11 @@
         <v>56000</v>
       </c>
       <c r="D161" s="4">
-        <f t="shared" si="4"/>
-        <v>11200</v>
+        <f t="shared" si="6"/>
+        <v>9333.3333333333285</v>
       </c>
       <c r="E161" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>ULTRA SPEAKER 130W FS-100</v>
       </c>
       <c r="F161" s="3"/>
@@ -8596,7 +9082,10 @@
       <c r="H161" s="3"/>
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
-      <c r="K161" s="3"/>
+      <c r="K161" s="21">
+        <f t="shared" si="8"/>
+        <v>9333.3333333333339</v>
+      </c>
       <c r="L161" s="3"/>
       <c r="M161" s="3"/>
       <c r="N161" s="3"/>
@@ -8620,11 +9109,11 @@
       <c r="B162" s="3"/>
       <c r="C162" s="4"/>
       <c r="D162" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E162" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">MICROPROCESSORI </v>
       </c>
       <c r="F162" s="3"/>
@@ -8632,7 +9121,10 @@
       <c r="H162" s="3"/>
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
-      <c r="K162" s="3"/>
+      <c r="K162" s="21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="L162" s="3"/>
       <c r="M162" s="3"/>
       <c r="N162" s="3"/>
@@ -8658,11 +9150,11 @@
         <v>216000</v>
       </c>
       <c r="D163" s="4">
-        <f t="shared" si="4"/>
-        <v>43200</v>
+        <f t="shared" si="6"/>
+        <v>36000</v>
       </c>
       <c r="E163" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">PENTIUM 166 INTEL MMX </v>
       </c>
       <c r="F163" s="3"/>
@@ -8670,7 +9162,10 @@
       <c r="H163" s="3"/>
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
-      <c r="K163" s="3"/>
+      <c r="K163" s="21">
+        <f t="shared" si="8"/>
+        <v>36000</v>
+      </c>
       <c r="L163" s="3"/>
       <c r="M163" s="3"/>
       <c r="N163" s="3"/>
@@ -8696,11 +9191,11 @@
         <v>250000</v>
       </c>
       <c r="D164" s="4">
-        <f t="shared" si="4"/>
-        <v>50000</v>
+        <f t="shared" si="6"/>
+        <v>41666.666666666657</v>
       </c>
       <c r="E164" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">PENTIUM 200 INTEL MMX </v>
       </c>
       <c r="F164" s="3"/>
@@ -8708,7 +9203,10 @@
       <c r="H164" s="3"/>
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
-      <c r="K164" s="3"/>
+      <c r="K164" s="21">
+        <f t="shared" si="8"/>
+        <v>41666.666666666672</v>
+      </c>
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
       <c r="N164" s="3"/>
@@ -8734,11 +9232,11 @@
         <v>382000</v>
       </c>
       <c r="D165" s="4">
-        <f t="shared" si="4"/>
-        <v>76400</v>
+        <f t="shared" si="6"/>
+        <v>63666.666666666628</v>
       </c>
       <c r="E165" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">PENTIUM 233 INTEL MMX </v>
       </c>
       <c r="F165" s="3"/>
@@ -8746,7 +9244,10 @@
       <c r="H165" s="3"/>
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
-      <c r="K165" s="3"/>
+      <c r="K165" s="21">
+        <f t="shared" si="8"/>
+        <v>63666.666666666672</v>
+      </c>
       <c r="L165" s="3"/>
       <c r="M165" s="3"/>
       <c r="N165" s="3"/>
@@ -8772,11 +9273,11 @@
         <v>524000</v>
       </c>
       <c r="D166" s="4">
-        <f t="shared" si="4"/>
-        <v>104800</v>
+        <f t="shared" si="6"/>
+        <v>87333.333333333314</v>
       </c>
       <c r="E166" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">PENTIUM II 233 INTEL 512k </v>
       </c>
       <c r="F166" s="3"/>
@@ -8784,7 +9285,10 @@
       <c r="H166" s="3"/>
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
-      <c r="K166" s="3"/>
+      <c r="K166" s="21">
+        <f t="shared" si="8"/>
+        <v>87333.333333333343</v>
+      </c>
       <c r="L166" s="3"/>
       <c r="M166" s="3"/>
       <c r="N166" s="3"/>
@@ -8810,11 +9314,11 @@
         <v>757000</v>
       </c>
       <c r="D167" s="4">
-        <f t="shared" si="4"/>
-        <v>151400</v>
+        <f t="shared" si="6"/>
+        <v>126166.66666666663</v>
       </c>
       <c r="E167" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">PENTIUM II 266 INTEL 512k </v>
       </c>
       <c r="F167" s="3"/>
@@ -8822,7 +9326,10 @@
       <c r="H167" s="3"/>
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
-      <c r="K167" s="3"/>
+      <c r="K167" s="21">
+        <f t="shared" si="8"/>
+        <v>126166.66666666667</v>
+      </c>
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
       <c r="N167" s="3"/>
@@ -8848,11 +9355,11 @@
         <v>1045000</v>
       </c>
       <c r="D168" s="4">
-        <f t="shared" si="4"/>
-        <v>209000</v>
+        <f t="shared" si="6"/>
+        <v>174166.66666666663</v>
       </c>
       <c r="E168" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">PENTIUM II 300 INTEL 512K </v>
       </c>
       <c r="F168" s="3"/>
@@ -8860,7 +9367,10 @@
       <c r="H168" s="3"/>
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
-      <c r="K168" s="3"/>
+      <c r="K168" s="21">
+        <f t="shared" si="8"/>
+        <v>174166.66666666669</v>
+      </c>
       <c r="L168" s="3"/>
       <c r="M168" s="3"/>
       <c r="N168" s="3"/>
@@ -8886,11 +9396,11 @@
         <v>1568000</v>
       </c>
       <c r="D169" s="4">
-        <f t="shared" si="4"/>
-        <v>313600</v>
+        <f t="shared" si="6"/>
+        <v>261333.33333333326</v>
       </c>
       <c r="E169" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">PENTIUM II 333 INTEL 512K </v>
       </c>
       <c r="F169" s="3"/>
@@ -8898,7 +9408,10 @@
       <c r="H169" s="3"/>
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
-      <c r="K169" s="3"/>
+      <c r="K169" s="21">
+        <f t="shared" si="8"/>
+        <v>261333.33333333334</v>
+      </c>
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3"/>
@@ -8924,11 +9437,11 @@
         <v>117000</v>
       </c>
       <c r="D170" s="4">
-        <f t="shared" si="4"/>
-        <v>23400</v>
+        <f t="shared" si="6"/>
+        <v>19500</v>
       </c>
       <c r="E170" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">SGS P 166+ </v>
       </c>
       <c r="F170" s="3"/>
@@ -8936,7 +9449,10 @@
       <c r="H170" s="3"/>
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
-      <c r="K170" s="3"/>
+      <c r="K170" s="21">
+        <f t="shared" si="8"/>
+        <v>19500</v>
+      </c>
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
       <c r="N170" s="3"/>
@@ -8962,11 +9478,11 @@
         <v>158000</v>
       </c>
       <c r="D171" s="4">
-        <f t="shared" si="4"/>
-        <v>31600</v>
+        <f t="shared" si="6"/>
+        <v>26333.333333333314</v>
       </c>
       <c r="E171" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">IBM 200 MX </v>
       </c>
       <c r="F171" s="3"/>
@@ -8974,7 +9490,10 @@
       <c r="H171" s="3"/>
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
-      <c r="K171" s="3"/>
+      <c r="K171" s="21">
+        <f t="shared" si="8"/>
+        <v>26333.333333333336</v>
+      </c>
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
       <c r="N171" s="3"/>
@@ -9000,11 +9519,11 @@
         <v>260000</v>
       </c>
       <c r="D172" s="4">
-        <f t="shared" si="4"/>
-        <v>52000</v>
+        <f t="shared" si="6"/>
+        <v>43333.333333333314</v>
       </c>
       <c r="E172" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">IBM 233 MX </v>
       </c>
       <c r="F172" s="3"/>
@@ -9012,7 +9531,10 @@
       <c r="H172" s="3"/>
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
-      <c r="K172" s="3"/>
+      <c r="K172" s="21">
+        <f t="shared" si="8"/>
+        <v>43333.333333333336</v>
+      </c>
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3"/>
@@ -9038,11 +9560,11 @@
         <v>193000</v>
       </c>
       <c r="D173" s="4">
-        <f t="shared" si="4"/>
-        <v>38600</v>
+        <f t="shared" si="6"/>
+        <v>32166.666666666657</v>
       </c>
       <c r="E173" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">AMD K6-166 </v>
       </c>
       <c r="F173" s="3"/>
@@ -9050,7 +9572,10 @@
       <c r="H173" s="3"/>
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
-      <c r="K173" s="3"/>
+      <c r="K173" s="21">
+        <f t="shared" si="8"/>
+        <v>32166.666666666668</v>
+      </c>
       <c r="L173" s="3"/>
       <c r="M173" s="3"/>
       <c r="N173" s="3"/>
@@ -9076,11 +9601,11 @@
         <v>270000</v>
       </c>
       <c r="D174" s="4">
-        <f t="shared" si="4"/>
-        <v>54000</v>
+        <f t="shared" si="6"/>
+        <v>45000</v>
       </c>
       <c r="E174" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">AMD K6-200 </v>
       </c>
       <c r="F174" s="3"/>
@@ -9088,7 +9613,10 @@
       <c r="H174" s="3"/>
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
-      <c r="K174" s="3"/>
+      <c r="K174" s="21">
+        <f t="shared" si="8"/>
+        <v>45000</v>
+      </c>
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
       <c r="N174" s="3"/>
@@ -9114,11 +9642,11 @@
         <v>314000</v>
       </c>
       <c r="D175" s="4">
-        <f t="shared" si="4"/>
-        <v>62800</v>
+        <f t="shared" si="6"/>
+        <v>52333.333333333314</v>
       </c>
       <c r="E175" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">AMD K6-233 </v>
       </c>
       <c r="F175" s="3"/>
@@ -9126,7 +9654,10 @@
       <c r="H175" s="3"/>
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
-      <c r="K175" s="3"/>
+      <c r="K175" s="21">
+        <f t="shared" si="8"/>
+        <v>52333.333333333336</v>
+      </c>
       <c r="L175" s="3"/>
       <c r="M175" s="3"/>
       <c r="N175" s="3"/>
@@ -9152,11 +9683,11 @@
         <v>894000</v>
       </c>
       <c r="D176" s="4">
-        <f t="shared" si="4"/>
-        <v>178800</v>
+        <f t="shared" si="6"/>
+        <v>149000</v>
       </c>
       <c r="E176" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">PENTIUM PRO 180 MZH </v>
       </c>
       <c r="F176" s="3"/>
@@ -9164,7 +9695,10 @@
       <c r="H176" s="3"/>
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
-      <c r="K176" s="3"/>
+      <c r="K176" s="21">
+        <f t="shared" si="8"/>
+        <v>149000</v>
+      </c>
       <c r="L176" s="3"/>
       <c r="M176" s="3"/>
       <c r="N176" s="3"/>
@@ -9190,11 +9724,11 @@
         <v>1040000</v>
       </c>
       <c r="D177" s="4">
-        <f t="shared" si="4"/>
-        <v>208000</v>
+        <f t="shared" si="6"/>
+        <v>173333.33333333326</v>
       </c>
       <c r="E177" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">PENTIUM PRO 200 MZH </v>
       </c>
       <c r="F177" s="3"/>
@@ -9202,7 +9736,10 @@
       <c r="H177" s="3"/>
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
-      <c r="K177" s="3"/>
+      <c r="K177" s="21">
+        <f t="shared" si="8"/>
+        <v>173333.33333333334</v>
+      </c>
       <c r="L177" s="3"/>
       <c r="M177" s="3"/>
       <c r="N177" s="3"/>
@@ -9228,11 +9765,11 @@
         <v>8000</v>
       </c>
       <c r="D178" s="4">
-        <f t="shared" si="4"/>
-        <v>1600</v>
+        <f t="shared" si="6"/>
+        <v>1333.333333333333</v>
       </c>
       <c r="E178" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">VENTOLINA PENTIUM 75-166 </v>
       </c>
       <c r="F178" s="3"/>
@@ -9240,7 +9777,10 @@
       <c r="H178" s="3"/>
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
-      <c r="K178" s="3"/>
+      <c r="K178" s="21">
+        <f t="shared" si="8"/>
+        <v>1333.3333333333335</v>
+      </c>
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
       <c r="N178" s="3"/>
@@ -9266,11 +9806,11 @@
         <v>10000</v>
       </c>
       <c r="D179" s="4">
-        <f t="shared" si="4"/>
-        <v>2000</v>
+        <f t="shared" si="6"/>
+        <v>1666.6666666666661</v>
       </c>
       <c r="E179" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">VENTOLINA PENTIUM 200 </v>
       </c>
       <c r="F179" s="3"/>
@@ -9278,7 +9818,10 @@
       <c r="H179" s="3"/>
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
-      <c r="K179" s="3"/>
+      <c r="K179" s="21">
+        <f t="shared" si="8"/>
+        <v>1666.6666666666667</v>
+      </c>
       <c r="L179" s="3"/>
       <c r="M179" s="3"/>
       <c r="N179" s="3"/>
@@ -9304,11 +9847,11 @@
         <v>24000</v>
       </c>
       <c r="D180" s="4">
-        <f t="shared" si="4"/>
-        <v>4800</v>
+        <f t="shared" si="6"/>
+        <v>4000</v>
       </c>
       <c r="E180" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">VENTOLA PER PENTIUM PRO </v>
       </c>
       <c r="F180" s="3"/>
@@ -9316,7 +9859,10 @@
       <c r="H180" s="3"/>
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
-      <c r="K180" s="3"/>
+      <c r="K180" s="21">
+        <f t="shared" si="8"/>
+        <v>4000</v>
+      </c>
       <c r="L180" s="3"/>
       <c r="M180" s="3"/>
       <c r="N180" s="3"/>
@@ -9344,11 +9890,11 @@
         <v>11000</v>
       </c>
       <c r="D181" s="4">
-        <f t="shared" si="4"/>
-        <v>2200</v>
+        <f t="shared" si="6"/>
+        <v>1833.3333333333321</v>
       </c>
       <c r="E181" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">VENTOLINA PER IBM/CYRIX 686  </v>
       </c>
       <c r="F181" s="3"/>
@@ -9356,7 +9902,10 @@
       <c r="H181" s="3"/>
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
-      <c r="K181" s="3"/>
+      <c r="K181" s="21">
+        <f t="shared" si="8"/>
+        <v>1833.3333333333335</v>
+      </c>
       <c r="L181" s="3"/>
       <c r="M181" s="3"/>
       <c r="N181" s="3"/>
@@ -9384,11 +9933,11 @@
         <v>10000</v>
       </c>
       <c r="D182" s="4">
-        <f t="shared" si="4"/>
-        <v>2000</v>
+        <f t="shared" si="6"/>
+        <v>1666.6666666666661</v>
       </c>
       <c r="E182" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">VENTOLA 3 PIN per TX97  </v>
       </c>
       <c r="F182" s="3"/>
@@ -9396,7 +9945,10 @@
       <c r="H182" s="3"/>
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
-      <c r="K182" s="3"/>
+      <c r="K182" s="21">
+        <f t="shared" si="8"/>
+        <v>1666.6666666666667</v>
+      </c>
       <c r="L182" s="3"/>
       <c r="M182" s="3"/>
       <c r="N182" s="3"/>
@@ -9424,11 +9976,11 @@
         <v>26000</v>
       </c>
       <c r="D183" s="4">
-        <f t="shared" si="4"/>
-        <v>5200</v>
+        <f t="shared" si="6"/>
+        <v>4333.3333333333321</v>
       </c>
       <c r="E183" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">VENTOLA PENTIUM II  </v>
       </c>
       <c r="F183" s="3"/>
@@ -9436,7 +9988,10 @@
       <c r="H183" s="3"/>
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
-      <c r="K183" s="3"/>
+      <c r="K183" s="21">
+        <f t="shared" si="8"/>
+        <v>4333.3333333333339</v>
+      </c>
       <c r="L183" s="3"/>
       <c r="M183" s="3"/>
       <c r="N183" s="3"/>
@@ -9460,11 +10015,11 @@
       <c r="B184" s="3"/>
       <c r="C184" s="4"/>
       <c r="D184" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E184" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">TASTIERE </v>
       </c>
       <c r="F184" s="3"/>
@@ -9472,7 +10027,10 @@
       <c r="H184" s="3"/>
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
-      <c r="K184" s="3"/>
+      <c r="K184" s="21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="L184" s="3"/>
       <c r="M184" s="3"/>
       <c r="N184" s="3"/>
@@ -9500,11 +10058,11 @@
         <v>22000</v>
       </c>
       <c r="D185" s="4">
-        <f t="shared" si="4"/>
-        <v>4400</v>
+        <f t="shared" si="6"/>
+        <v>3666.6666666666642</v>
       </c>
       <c r="E185" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>TAST. ITA 105 TASTI WIN 95 UNIKEY</v>
       </c>
       <c r="F185" s="3"/>
@@ -9512,7 +10070,10 @@
       <c r="H185" s="3"/>
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
-      <c r="K185" s="3"/>
+      <c r="K185" s="21">
+        <f t="shared" si="8"/>
+        <v>3666.666666666667</v>
+      </c>
       <c r="L185" s="3"/>
       <c r="M185" s="3"/>
       <c r="N185" s="3"/>
@@ -9540,11 +10101,11 @@
         <v>63000</v>
       </c>
       <c r="D186" s="4">
-        <f t="shared" si="4"/>
-        <v>12600</v>
+        <f t="shared" si="6"/>
+        <v>10500</v>
       </c>
       <c r="E186" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>TAST. ITA   79t BTC</v>
       </c>
       <c r="F186" s="3"/>
@@ -9552,7 +10113,10 @@
       <c r="H186" s="3"/>
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
-      <c r="K186" s="3"/>
+      <c r="K186" s="21">
+        <f t="shared" si="8"/>
+        <v>10500</v>
+      </c>
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
       <c r="N186" s="3"/>
@@ -9580,11 +10144,11 @@
         <v>63000</v>
       </c>
       <c r="D187" s="4">
-        <f t="shared" si="4"/>
-        <v>12600</v>
+        <f t="shared" si="6"/>
+        <v>10500</v>
       </c>
       <c r="E187" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>TAST. USA 79t BTC</v>
       </c>
       <c r="F187" s="3"/>
@@ -9592,7 +10156,10 @@
       <c r="H187" s="3"/>
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
-      <c r="K187" s="3"/>
+      <c r="K187" s="21">
+        <f t="shared" si="8"/>
+        <v>10500</v>
+      </c>
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
       <c r="N187" s="3"/>
@@ -9620,11 +10187,11 @@
         <v>26000</v>
       </c>
       <c r="D188" s="4">
-        <f t="shared" si="4"/>
-        <v>5200</v>
+        <f t="shared" si="6"/>
+        <v>4333.3333333333321</v>
       </c>
       <c r="E188" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>TAST. USA 105 TASTI WIN95 BTC</v>
       </c>
       <c r="F188" s="3"/>
@@ -9632,7 +10199,10 @@
       <c r="H188" s="3"/>
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
-      <c r="K188" s="3"/>
+      <c r="K188" s="21">
+        <f t="shared" si="8"/>
+        <v>4333.3333333333339</v>
+      </c>
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
       <c r="N188" s="3"/>
@@ -9660,11 +10230,11 @@
         <v>25000</v>
       </c>
       <c r="D189" s="4">
-        <f t="shared" si="4"/>
-        <v>5000</v>
+        <f t="shared" si="6"/>
+        <v>4166.6666666666642</v>
       </c>
       <c r="E189" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>TAST. ITA  105 TASTI NMB, WIN95 NMB</v>
       </c>
       <c r="F189" s="3"/>
@@ -9672,7 +10242,10 @@
       <c r="H189" s="3"/>
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
-      <c r="K189" s="3"/>
+      <c r="K189" s="21">
+        <f t="shared" si="8"/>
+        <v>4166.666666666667</v>
+      </c>
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
       <c r="N189" s="3"/>
@@ -9700,11 +10273,11 @@
         <v>25000</v>
       </c>
       <c r="D190" s="4">
-        <f t="shared" si="4"/>
-        <v>5000</v>
+        <f t="shared" si="6"/>
+        <v>4166.6666666666642</v>
       </c>
       <c r="E190" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>TAST. ITA  105 TASTI NMB, PS/2 WIN95 NMB</v>
       </c>
       <c r="F190" s="3"/>
@@ -9712,7 +10285,10 @@
       <c r="H190" s="3"/>
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
-      <c r="K190" s="3"/>
+      <c r="K190" s="21">
+        <f t="shared" si="8"/>
+        <v>4166.666666666667</v>
+      </c>
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
       <c r="N190" s="3"/>
@@ -9740,11 +10316,11 @@
         <v>46000</v>
       </c>
       <c r="D191" s="4">
-        <f t="shared" si="4"/>
-        <v>9200</v>
+        <f t="shared" si="6"/>
+        <v>7666.6666666666642</v>
       </c>
       <c r="E191" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>TAST. ITA 105 TASTI "CYPRESS"  WIN95 NMB</v>
       </c>
       <c r="F191" s="3"/>
@@ -9752,7 +10328,10 @@
       <c r="H191" s="3"/>
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
-      <c r="K191" s="3"/>
+      <c r="K191" s="21">
+        <f t="shared" si="8"/>
+        <v>7666.666666666667</v>
+      </c>
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
       <c r="N191" s="3"/>
@@ -9776,11 +10355,11 @@
       <c r="B192" s="3"/>
       <c r="C192" s="4"/>
       <c r="D192" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E192" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">SCANNER E ACCESSORI </v>
       </c>
       <c r="F192" s="3"/>
@@ -9788,7 +10367,10 @@
       <c r="H192" s="3"/>
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
-      <c r="K192" s="3"/>
+      <c r="K192" s="21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
       <c r="N192" s="3"/>
@@ -9816,11 +10398,11 @@
         <v>37000</v>
       </c>
       <c r="D193" s="4">
-        <f t="shared" si="4"/>
-        <v>7400</v>
+        <f t="shared" si="6"/>
+        <v>6166.6666666666642</v>
       </c>
       <c r="E193" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>MOUSE  PILOT SERIALE LOGITECH</v>
       </c>
       <c r="F193" s="3"/>
@@ -9828,7 +10410,10 @@
       <c r="H193" s="3"/>
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
-      <c r="K193" s="3"/>
+      <c r="K193" s="21">
+        <f t="shared" si="8"/>
+        <v>6166.666666666667</v>
+      </c>
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
       <c r="N193" s="3"/>
@@ -9856,11 +10441,11 @@
         <v>37000</v>
       </c>
       <c r="D194" s="4">
-        <f t="shared" si="4"/>
-        <v>7400</v>
+        <f t="shared" si="6"/>
+        <v>6166.6666666666642</v>
       </c>
       <c r="E194" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>MOUSE  PILOT P/S2 LOGITECH</v>
       </c>
       <c r="F194" s="3"/>
@@ -9868,7 +10453,10 @@
       <c r="H194" s="3"/>
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
-      <c r="K194" s="3"/>
+      <c r="K194" s="21">
+        <f t="shared" si="8"/>
+        <v>6166.666666666667</v>
+      </c>
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
       <c r="N194" s="3"/>
@@ -9896,11 +10484,11 @@
         <v>11000</v>
       </c>
       <c r="D195" s="4">
-        <f t="shared" ref="D195:D258" si="6">C195*$G$2</f>
-        <v>2200</v>
+        <f t="shared" ref="D195:D258" si="9">C195-(C195/(1+($G$2)))</f>
+        <v>1833.3333333333321</v>
       </c>
       <c r="E195" s="3" t="str">
-        <f t="shared" ref="E195:E258" si="7">_xlfn.CONCAT(A195," ",B195)</f>
+        <f t="shared" ref="E195:E258" si="10">_xlfn.CONCAT(A195," ",B195)</f>
         <v>MOUSE SERIALE 3 TASTI PRIMAX</v>
       </c>
       <c r="F195" s="3"/>
@@ -9908,7 +10496,10 @@
       <c r="H195" s="3"/>
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
-      <c r="K195" s="3"/>
+      <c r="K195" s="21">
+        <f t="shared" ref="K195:K258" si="11">(C195*$G$2)/$H$2</f>
+        <v>1833.3333333333335</v>
+      </c>
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
       <c r="N195" s="3"/>
@@ -9936,11 +10527,11 @@
         <v>46000</v>
       </c>
       <c r="D196" s="4">
-        <f t="shared" si="6"/>
-        <v>9200</v>
+        <f t="shared" si="9"/>
+        <v>7666.6666666666642</v>
       </c>
       <c r="E196" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>MOUSE TRACKBALL  PRIMAX</v>
       </c>
       <c r="F196" s="3"/>
@@ -9948,7 +10539,10 @@
       <c r="H196" s="3"/>
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
-      <c r="K196" s="3"/>
+      <c r="K196" s="21">
+        <f t="shared" si="11"/>
+        <v>7666.666666666667</v>
+      </c>
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
       <c r="N196" s="3"/>
@@ -9976,11 +10570,11 @@
         <v>19000</v>
       </c>
       <c r="D197" s="4">
-        <f t="shared" si="6"/>
-        <v>3800</v>
+        <f t="shared" si="9"/>
+        <v>3166.6666666666661</v>
       </c>
       <c r="E197" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>MOUSE "RAINBOW" SERIALE PRIMAX</v>
       </c>
       <c r="F197" s="3"/>
@@ -9988,7 +10582,10 @@
       <c r="H197" s="3"/>
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
-      <c r="K197" s="3"/>
+      <c r="K197" s="21">
+        <f t="shared" si="11"/>
+        <v>3166.666666666667</v>
+      </c>
       <c r="L197" s="3"/>
       <c r="M197" s="3"/>
       <c r="N197" s="3"/>
@@ -10016,11 +10613,11 @@
         <v>13000</v>
       </c>
       <c r="D198" s="4">
-        <f t="shared" si="6"/>
-        <v>2600</v>
+        <f t="shared" si="9"/>
+        <v>2166.6666666666661</v>
       </c>
       <c r="E198" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>MOUSE  ECHO PS/2 PRIMAX</v>
       </c>
       <c r="F198" s="3"/>
@@ -10028,7 +10625,10 @@
       <c r="H198" s="3"/>
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
-      <c r="K198" s="3"/>
+      <c r="K198" s="21">
+        <f t="shared" si="11"/>
+        <v>2166.666666666667</v>
+      </c>
       <c r="L198" s="3"/>
       <c r="M198" s="3"/>
       <c r="N198" s="3"/>
@@ -10056,11 +10656,11 @@
         <v>26000</v>
       </c>
       <c r="D199" s="4">
-        <f t="shared" si="6"/>
-        <v>5200</v>
+        <f t="shared" si="9"/>
+        <v>4333.3333333333321</v>
       </c>
       <c r="E199" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>VENUS MOUSE SERIALE PRIMAX</v>
       </c>
       <c r="F199" s="3"/>
@@ -10068,7 +10668,10 @@
       <c r="H199" s="3"/>
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
-      <c r="K199" s="3"/>
+      <c r="K199" s="21">
+        <f t="shared" si="11"/>
+        <v>4333.3333333333339</v>
+      </c>
       <c r="L199" s="3"/>
       <c r="M199" s="3"/>
       <c r="N199" s="3"/>
@@ -10096,11 +10699,11 @@
         <v>26000</v>
       </c>
       <c r="D200" s="4">
-        <f t="shared" si="6"/>
-        <v>5200</v>
+        <f t="shared" si="9"/>
+        <v>4333.3333333333321</v>
       </c>
       <c r="E200" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>VENUS MOUSE PS/2 PRIMAX</v>
       </c>
       <c r="F200" s="3"/>
@@ -10108,7 +10711,10 @@
       <c r="H200" s="3"/>
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
-      <c r="K200" s="3"/>
+      <c r="K200" s="21">
+        <f t="shared" si="11"/>
+        <v>4333.3333333333339</v>
+      </c>
       <c r="L200" s="3"/>
       <c r="M200" s="3"/>
       <c r="N200" s="3"/>
@@ -10136,11 +10742,11 @@
         <v>20000</v>
       </c>
       <c r="D201" s="4">
-        <f t="shared" si="6"/>
-        <v>4000</v>
+        <f t="shared" si="9"/>
+        <v>3333.3333333333321</v>
       </c>
       <c r="E201" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>JOYSTICK DIGITALE PRIMAX</v>
       </c>
       <c r="F201" s="3"/>
@@ -10148,7 +10754,10 @@
       <c r="H201" s="3"/>
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
-      <c r="K201" s="3"/>
+      <c r="K201" s="21">
+        <f t="shared" si="11"/>
+        <v>3333.3333333333335</v>
+      </c>
       <c r="L201" s="3"/>
       <c r="M201" s="3"/>
       <c r="N201" s="3"/>
@@ -10176,11 +10785,11 @@
         <v>49000</v>
       </c>
       <c r="D202" s="4">
-        <f t="shared" si="6"/>
-        <v>9800</v>
+        <f t="shared" si="9"/>
+        <v>8166.6666666666642</v>
       </c>
       <c r="E202" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>JOYSTICK ULTRASTRIKER PRIMAX</v>
       </c>
       <c r="F202" s="3"/>
@@ -10188,7 +10797,10 @@
       <c r="H202" s="3"/>
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
-      <c r="K202" s="3"/>
+      <c r="K202" s="21">
+        <f t="shared" si="11"/>
+        <v>8166.666666666667</v>
+      </c>
       <c r="L202" s="3"/>
       <c r="M202" s="3"/>
       <c r="N202" s="3"/>
@@ -10216,11 +10828,11 @@
         <v>33000</v>
       </c>
       <c r="D203" s="4">
-        <f t="shared" si="6"/>
-        <v>6600</v>
+        <f t="shared" si="9"/>
+        <v>5500</v>
       </c>
       <c r="E203" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NAVIGATOR MOUSE PRIMAX</v>
       </c>
       <c r="F203" s="3"/>
@@ -10228,7 +10840,10 @@
       <c r="H203" s="3"/>
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
-      <c r="K203" s="3"/>
+      <c r="K203" s="21">
+        <f t="shared" si="11"/>
+        <v>5500</v>
+      </c>
       <c r="L203" s="3"/>
       <c r="M203" s="3"/>
       <c r="N203" s="3"/>
@@ -10256,11 +10871,11 @@
         <v>68000</v>
       </c>
       <c r="D204" s="4">
-        <f t="shared" si="6"/>
-        <v>13600</v>
+        <f t="shared" si="9"/>
+        <v>11333.333333333328</v>
       </c>
       <c r="E204" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>JOYSTICK EXCALIBUR PRIMAX</v>
       </c>
       <c r="F204" s="3"/>
@@ -10268,7 +10883,10 @@
       <c r="H204" s="3"/>
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
-      <c r="K204" s="3"/>
+      <c r="K204" s="21">
+        <f t="shared" si="11"/>
+        <v>11333.333333333334</v>
+      </c>
       <c r="L204" s="3"/>
       <c r="M204" s="3"/>
       <c r="N204" s="3"/>
@@ -10296,11 +10914,11 @@
         <v>33000</v>
       </c>
       <c r="D205" s="4">
-        <f t="shared" si="6"/>
-        <v>6600</v>
+        <f t="shared" si="9"/>
+        <v>5500</v>
       </c>
       <c r="E205" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>GAMEPAD CONQUEROR PRIMAX</v>
       </c>
       <c r="F205" s="3"/>
@@ -10308,7 +10926,10 @@
       <c r="H205" s="3"/>
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
-      <c r="K205" s="3"/>
+      <c r="K205" s="21">
+        <f t="shared" si="11"/>
+        <v>5500</v>
+      </c>
       <c r="L205" s="3"/>
       <c r="M205" s="3"/>
       <c r="N205" s="3"/>
@@ -10336,11 +10957,11 @@
         <v>147000</v>
       </c>
       <c r="D206" s="4">
-        <f t="shared" si="6"/>
-        <v>29400</v>
+        <f t="shared" si="9"/>
+        <v>24500</v>
       </c>
       <c r="E206" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>COLOR HAND SCANNER PRIMAX</v>
       </c>
       <c r="F206" s="3"/>
@@ -10348,7 +10969,10 @@
       <c r="H206" s="3"/>
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
-      <c r="K206" s="3"/>
+      <c r="K206" s="21">
+        <f t="shared" si="11"/>
+        <v>24500</v>
+      </c>
       <c r="L206" s="3"/>
       <c r="M206" s="3"/>
       <c r="N206" s="3"/>
@@ -10376,11 +11000,11 @@
         <v>151000</v>
       </c>
       <c r="D207" s="4">
-        <f t="shared" si="6"/>
-        <v>30200</v>
+        <f t="shared" si="9"/>
+        <v>25166.666666666657</v>
       </c>
       <c r="E207" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>SCANNER COLORADO 4800 SW + OCR  PRIMAX</v>
       </c>
       <c r="F207" s="3"/>
@@ -10388,7 +11012,10 @@
       <c r="H207" s="3"/>
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
-      <c r="K207" s="3"/>
+      <c r="K207" s="21">
+        <f t="shared" si="11"/>
+        <v>25166.666666666668</v>
+      </c>
       <c r="L207" s="3"/>
       <c r="M207" s="3"/>
       <c r="N207" s="3"/>
@@ -10416,11 +11043,11 @@
         <v>197000</v>
       </c>
       <c r="D208" s="4">
-        <f t="shared" si="6"/>
-        <v>39400</v>
+        <f t="shared" si="9"/>
+        <v>32833.333333333314</v>
       </c>
       <c r="E208" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>SCANNER COLORADO D600 SW + OCR  PRIMAX</v>
       </c>
       <c r="F208" s="3"/>
@@ -10428,7 +11055,10 @@
       <c r="H208" s="3"/>
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
-      <c r="K208" s="3"/>
+      <c r="K208" s="21">
+        <f t="shared" si="11"/>
+        <v>32833.333333333336</v>
+      </c>
       <c r="L208" s="3"/>
       <c r="M208" s="3"/>
       <c r="N208" s="3"/>
@@ -10456,11 +11086,11 @@
         <v>310000</v>
       </c>
       <c r="D209" s="4">
-        <f t="shared" si="6"/>
-        <v>62000</v>
+        <f t="shared" si="9"/>
+        <v>51666.666666666657</v>
       </c>
       <c r="E209" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>SCANNER  DIRECT 9600 SW + OCR PRIMAX</v>
       </c>
       <c r="F209" s="3"/>
@@ -10468,7 +11098,10 @@
       <c r="H209" s="3"/>
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
-      <c r="K209" s="3"/>
+      <c r="K209" s="21">
+        <f t="shared" si="11"/>
+        <v>51666.666666666672</v>
+      </c>
       <c r="L209" s="3"/>
       <c r="M209" s="3"/>
       <c r="N209" s="3"/>
@@ -10496,11 +11129,11 @@
         <v>271000</v>
       </c>
       <c r="D210" s="4">
-        <f t="shared" si="6"/>
-        <v>54200</v>
+        <f t="shared" si="9"/>
+        <v>45166.666666666657</v>
       </c>
       <c r="E210" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>SCANNER  JEWEL 4800 SCSI PRIMAX</v>
       </c>
       <c r="F210" s="3"/>
@@ -10508,7 +11141,10 @@
       <c r="H210" s="3"/>
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
-      <c r="K210" s="3"/>
+      <c r="K210" s="21">
+        <f t="shared" si="11"/>
+        <v>45166.666666666672</v>
+      </c>
       <c r="L210" s="3"/>
       <c r="M210" s="3"/>
       <c r="N210" s="3"/>
@@ -10536,11 +11172,11 @@
         <v>458000</v>
       </c>
       <c r="D211" s="4">
-        <f t="shared" si="6"/>
-        <v>91600</v>
+        <f t="shared" si="9"/>
+        <v>76333.333333333314</v>
       </c>
       <c r="E211" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>SCANNER PROFI  9600 SCSI PRIMAX</v>
       </c>
       <c r="F211" s="3"/>
@@ -10548,7 +11184,10 @@
       <c r="H211" s="3"/>
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
-      <c r="K211" s="3"/>
+      <c r="K211" s="21">
+        <f t="shared" si="11"/>
+        <v>76333.333333333343</v>
+      </c>
       <c r="L211" s="3"/>
       <c r="M211" s="3"/>
       <c r="N211" s="3"/>
@@ -10576,11 +11215,11 @@
         <v>412000</v>
       </c>
       <c r="D212" s="4">
-        <f t="shared" si="6"/>
-        <v>82400</v>
+        <f t="shared" si="9"/>
+        <v>68666.666666666628</v>
       </c>
       <c r="E212" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>SCANNER PHODOX U. S. 300 PRIMAX</v>
       </c>
       <c r="F212" s="3"/>
@@ -10588,7 +11227,10 @@
       <c r="H212" s="3"/>
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
-      <c r="K212" s="3"/>
+      <c r="K212" s="21">
+        <f t="shared" si="11"/>
+        <v>68666.666666666672</v>
+      </c>
       <c r="L212" s="3"/>
       <c r="M212" s="3"/>
       <c r="N212" s="3"/>
@@ -10616,11 +11258,11 @@
         <v>807000</v>
       </c>
       <c r="D213" s="4">
-        <f t="shared" si="6"/>
-        <v>161400</v>
+        <f t="shared" si="9"/>
+        <v>134500</v>
       </c>
       <c r="E213" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>FILMSCAN-200PC EPSON</v>
       </c>
       <c r="F213" s="3"/>
@@ -10628,7 +11270,10 @@
       <c r="H213" s="3"/>
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
-      <c r="K213" s="3"/>
+      <c r="K213" s="21">
+        <f t="shared" si="11"/>
+        <v>134500</v>
+      </c>
       <c r="L213" s="3"/>
       <c r="M213" s="3"/>
       <c r="N213" s="3"/>
@@ -10654,11 +11299,11 @@
         <v>4000</v>
       </c>
       <c r="D214" s="4">
-        <f t="shared" si="6"/>
-        <v>800</v>
+        <f t="shared" si="9"/>
+        <v>666.66666666666652</v>
       </c>
       <c r="E214" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">TAPPETINO PER MOUSE </v>
       </c>
       <c r="F214" s="3"/>
@@ -10666,7 +11311,10 @@
       <c r="H214" s="3"/>
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
-      <c r="K214" s="3"/>
+      <c r="K214" s="21">
+        <f t="shared" si="11"/>
+        <v>666.66666666666674</v>
+      </c>
       <c r="L214" s="3"/>
       <c r="M214" s="3"/>
       <c r="N214" s="3"/>
@@ -10692,11 +11340,11 @@
         <v>81000</v>
       </c>
       <c r="D215" s="4">
-        <f t="shared" si="6"/>
-        <v>16200</v>
+        <f t="shared" si="9"/>
+        <v>13500</v>
       </c>
       <c r="E215" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">ALIMENTATORE 200 W CE </v>
       </c>
       <c r="F215" s="3"/>
@@ -10704,7 +11352,10 @@
       <c r="H215" s="3"/>
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
-      <c r="K215" s="3"/>
+      <c r="K215" s="21">
+        <f t="shared" si="11"/>
+        <v>13500</v>
+      </c>
       <c r="L215" s="3"/>
       <c r="M215" s="3"/>
       <c r="N215" s="3"/>
@@ -10730,11 +11381,11 @@
         <v>125000</v>
       </c>
       <c r="D216" s="4">
-        <f t="shared" si="6"/>
-        <v>25000</v>
+        <f t="shared" si="9"/>
+        <v>20833.333333333328</v>
       </c>
       <c r="E216" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">ALIMENTATORE 250 W CE ATX </v>
       </c>
       <c r="F216" s="3"/>
@@ -10742,7 +11393,10 @@
       <c r="H216" s="3"/>
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
-      <c r="K216" s="3"/>
+      <c r="K216" s="21">
+        <f t="shared" si="11"/>
+        <v>20833.333333333336</v>
+      </c>
       <c r="L216" s="3"/>
       <c r="M216" s="3"/>
       <c r="N216" s="3"/>
@@ -10768,11 +11422,11 @@
         <v>98000</v>
       </c>
       <c r="D217" s="4">
-        <f t="shared" si="6"/>
-        <v>19600</v>
+        <f t="shared" si="9"/>
+        <v>16333.333333333328</v>
       </c>
       <c r="E217" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">ALIMENTATORE 230 W CE ATX </v>
       </c>
       <c r="F217" s="3"/>
@@ -10780,7 +11434,10 @@
       <c r="H217" s="3"/>
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
-      <c r="K217" s="3"/>
+      <c r="K217" s="21">
+        <f t="shared" si="11"/>
+        <v>16333.333333333334</v>
+      </c>
       <c r="L217" s="3"/>
       <c r="M217" s="3"/>
       <c r="N217" s="3"/>
@@ -10806,11 +11463,11 @@
         <v>140000</v>
       </c>
       <c r="D218" s="4">
-        <f t="shared" si="6"/>
-        <v>28000</v>
+        <f t="shared" si="9"/>
+        <v>23333.333333333328</v>
       </c>
       <c r="E218" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">ALIMENTATORE 300 W CE ATX </v>
       </c>
       <c r="F218" s="3"/>
@@ -10818,7 +11475,10 @@
       <c r="H218" s="3"/>
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
-      <c r="K218" s="3"/>
+      <c r="K218" s="21">
+        <f t="shared" si="11"/>
+        <v>23333.333333333336</v>
+      </c>
       <c r="L218" s="3"/>
       <c r="M218" s="3"/>
       <c r="N218" s="3"/>
@@ -10846,11 +11506,11 @@
         <v>5000</v>
       </c>
       <c r="D219" s="4">
-        <f t="shared" si="6"/>
-        <v>1000</v>
+        <f t="shared" si="9"/>
+        <v>833.33333333333303</v>
       </c>
       <c r="E219" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>CAVO PARALLELO STAMP. MT 1,8 Unidirez.</v>
       </c>
       <c r="F219" s="3"/>
@@ -10858,7 +11518,10 @@
       <c r="H219" s="3"/>
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
-      <c r="K219" s="3"/>
+      <c r="K219" s="21">
+        <f t="shared" si="11"/>
+        <v>833.33333333333337</v>
+      </c>
       <c r="L219" s="3"/>
       <c r="M219" s="3"/>
       <c r="N219" s="3"/>
@@ -10886,11 +11549,11 @@
         <v>6000</v>
       </c>
       <c r="D220" s="4">
-        <f t="shared" si="6"/>
-        <v>1200</v>
+        <f t="shared" si="9"/>
+        <v>1000</v>
       </c>
       <c r="E220" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>CAVO PARALLELO STAMP. MT 1,8 Bidirez.</v>
       </c>
       <c r="F220" s="3"/>
@@ -10898,7 +11561,10 @@
       <c r="H220" s="3"/>
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
-      <c r="K220" s="3"/>
+      <c r="K220" s="21">
+        <f t="shared" si="11"/>
+        <v>1000</v>
+      </c>
       <c r="L220" s="3"/>
       <c r="M220" s="3"/>
       <c r="N220" s="3"/>
@@ -10924,11 +11590,11 @@
         <v>9000</v>
       </c>
       <c r="D221" s="4">
-        <f t="shared" si="6"/>
-        <v>1800</v>
+        <f t="shared" si="9"/>
+        <v>1500</v>
       </c>
       <c r="E221" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">CAVO PARALLELO STAMP. MT 3 </v>
       </c>
       <c r="F221" s="3"/>
@@ -10936,7 +11602,10 @@
       <c r="H221" s="3"/>
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
-      <c r="K221" s="3"/>
+      <c r="K221" s="21">
+        <f t="shared" si="11"/>
+        <v>1500</v>
+      </c>
       <c r="L221" s="3"/>
       <c r="M221" s="3"/>
       <c r="N221" s="3"/>
@@ -10964,11 +11633,11 @@
         <v>8000</v>
       </c>
       <c r="D222" s="4">
-        <f t="shared" si="6"/>
-        <v>1600</v>
+        <f t="shared" si="9"/>
+        <v>1333.333333333333</v>
       </c>
       <c r="E222" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>CONNETTORE MOUSE PS/2 per M/B ASUS P55T2P4</v>
       </c>
       <c r="F222" s="3"/>
@@ -10976,7 +11645,10 @@
       <c r="H222" s="3"/>
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
-      <c r="K222" s="3"/>
+      <c r="K222" s="21">
+        <f t="shared" si="11"/>
+        <v>1333.3333333333335</v>
+      </c>
       <c r="L222" s="3"/>
       <c r="M222" s="3"/>
       <c r="N222" s="3"/>
@@ -11002,11 +11674,11 @@
         <v>11000</v>
       </c>
       <c r="D223" s="4">
-        <f t="shared" si="6"/>
-        <v>2200</v>
+        <f t="shared" si="9"/>
+        <v>1833.3333333333321</v>
       </c>
       <c r="E223" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">CONNETTORE TASTIERA PS/2 </v>
       </c>
       <c r="F223" s="3"/>
@@ -11014,7 +11686,10 @@
       <c r="H223" s="3"/>
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
-      <c r="K223" s="3"/>
+      <c r="K223" s="21">
+        <f t="shared" si="11"/>
+        <v>1833.3333333333335</v>
+      </c>
       <c r="L223" s="3"/>
       <c r="M223" s="3"/>
       <c r="N223" s="3"/>
@@ -11042,11 +11717,11 @@
         <v>21000</v>
       </c>
       <c r="D224" s="4">
-        <f t="shared" si="6"/>
-        <v>4200</v>
+        <f t="shared" si="9"/>
+        <v>3500</v>
       </c>
       <c r="E224" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>CONNETTORE USB/MIR per M/B ASUS TX97</v>
       </c>
       <c r="F224" s="3"/>
@@ -11054,7 +11729,10 @@
       <c r="H224" s="3"/>
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
-      <c r="K224" s="3"/>
+      <c r="K224" s="21">
+        <f t="shared" si="11"/>
+        <v>3500</v>
+      </c>
       <c r="L224" s="3"/>
       <c r="M224" s="3"/>
       <c r="N224" s="3"/>
@@ -11082,11 +11760,11 @@
         <v>14000</v>
       </c>
       <c r="D225" s="4">
-        <f t="shared" si="6"/>
-        <v>2800</v>
+        <f t="shared" si="9"/>
+        <v>2333.3333333333321</v>
       </c>
       <c r="E225" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>DATA-SWITCH 2/1 MANUALE PRIMAX</v>
       </c>
       <c r="F225" s="3"/>
@@ -11094,7 +11772,10 @@
       <c r="H225" s="3"/>
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
-      <c r="K225" s="3"/>
+      <c r="K225" s="21">
+        <f t="shared" si="11"/>
+        <v>2333.3333333333335</v>
+      </c>
       <c r="L225" s="3"/>
       <c r="M225" s="3"/>
       <c r="N225" s="3"/>
@@ -11122,11 +11803,11 @@
         <v>23000</v>
       </c>
       <c r="D226" s="4">
-        <f t="shared" si="6"/>
-        <v>4600</v>
+        <f t="shared" si="9"/>
+        <v>3833.3333333333321</v>
       </c>
       <c r="E226" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>DATA-SWITCH 2/2 MANUALE PRIMAX</v>
       </c>
       <c r="F226" s="3"/>
@@ -11134,7 +11815,10 @@
       <c r="H226" s="3"/>
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
-      <c r="K226" s="3"/>
+      <c r="K226" s="21">
+        <f t="shared" si="11"/>
+        <v>3833.3333333333335</v>
+      </c>
       <c r="L226" s="3"/>
       <c r="M226" s="3"/>
       <c r="N226" s="3"/>
@@ -11162,11 +11846,11 @@
         <v>51000</v>
       </c>
       <c r="D227" s="4">
-        <f t="shared" si="6"/>
-        <v>10200</v>
+        <f t="shared" si="9"/>
+        <v>8500</v>
       </c>
       <c r="E227" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>DATA-SWITCH 2/1 BIDIREZ. PRIMAX</v>
       </c>
       <c r="F227" s="3"/>
@@ -11174,7 +11858,10 @@
       <c r="H227" s="3"/>
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
-      <c r="K227" s="3"/>
+      <c r="K227" s="21">
+        <f t="shared" si="11"/>
+        <v>8500</v>
+      </c>
       <c r="L227" s="3"/>
       <c r="M227" s="3"/>
       <c r="N227" s="3"/>
@@ -11198,11 +11885,11 @@
       <c r="B228" s="3"/>
       <c r="C228" s="4"/>
       <c r="D228" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E228" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">SOFTWARE </v>
       </c>
       <c r="F228" s="3"/>
@@ -11210,7 +11897,10 @@
       <c r="H228" s="3"/>
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
-      <c r="K228" s="3"/>
+      <c r="K228" s="21">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="L228" s="3"/>
       <c r="M228" s="3"/>
       <c r="N228" s="3"/>
@@ -11238,11 +11928,11 @@
         <v>198000</v>
       </c>
       <c r="D229" s="4">
-        <f t="shared" si="6"/>
-        <v>39600</v>
+        <f t="shared" si="9"/>
+        <v>33000</v>
       </c>
       <c r="E229" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>COMBO DOS6.22+WIN3.11+DSK.MAN. MICROSOFT  OEM</v>
       </c>
       <c r="F229" s="3"/>
@@ -11250,7 +11940,10 @@
       <c r="H229" s="3"/>
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
-      <c r="K229" s="3"/>
+      <c r="K229" s="21">
+        <f t="shared" si="11"/>
+        <v>33000</v>
+      </c>
       <c r="L229" s="3"/>
       <c r="M229" s="3"/>
       <c r="N229" s="3"/>
@@ -11278,11 +11971,11 @@
         <v>167000</v>
       </c>
       <c r="D230" s="4">
-        <f t="shared" si="6"/>
-        <v>33400</v>
+        <f t="shared" si="9"/>
+        <v>27833.333333333314</v>
       </c>
       <c r="E230" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>WINDOWS 95, MANUALI + CD MICROSOFT  OEM</v>
       </c>
       <c r="F230" s="3"/>
@@ -11290,7 +11983,10 @@
       <c r="H230" s="3"/>
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
-      <c r="K230" s="3"/>
+      <c r="K230" s="21">
+        <f t="shared" si="11"/>
+        <v>27833.333333333336</v>
+      </c>
       <c r="L230" s="3"/>
       <c r="M230" s="3"/>
       <c r="N230" s="3"/>
@@ -11318,11 +12014,11 @@
         <v>95000</v>
       </c>
       <c r="D231" s="4">
-        <f t="shared" si="6"/>
-        <v>19000</v>
+        <f t="shared" si="9"/>
+        <v>15833.333333333328</v>
       </c>
       <c r="E231" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>LICENZA STUDENTE SISTEMI  MICROSOFT  STUDENTE</v>
       </c>
       <c r="F231" s="3"/>
@@ -11330,7 +12026,10 @@
       <c r="H231" s="3"/>
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
-      <c r="K231" s="3"/>
+      <c r="K231" s="21">
+        <f t="shared" si="11"/>
+        <v>15833.333333333334</v>
+      </c>
       <c r="L231" s="3"/>
       <c r="M231" s="3"/>
       <c r="N231" s="3"/>
@@ -11358,11 +12057,11 @@
         <v>141000</v>
       </c>
       <c r="D232" s="4">
-        <f t="shared" si="6"/>
-        <v>28200</v>
+        <f t="shared" si="9"/>
+        <v>23500</v>
       </c>
       <c r="E232" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>LICENZA STUDENTE APPLICAZIONI MICROSOFT  STUDENTE</v>
       </c>
       <c r="F232" s="3"/>
@@ -11370,7 +12069,10 @@
       <c r="H232" s="3"/>
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
-      <c r="K232" s="3"/>
+      <c r="K232" s="21">
+        <f t="shared" si="11"/>
+        <v>23500</v>
+      </c>
       <c r="L232" s="3"/>
       <c r="M232" s="3"/>
       <c r="N232" s="3"/>
@@ -11398,11 +12100,11 @@
         <v>351000</v>
       </c>
       <c r="D233" s="4">
-        <f t="shared" si="6"/>
-        <v>70200</v>
+        <f t="shared" si="9"/>
+        <v>58500</v>
       </c>
       <c r="E233" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>WIN NT WORKSTATION 4.0 MICROSOFT  OEM</v>
       </c>
       <c r="F233" s="3"/>
@@ -11410,7 +12112,10 @@
       <c r="H233" s="3"/>
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
-      <c r="K233" s="3"/>
+      <c r="K233" s="21">
+        <f t="shared" si="11"/>
+        <v>58500</v>
+      </c>
       <c r="L233" s="3"/>
       <c r="M233" s="3"/>
       <c r="N233" s="3"/>
@@ -11438,11 +12143,11 @@
         <v>414000</v>
       </c>
       <c r="D234" s="4">
-        <f t="shared" si="6"/>
-        <v>82800</v>
+        <f t="shared" si="9"/>
+        <v>69000</v>
       </c>
       <c r="E234" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>OFFICE SMALL BUSINESS WORD97,EXCEL97,OUTLOOK97,PUBLISHER97</v>
       </c>
       <c r="F234" s="3"/>
@@ -11450,7 +12155,10 @@
       <c r="H234" s="3"/>
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
-      <c r="K234" s="3"/>
+      <c r="K234" s="21">
+        <f t="shared" si="11"/>
+        <v>69000</v>
+      </c>
       <c r="L234" s="3"/>
       <c r="M234" s="3"/>
       <c r="N234" s="3"/>
@@ -11478,11 +12186,11 @@
         <v>61000</v>
       </c>
       <c r="D235" s="4">
-        <f t="shared" si="6"/>
-        <v>12200</v>
+        <f t="shared" si="9"/>
+        <v>10166.666666666664</v>
       </c>
       <c r="E235" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>WORKS 4.5 ITA, MANUALI + CD MICROSOFT  OEM</v>
       </c>
       <c r="F235" s="3"/>
@@ -11490,7 +12198,10 @@
       <c r="H235" s="3"/>
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
-      <c r="K235" s="3"/>
+      <c r="K235" s="21">
+        <f t="shared" si="11"/>
+        <v>10166.666666666668</v>
+      </c>
       <c r="L235" s="3"/>
       <c r="M235" s="3"/>
       <c r="N235" s="3"/>
@@ -11518,11 +12229,11 @@
         <v>893000</v>
       </c>
       <c r="D236" s="4">
-        <f t="shared" si="6"/>
-        <v>178600</v>
+        <f t="shared" si="9"/>
+        <v>148833.33333333326</v>
       </c>
       <c r="E236" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>FIVE PACK WIN 95 MICROSOFT  OEM</v>
       </c>
       <c r="F236" s="3"/>
@@ -11530,7 +12241,10 @@
       <c r="H236" s="3"/>
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
-      <c r="K236" s="3"/>
+      <c r="K236" s="21">
+        <f t="shared" si="11"/>
+        <v>148833.33333333334</v>
+      </c>
       <c r="L236" s="3"/>
       <c r="M236" s="3"/>
       <c r="N236" s="3"/>
@@ -11558,11 +12272,11 @@
         <v>985000</v>
       </c>
       <c r="D237" s="4">
-        <f t="shared" si="6"/>
-        <v>197000</v>
+        <f t="shared" si="9"/>
+        <v>164166.66666666663</v>
       </c>
       <c r="E237" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>FIVE PACK COMBO WIN3.11-DOS MICROSOFT  OEM</v>
       </c>
       <c r="F237" s="3"/>
@@ -11570,7 +12284,10 @@
       <c r="H237" s="3"/>
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
-      <c r="K237" s="3"/>
+      <c r="K237" s="21">
+        <f t="shared" si="11"/>
+        <v>164166.66666666669</v>
+      </c>
       <c r="L237" s="3"/>
       <c r="M237" s="3"/>
       <c r="N237" s="3"/>
@@ -11598,11 +12315,11 @@
         <v>296000</v>
       </c>
       <c r="D238" s="4">
-        <f t="shared" si="6"/>
-        <v>59200</v>
+        <f t="shared" si="9"/>
+        <v>49333.333333333314</v>
       </c>
       <c r="E238" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>FIVE PACK WORKS 4.5 MICROSOFT  OEM</v>
       </c>
       <c r="F238" s="3"/>
@@ -11610,7 +12327,10 @@
       <c r="H238" s="3"/>
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
-      <c r="K238" s="3"/>
+      <c r="K238" s="21">
+        <f t="shared" si="11"/>
+        <v>49333.333333333336</v>
+      </c>
       <c r="L238" s="3"/>
       <c r="M238" s="3"/>
       <c r="N238" s="3"/>
@@ -11638,11 +12358,11 @@
         <v>685000</v>
       </c>
       <c r="D239" s="4">
-        <f t="shared" si="6"/>
-        <v>137000</v>
+        <f t="shared" si="9"/>
+        <v>114166.66666666663</v>
       </c>
       <c r="E239" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>3-PACK  HOME ESSENTIALS 98 MICROSOFT  OEM</v>
       </c>
       <c r="F239" s="3"/>
@@ -11650,7 +12370,10 @@
       <c r="H239" s="3"/>
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
-      <c r="K239" s="3"/>
+      <c r="K239" s="21">
+        <f t="shared" si="11"/>
+        <v>114166.66666666667</v>
+      </c>
       <c r="L239" s="3"/>
       <c r="M239" s="3"/>
       <c r="N239" s="3"/>
@@ -11678,11 +12401,11 @@
         <v>1138000</v>
       </c>
       <c r="D240" s="4">
-        <f t="shared" si="6"/>
-        <v>227600</v>
+        <f t="shared" si="9"/>
+        <v>189666.66666666663</v>
       </c>
       <c r="E240" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>3-PACK WIN NT WORKSTATION 4.0 MICROSOFT  OEM</v>
       </c>
       <c r="F240" s="3"/>
@@ -11690,7 +12413,10 @@
       <c r="H240" s="3"/>
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
-      <c r="K240" s="3"/>
+      <c r="K240" s="21">
+        <f t="shared" si="11"/>
+        <v>189666.66666666669</v>
+      </c>
       <c r="L240" s="3"/>
       <c r="M240" s="3"/>
       <c r="N240" s="3"/>
@@ -11718,11 +12444,11 @@
         <v>1334000</v>
       </c>
       <c r="D241" s="4">
-        <f t="shared" si="6"/>
-        <v>266800</v>
+        <f t="shared" si="9"/>
+        <v>222333.33333333326</v>
       </c>
       <c r="E241" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>3-PACK OFFICE SMALL BUSINESS MICROSOFT  OEM</v>
       </c>
       <c r="F241" s="3"/>
@@ -11730,7 +12456,10 @@
       <c r="H241" s="3"/>
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
-      <c r="K241" s="3"/>
+      <c r="K241" s="21">
+        <f t="shared" si="11"/>
+        <v>222333.33333333334</v>
+      </c>
       <c r="L241" s="3"/>
       <c r="M241" s="3"/>
       <c r="N241" s="3"/>
@@ -11758,11 +12487,11 @@
         <v>30000</v>
       </c>
       <c r="D242" s="4">
-        <f t="shared" si="6"/>
-        <v>6000</v>
+        <f t="shared" si="9"/>
+        <v>5000</v>
       </c>
       <c r="E242" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">CD VIDEOGUIDA  WIN'95  </v>
       </c>
       <c r="F242" s="3"/>
@@ -11770,7 +12499,10 @@
       <c r="H242" s="3"/>
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
-      <c r="K242" s="3"/>
+      <c r="K242" s="21">
+        <f t="shared" si="11"/>
+        <v>5000</v>
+      </c>
       <c r="L242" s="3"/>
       <c r="M242" s="3"/>
       <c r="N242" s="3"/>
@@ -11798,11 +12530,11 @@
         <v>30000</v>
       </c>
       <c r="D243" s="4">
-        <f t="shared" si="6"/>
-        <v>6000</v>
+        <f t="shared" si="9"/>
+        <v>5000</v>
       </c>
       <c r="E243" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">CD VIDEGUIDA INTERNET  </v>
       </c>
       <c r="F243" s="3"/>
@@ -11810,7 +12542,10 @@
       <c r="H243" s="3"/>
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
-      <c r="K243" s="3"/>
+      <c r="K243" s="21">
+        <f t="shared" si="11"/>
+        <v>5000</v>
+      </c>
       <c r="L243" s="3"/>
       <c r="M243" s="3"/>
       <c r="N243" s="3"/>
@@ -11838,11 +12573,11 @@
         <v>406000</v>
       </c>
       <c r="D244" s="4">
-        <f t="shared" si="6"/>
-        <v>81200</v>
+        <f t="shared" si="9"/>
+        <v>67666.666666666628</v>
       </c>
       <c r="E244" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>WINDOWS 95  MICROSOFT</v>
       </c>
       <c r="F244" s="3"/>
@@ -11850,7 +12585,10 @@
       <c r="H244" s="3"/>
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
-      <c r="K244" s="3"/>
+      <c r="K244" s="21">
+        <f t="shared" si="11"/>
+        <v>67666.666666666672</v>
+      </c>
       <c r="L244" s="3"/>
       <c r="M244" s="3"/>
       <c r="N244" s="3"/>
@@ -11878,11 +12616,11 @@
         <v>197000</v>
       </c>
       <c r="D245" s="4">
-        <f t="shared" si="6"/>
-        <v>39400</v>
+        <f t="shared" si="9"/>
+        <v>32833.333333333314</v>
       </c>
       <c r="E245" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>WINDOWS 95 Lic. Agg. MICROSOFT</v>
       </c>
       <c r="F245" s="3"/>
@@ -11890,7 +12628,10 @@
       <c r="H245" s="3"/>
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
-      <c r="K245" s="3"/>
+      <c r="K245" s="21">
+        <f t="shared" si="11"/>
+        <v>32833.333333333336</v>
+      </c>
       <c r="L245" s="3"/>
       <c r="M245" s="3"/>
       <c r="N245" s="3"/>
@@ -11918,11 +12659,11 @@
         <v>645000</v>
       </c>
       <c r="D246" s="4">
-        <f t="shared" si="6"/>
-        <v>129000</v>
+        <f t="shared" si="9"/>
+        <v>107500</v>
       </c>
       <c r="E246" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>EXCEL 7.0 MICROSOFT</v>
       </c>
       <c r="F246" s="3"/>
@@ -11930,7 +12671,10 @@
       <c r="H246" s="3"/>
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
-      <c r="K246" s="3"/>
+      <c r="K246" s="21">
+        <f t="shared" si="11"/>
+        <v>107500</v>
+      </c>
       <c r="L246" s="3"/>
       <c r="M246" s="3"/>
       <c r="N246" s="3"/>
@@ -11958,11 +12702,11 @@
         <v>645000</v>
       </c>
       <c r="D247" s="4">
-        <f t="shared" si="6"/>
-        <v>129000</v>
+        <f t="shared" si="9"/>
+        <v>107500</v>
       </c>
       <c r="E247" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>EXCEL 97 MICROSOFT</v>
       </c>
       <c r="F247" s="3"/>
@@ -11970,7 +12714,10 @@
       <c r="H247" s="3"/>
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
-      <c r="K247" s="3"/>
+      <c r="K247" s="21">
+        <f t="shared" si="11"/>
+        <v>107500</v>
+      </c>
       <c r="L247" s="3"/>
       <c r="M247" s="3"/>
       <c r="N247" s="3"/>
@@ -11998,11 +12745,11 @@
         <v>259000</v>
       </c>
       <c r="D248" s="4">
-        <f t="shared" si="6"/>
-        <v>51800</v>
+        <f t="shared" si="9"/>
+        <v>43166.666666666657</v>
       </c>
       <c r="E248" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>EXCEL 97 Agg. MICROSOFT</v>
       </c>
       <c r="F248" s="3"/>
@@ -12010,7 +12757,10 @@
       <c r="H248" s="3"/>
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
-      <c r="K248" s="3"/>
+      <c r="K248" s="21">
+        <f t="shared" si="11"/>
+        <v>43166.666666666672</v>
+      </c>
       <c r="L248" s="3"/>
       <c r="M248" s="3"/>
       <c r="N248" s="3"/>
@@ -12038,11 +12788,11 @@
         <v>646000</v>
       </c>
       <c r="D249" s="4">
-        <f t="shared" si="6"/>
-        <v>129200</v>
+        <f t="shared" si="9"/>
+        <v>107666.66666666663</v>
       </c>
       <c r="E249" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>WORD 97 MICROSOFT</v>
       </c>
       <c r="F249" s="3"/>
@@ -12050,7 +12800,10 @@
       <c r="H249" s="3"/>
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
-      <c r="K249" s="3"/>
+      <c r="K249" s="21">
+        <f t="shared" si="11"/>
+        <v>107666.66666666667</v>
+      </c>
       <c r="L249" s="3"/>
       <c r="M249" s="3"/>
       <c r="N249" s="3"/>
@@ -12078,11 +12831,11 @@
         <v>259000</v>
       </c>
       <c r="D250" s="4">
-        <f t="shared" si="6"/>
-        <v>51800</v>
+        <f t="shared" si="9"/>
+        <v>43166.666666666657</v>
       </c>
       <c r="E250" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>WORD 97 Agg. MICROSOFT</v>
       </c>
       <c r="F250" s="3"/>
@@ -12090,7 +12843,10 @@
       <c r="H250" s="3"/>
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
-      <c r="K250" s="3"/>
+      <c r="K250" s="21">
+        <f t="shared" si="11"/>
+        <v>43166.666666666672</v>
+      </c>
       <c r="L250" s="3"/>
       <c r="M250" s="3"/>
       <c r="N250" s="3"/>
@@ -12118,11 +12874,11 @@
         <v>645000</v>
       </c>
       <c r="D251" s="4">
-        <f t="shared" si="6"/>
-        <v>129000</v>
+        <f t="shared" si="9"/>
+        <v>107500</v>
       </c>
       <c r="E251" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ACCESS 97 MICROSOFT</v>
       </c>
       <c r="F251" s="3"/>
@@ -12130,7 +12886,10 @@
       <c r="H251" s="3"/>
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
-      <c r="K251" s="3"/>
+      <c r="K251" s="21">
+        <f t="shared" si="11"/>
+        <v>107500</v>
+      </c>
       <c r="L251" s="3"/>
       <c r="M251" s="3"/>
       <c r="N251" s="3"/>
@@ -12158,11 +12917,11 @@
         <v>879000</v>
       </c>
       <c r="D252" s="4">
-        <f t="shared" si="6"/>
-        <v>175800</v>
+        <f t="shared" si="9"/>
+        <v>146500</v>
       </c>
       <c r="E252" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>OFFICE 97 SMALL BUSINESS MICROSOFT</v>
       </c>
       <c r="F252" s="3"/>
@@ -12170,7 +12929,10 @@
       <c r="H252" s="3"/>
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
-      <c r="K252" s="3"/>
+      <c r="K252" s="21">
+        <f t="shared" si="11"/>
+        <v>146500</v>
+      </c>
       <c r="L252" s="3"/>
       <c r="M252" s="3"/>
       <c r="N252" s="3"/>
@@ -12198,11 +12960,11 @@
         <v>259000</v>
       </c>
       <c r="D253" s="4">
-        <f t="shared" si="6"/>
-        <v>51800</v>
+        <f t="shared" si="9"/>
+        <v>43166.666666666657</v>
       </c>
       <c r="E253" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>HOME ESSENTIALS 98 MICROSOFT</v>
       </c>
       <c r="F253" s="3"/>
@@ -12210,7 +12972,10 @@
       <c r="H253" s="3"/>
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
-      <c r="K253" s="3"/>
+      <c r="K253" s="21">
+        <f t="shared" si="11"/>
+        <v>43166.666666666672</v>
+      </c>
       <c r="L253" s="3"/>
       <c r="M253" s="3"/>
       <c r="N253" s="3"/>
@@ -12238,11 +13003,11 @@
         <v>274000</v>
       </c>
       <c r="D254" s="4">
-        <f t="shared" si="6"/>
-        <v>54800</v>
+        <f t="shared" si="9"/>
+        <v>45666.666666666657</v>
       </c>
       <c r="E254" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>FRONTPAGE 98 MICROSOFT</v>
       </c>
       <c r="F254" s="3"/>
@@ -12250,7 +13015,10 @@
       <c r="H254" s="3"/>
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
-      <c r="K254" s="3"/>
+      <c r="K254" s="21">
+        <f t="shared" si="11"/>
+        <v>45666.666666666672</v>
+      </c>
       <c r="L254" s="3"/>
       <c r="M254" s="3"/>
       <c r="N254" s="3"/>
@@ -12278,11 +13046,11 @@
         <v>975000</v>
       </c>
       <c r="D255" s="4">
-        <f t="shared" si="6"/>
-        <v>195000</v>
+        <f t="shared" si="9"/>
+        <v>162500</v>
       </c>
       <c r="E255" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>OFFICE '97 MICROSOFT</v>
       </c>
       <c r="F255" s="3"/>
@@ -12290,7 +13058,10 @@
       <c r="H255" s="3"/>
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
-      <c r="K255" s="3"/>
+      <c r="K255" s="21">
+        <f t="shared" si="11"/>
+        <v>162500</v>
+      </c>
       <c r="L255" s="3"/>
       <c r="M255" s="3"/>
       <c r="N255" s="3"/>
@@ -12318,11 +13089,11 @@
         <v>480000</v>
       </c>
       <c r="D256" s="4">
-        <f t="shared" si="6"/>
-        <v>96000</v>
+        <f t="shared" si="9"/>
+        <v>80000</v>
       </c>
       <c r="E256" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>OFFICE '97 Agg. MICROSOFT</v>
       </c>
       <c r="F256" s="3"/>
@@ -12330,7 +13101,10 @@
       <c r="H256" s="3"/>
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
-      <c r="K256" s="3"/>
+      <c r="K256" s="21">
+        <f t="shared" si="11"/>
+        <v>80000</v>
+      </c>
       <c r="L256" s="3"/>
       <c r="M256" s="3"/>
       <c r="N256" s="3"/>
@@ -12358,11 +13132,11 @@
         <v>1187000</v>
       </c>
       <c r="D257" s="4">
-        <f t="shared" si="6"/>
-        <v>237400</v>
+        <f t="shared" si="9"/>
+        <v>197833.33333333326</v>
       </c>
       <c r="E257" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>OFFICE '97 Professional MICROSOFT</v>
       </c>
       <c r="F257" s="3"/>
@@ -12370,7 +13144,10 @@
       <c r="H257" s="3"/>
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
-      <c r="K257" s="3"/>
+      <c r="K257" s="21">
+        <f t="shared" si="11"/>
+        <v>197833.33333333334</v>
+      </c>
       <c r="L257" s="3"/>
       <c r="M257" s="3"/>
       <c r="N257" s="3"/>
@@ -12398,11 +13175,11 @@
         <v>832000</v>
       </c>
       <c r="D258" s="4">
-        <f t="shared" si="6"/>
-        <v>166400</v>
+        <f t="shared" si="9"/>
+        <v>138666.66666666663</v>
       </c>
       <c r="E258" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>OFFICE '97 Professional Agg. MICROSOFT</v>
       </c>
       <c r="F258" s="3"/>
@@ -12410,7 +13187,10 @@
       <c r="H258" s="3"/>
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
-      <c r="K258" s="3"/>
+      <c r="K258" s="21">
+        <f t="shared" si="11"/>
+        <v>138666.66666666669</v>
+      </c>
       <c r="L258" s="3"/>
       <c r="M258" s="3"/>
       <c r="N258" s="3"/>
@@ -12438,11 +13218,11 @@
         <v>227000</v>
       </c>
       <c r="D259" s="4">
-        <f t="shared" ref="D259:D322" si="8">C259*$G$2</f>
-        <v>45400</v>
+        <f t="shared" ref="D259:D322" si="12">C259-(C259/(1+($G$2)))</f>
+        <v>37833.333333333314</v>
       </c>
       <c r="E259" s="3" t="str">
-        <f t="shared" ref="E259:E322" si="9">_xlfn.CONCAT(A259," ",B259)</f>
+        <f t="shared" ref="E259:E322" si="13">_xlfn.CONCAT(A259," ",B259)</f>
         <v>VISUAL BASIC 4.0 STD MICROSOFT</v>
       </c>
       <c r="F259" s="3"/>
@@ -12450,7 +13230,10 @@
       <c r="H259" s="3"/>
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
-      <c r="K259" s="3"/>
+      <c r="K259" s="21">
+        <f t="shared" ref="K259:K322" si="14">(C259*$G$2)/$H$2</f>
+        <v>37833.333333333336</v>
+      </c>
       <c r="L259" s="3"/>
       <c r="M259" s="3"/>
       <c r="N259" s="3"/>
@@ -12478,11 +13261,11 @@
         <v>98000</v>
       </c>
       <c r="D260" s="4">
-        <f t="shared" si="8"/>
-        <v>19600</v>
+        <f t="shared" si="12"/>
+        <v>16333.333333333328</v>
       </c>
       <c r="E260" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>VISUAL BASIC 4.0 Agg. MICROSOFT</v>
       </c>
       <c r="F260" s="3"/>
@@ -12490,7 +13273,10 @@
       <c r="H260" s="3"/>
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
-      <c r="K260" s="3"/>
+      <c r="K260" s="21">
+        <f t="shared" si="14"/>
+        <v>16333.333333333334</v>
+      </c>
       <c r="L260" s="3"/>
       <c r="M260" s="3"/>
       <c r="N260" s="3"/>
@@ -12518,11 +13304,11 @@
         <v>1190000</v>
       </c>
       <c r="D261" s="4">
-        <f t="shared" si="8"/>
-        <v>238000</v>
+        <f t="shared" si="12"/>
+        <v>198333.33333333326</v>
       </c>
       <c r="E261" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>VISUAL BASIC 4.0 PROFESSIONAL MICROSOFT</v>
       </c>
       <c r="F261" s="3"/>
@@ -12530,7 +13316,10 @@
       <c r="H261" s="3"/>
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
-      <c r="K261" s="3"/>
+      <c r="K261" s="21">
+        <f t="shared" si="14"/>
+        <v>198333.33333333334</v>
+      </c>
       <c r="L261" s="3"/>
       <c r="M261" s="3"/>
       <c r="N261" s="3"/>
@@ -12558,11 +13347,11 @@
         <v>300000</v>
       </c>
       <c r="D262" s="4">
-        <f t="shared" si="8"/>
-        <v>60000</v>
+        <f t="shared" si="12"/>
+        <v>50000</v>
       </c>
       <c r="E262" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>VISUAL BASIC 4.0 PROF. Agg. MICROSOFT</v>
       </c>
       <c r="F262" s="3"/>
@@ -12570,7 +13359,10 @@
       <c r="H262" s="3"/>
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
-      <c r="K262" s="3"/>
+      <c r="K262" s="21">
+        <f t="shared" si="14"/>
+        <v>50000</v>
+      </c>
       <c r="L262" s="3"/>
       <c r="M262" s="3"/>
       <c r="N262" s="3"/>
@@ -12598,11 +13390,11 @@
         <v>2407000</v>
       </c>
       <c r="D263" s="4">
-        <f t="shared" si="8"/>
-        <v>481400</v>
+        <f t="shared" si="12"/>
+        <v>401166.66666666651</v>
       </c>
       <c r="E263" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>VISUAL BASIC 4.0 ENTERPRICE MICROSOFT</v>
       </c>
       <c r="F263" s="3"/>
@@ -12610,7 +13402,10 @@
       <c r="H263" s="3"/>
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
-      <c r="K263" s="3"/>
+      <c r="K263" s="21">
+        <f t="shared" si="14"/>
+        <v>401166.66666666669</v>
+      </c>
       <c r="L263" s="3"/>
       <c r="M263" s="3"/>
       <c r="N263" s="3"/>
@@ -12638,11 +13433,11 @@
         <v>1021000</v>
       </c>
       <c r="D264" s="4">
-        <f t="shared" si="8"/>
-        <v>204200</v>
+        <f t="shared" si="12"/>
+        <v>170166.66666666663</v>
       </c>
       <c r="E264" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>VISUAL BASIC 4.0 ENTERPRICE Agg. MICROSOFT</v>
       </c>
       <c r="F264" s="3"/>
@@ -12650,7 +13445,10 @@
       <c r="H264" s="3"/>
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
-      <c r="K264" s="3"/>
+      <c r="K264" s="21">
+        <f t="shared" si="14"/>
+        <v>170166.66666666669</v>
+      </c>
       <c r="L264" s="3"/>
       <c r="M264" s="3"/>
       <c r="N264" s="3"/>
@@ -12678,11 +13476,11 @@
         <v>646000</v>
       </c>
       <c r="D265" s="4">
-        <f t="shared" si="8"/>
-        <v>129200</v>
+        <f t="shared" si="12"/>
+        <v>107666.66666666663</v>
       </c>
       <c r="E265" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>POWERPOINT 97 MICROSOFT</v>
       </c>
       <c r="F265" s="3"/>
@@ -12690,7 +13488,10 @@
       <c r="H265" s="3"/>
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
-      <c r="K265" s="3"/>
+      <c r="K265" s="21">
+        <f t="shared" si="14"/>
+        <v>107666.66666666667</v>
+      </c>
       <c r="L265" s="3"/>
       <c r="M265" s="3"/>
       <c r="N265" s="3"/>
@@ -12718,11 +13519,11 @@
         <v>259000</v>
       </c>
       <c r="D266" s="4">
-        <f t="shared" si="8"/>
-        <v>51800</v>
+        <f t="shared" si="12"/>
+        <v>43166.666666666657</v>
       </c>
       <c r="E266" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>POWERPOINT 97 Agg. MICROSOFT</v>
       </c>
       <c r="F266" s="3"/>
@@ -12730,7 +13531,10 @@
       <c r="H266" s="3"/>
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
-      <c r="K266" s="3"/>
+      <c r="K266" s="21">
+        <f t="shared" si="14"/>
+        <v>43166.666666666672</v>
+      </c>
       <c r="L266" s="3"/>
       <c r="M266" s="3"/>
       <c r="N266" s="3"/>
@@ -12758,11 +13562,11 @@
         <v>193000</v>
       </c>
       <c r="D267" s="4">
-        <f t="shared" si="8"/>
-        <v>38600</v>
+        <f t="shared" si="12"/>
+        <v>32166.666666666657</v>
       </c>
       <c r="E267" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>PUBLISHER 3.0 MICROSOFT</v>
       </c>
       <c r="F267" s="3"/>
@@ -12770,7 +13574,10 @@
       <c r="H267" s="3"/>
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
-      <c r="K267" s="3"/>
+      <c r="K267" s="21">
+        <f t="shared" si="14"/>
+        <v>32166.666666666668</v>
+      </c>
       <c r="L267" s="3"/>
       <c r="M267" s="3"/>
       <c r="N267" s="3"/>
@@ -12798,11 +13605,11 @@
         <v>96000</v>
       </c>
       <c r="D268" s="4">
-        <f t="shared" si="8"/>
-        <v>19200</v>
+        <f t="shared" si="12"/>
+        <v>16000</v>
       </c>
       <c r="E268" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>PUBLISHER 3.0 Agg. MICROSOFT</v>
       </c>
       <c r="F268" s="3"/>
@@ -12810,7 +13617,10 @@
       <c r="H268" s="3"/>
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
-      <c r="K268" s="3"/>
+      <c r="K268" s="21">
+        <f t="shared" si="14"/>
+        <v>16000</v>
+      </c>
       <c r="L268" s="3"/>
       <c r="M268" s="3"/>
       <c r="N268" s="3"/>
@@ -12838,11 +13648,11 @@
         <v>594000</v>
       </c>
       <c r="D269" s="4">
-        <f t="shared" si="8"/>
-        <v>118800</v>
+        <f t="shared" si="12"/>
+        <v>99000</v>
       </c>
       <c r="E269" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>WINDOWS NT 4.0 WORKSTATION MICROSOFT</v>
       </c>
       <c r="F269" s="3"/>
@@ -12850,7 +13660,10 @@
       <c r="H269" s="3"/>
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
-      <c r="K269" s="3"/>
+      <c r="K269" s="21">
+        <f t="shared" si="14"/>
+        <v>99000</v>
+      </c>
       <c r="L269" s="3"/>
       <c r="M269" s="3"/>
       <c r="N269" s="3"/>
@@ -12878,11 +13691,11 @@
         <v>282000</v>
       </c>
       <c r="D270" s="4">
-        <f t="shared" si="8"/>
-        <v>56400</v>
+        <f t="shared" si="12"/>
+        <v>47000</v>
       </c>
       <c r="E270" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>WINDOWS NT 4.0 Agg. WORKSTATION MICROSOFT</v>
       </c>
       <c r="F270" s="3"/>
@@ -12890,7 +13703,10 @@
       <c r="H270" s="3"/>
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
-      <c r="K270" s="3"/>
+      <c r="K270" s="21">
+        <f t="shared" si="14"/>
+        <v>47000</v>
+      </c>
       <c r="L270" s="3"/>
       <c r="M270" s="3"/>
       <c r="N270" s="3"/>
@@ -12918,11 +13734,11 @@
         <v>1814000</v>
       </c>
       <c r="D271" s="4">
-        <f t="shared" si="8"/>
-        <v>362800</v>
+        <f t="shared" si="12"/>
+        <v>302333.33333333326</v>
       </c>
       <c r="E271" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>WINDOWS NT 4.0 SERVER 5 client MICROSOFT</v>
       </c>
       <c r="F271" s="3"/>
@@ -12930,7 +13746,10 @@
       <c r="H271" s="3"/>
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
-      <c r="K271" s="3"/>
+      <c r="K271" s="21">
+        <f t="shared" si="14"/>
+        <v>302333.33333333337</v>
+      </c>
       <c r="L271" s="3"/>
       <c r="M271" s="3"/>
       <c r="N271" s="3"/>
@@ -12958,11 +13777,11 @@
         <v>193000</v>
       </c>
       <c r="D272" s="4">
-        <f t="shared" si="8"/>
-        <v>38600</v>
+        <f t="shared" si="12"/>
+        <v>32166.666666666657</v>
       </c>
       <c r="E272" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>WINDOWS 3.1 MICROSOFT</v>
       </c>
       <c r="F272" s="3"/>
@@ -12970,7 +13789,10 @@
       <c r="H272" s="3"/>
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
-      <c r="K272" s="3"/>
+      <c r="K272" s="21">
+        <f t="shared" si="14"/>
+        <v>32166.666666666668</v>
+      </c>
       <c r="L272" s="3"/>
       <c r="M272" s="3"/>
       <c r="N272" s="3"/>
@@ -12998,11 +13820,11 @@
         <v>654000</v>
       </c>
       <c r="D273" s="4">
-        <f t="shared" si="8"/>
-        <v>130800</v>
+        <f t="shared" si="12"/>
+        <v>109000</v>
       </c>
       <c r="E273" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>POWERPOINT 4.0 MICROSOFT</v>
       </c>
       <c r="F273" s="3"/>
@@ -13010,7 +13832,10 @@
       <c r="H273" s="3"/>
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
-      <c r="K273" s="3"/>
+      <c r="K273" s="21">
+        <f t="shared" si="14"/>
+        <v>109000</v>
+      </c>
       <c r="L273" s="3"/>
       <c r="M273" s="3"/>
       <c r="N273" s="3"/>
@@ -13038,11 +13863,11 @@
         <v>729000</v>
       </c>
       <c r="D274" s="4">
-        <f t="shared" si="8"/>
-        <v>145800</v>
+        <f t="shared" si="12"/>
+        <v>121500</v>
       </c>
       <c r="E274" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>EXCEL 5.0 MICROSOFT</v>
       </c>
       <c r="F274" s="3"/>
@@ -13050,7 +13875,10 @@
       <c r="H274" s="3"/>
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
-      <c r="K274" s="3"/>
+      <c r="K274" s="21">
+        <f t="shared" si="14"/>
+        <v>121500</v>
+      </c>
       <c r="L274" s="3"/>
       <c r="M274" s="3"/>
       <c r="N274" s="3"/>
@@ -13078,11 +13906,11 @@
         <v>632000</v>
       </c>
       <c r="D275" s="4">
-        <f t="shared" si="8"/>
-        <v>126400</v>
+        <f t="shared" si="12"/>
+        <v>105333.33333333326</v>
       </c>
       <c r="E275" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>ACCESS 2.0 MICROSOFT</v>
       </c>
       <c r="F275" s="3"/>
@@ -13090,7 +13918,10 @@
       <c r="H275" s="3"/>
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
-      <c r="K275" s="3"/>
+      <c r="K275" s="21">
+        <f t="shared" si="14"/>
+        <v>105333.33333333334</v>
+      </c>
       <c r="L275" s="3"/>
       <c r="M275" s="3"/>
       <c r="N275" s="3"/>
@@ -13118,11 +13949,11 @@
         <v>240000</v>
       </c>
       <c r="D276" s="4">
-        <f t="shared" si="8"/>
-        <v>48000</v>
+        <f t="shared" si="12"/>
+        <v>40000</v>
       </c>
       <c r="E276" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>ACCESS 2.0 Competitivo MICROSOFT</v>
       </c>
       <c r="F276" s="3"/>
@@ -13130,7 +13961,10 @@
       <c r="H276" s="3"/>
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
-      <c r="K276" s="3"/>
+      <c r="K276" s="21">
+        <f t="shared" si="14"/>
+        <v>40000</v>
+      </c>
       <c r="L276" s="3"/>
       <c r="M276" s="3"/>
       <c r="N276" s="3"/>
@@ -13158,11 +13992,11 @@
         <v>955000</v>
       </c>
       <c r="D277" s="4">
-        <f t="shared" si="8"/>
-        <v>191000</v>
+        <f t="shared" si="12"/>
+        <v>159166.66666666663</v>
       </c>
       <c r="E277" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">OFFICE 4.2 MICROSOFT </v>
       </c>
       <c r="F277" s="3"/>
@@ -13170,7 +14004,10 @@
       <c r="H277" s="3"/>
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
-      <c r="K277" s="3"/>
+      <c r="K277" s="21">
+        <f t="shared" si="14"/>
+        <v>159166.66666666669</v>
+      </c>
       <c r="L277" s="3"/>
       <c r="M277" s="3"/>
       <c r="N277" s="3"/>
@@ -13198,11 +14035,11 @@
         <v>1126000</v>
       </c>
       <c r="D278" s="4">
-        <f t="shared" si="8"/>
-        <v>225200</v>
+        <f t="shared" si="12"/>
+        <v>187666.66666666663</v>
       </c>
       <c r="E278" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">OFFICE 4.3 PROFESSIONAL MICROSOFT </v>
       </c>
       <c r="F278" s="3"/>
@@ -13210,7 +14047,10 @@
       <c r="H278" s="3"/>
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
-      <c r="K278" s="3"/>
+      <c r="K278" s="21">
+        <f t="shared" si="14"/>
+        <v>187666.66666666669</v>
+      </c>
       <c r="L278" s="3"/>
       <c r="M278" s="3"/>
       <c r="N278" s="3"/>
@@ -13234,11 +14074,11 @@
       <c r="B279" s="3"/>
       <c r="C279" s="4"/>
       <c r="D279" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E279" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">STAMPANTI </v>
       </c>
       <c r="F279" s="3"/>
@@ -13246,7 +14086,10 @@
       <c r="H279" s="3"/>
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
-      <c r="K279" s="3"/>
+      <c r="K279" s="21">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="L279" s="3"/>
       <c r="M279" s="3"/>
       <c r="N279" s="3"/>
@@ -13274,11 +14117,11 @@
         <v>297000</v>
       </c>
       <c r="D280" s="4">
-        <f t="shared" si="8"/>
-        <v>59400</v>
+        <f t="shared" si="12"/>
+        <v>49500</v>
       </c>
       <c r="E280" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON LX300 9 aghi, 80 col. 220 cps. opz. colore</v>
       </c>
       <c r="F280" s="3"/>
@@ -13286,7 +14129,10 @@
       <c r="H280" s="3"/>
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
-      <c r="K280" s="3"/>
+      <c r="K280" s="21">
+        <f t="shared" si="14"/>
+        <v>49500</v>
+      </c>
       <c r="L280" s="3"/>
       <c r="M280" s="3"/>
       <c r="N280" s="3"/>
@@ -13314,11 +14160,11 @@
         <v>646000</v>
       </c>
       <c r="D281" s="4">
-        <f t="shared" si="8"/>
-        <v>129200</v>
+        <f t="shared" si="12"/>
+        <v>107666.66666666663</v>
       </c>
       <c r="E281" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON LX1050+ 9 aghi, 136 col. 200 cps</v>
       </c>
       <c r="F281" s="3"/>
@@ -13326,7 +14172,10 @@
       <c r="H281" s="3"/>
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
-      <c r="K281" s="3"/>
+      <c r="K281" s="21">
+        <f t="shared" si="14"/>
+        <v>107666.66666666667</v>
+      </c>
       <c r="L281" s="3"/>
       <c r="M281" s="3"/>
       <c r="N281" s="3"/>
@@ -13354,11 +14203,11 @@
         <v>714000</v>
       </c>
       <c r="D282" s="4">
-        <f t="shared" si="8"/>
-        <v>142800</v>
+        <f t="shared" si="12"/>
+        <v>119000</v>
       </c>
       <c r="E282" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON FX870 9 aghi, 80 col. 380 cps</v>
       </c>
       <c r="F282" s="3"/>
@@ -13366,7 +14215,10 @@
       <c r="H282" s="3"/>
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
-      <c r="K282" s="3"/>
+      <c r="K282" s="21">
+        <f t="shared" si="14"/>
+        <v>119000</v>
+      </c>
       <c r="L282" s="3"/>
       <c r="M282" s="3"/>
       <c r="N282" s="3"/>
@@ -13394,11 +14246,11 @@
         <v>807000</v>
       </c>
       <c r="D283" s="4">
-        <f t="shared" si="8"/>
-        <v>161400</v>
+        <f t="shared" si="12"/>
+        <v>134500</v>
       </c>
       <c r="E283" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON FX1170 9 aghi, 136 col.380 cps</v>
       </c>
       <c r="F283" s="3"/>
@@ -13406,7 +14258,10 @@
       <c r="H283" s="3"/>
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
-      <c r="K283" s="3"/>
+      <c r="K283" s="21">
+        <f t="shared" si="14"/>
+        <v>134500</v>
+      </c>
       <c r="L283" s="3"/>
       <c r="M283" s="3"/>
       <c r="N283" s="3"/>
@@ -13434,11 +14289,11 @@
         <v>591000</v>
       </c>
       <c r="D284" s="4">
-        <f t="shared" si="8"/>
-        <v>118200</v>
+        <f t="shared" si="12"/>
+        <v>98500</v>
       </c>
       <c r="E284" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON LQ570+ 24 aghi, 80 col. 225 cps</v>
       </c>
       <c r="F284" s="3"/>
@@ -13446,7 +14301,10 @@
       <c r="H284" s="3"/>
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
-      <c r="K284" s="3"/>
+      <c r="K284" s="21">
+        <f t="shared" si="14"/>
+        <v>98500</v>
+      </c>
       <c r="L284" s="3"/>
       <c r="M284" s="3"/>
       <c r="N284" s="3"/>
@@ -13474,11 +14332,11 @@
         <v>918000</v>
       </c>
       <c r="D285" s="4">
-        <f t="shared" si="8"/>
-        <v>183600</v>
+        <f t="shared" si="12"/>
+        <v>153000</v>
       </c>
       <c r="E285" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON LQ2070+ 24 aghi, 136 col. 225 cps</v>
       </c>
       <c r="F285" s="3"/>
@@ -13486,7 +14344,10 @@
       <c r="H285" s="3"/>
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
-      <c r="K285" s="3"/>
+      <c r="K285" s="21">
+        <f t="shared" si="14"/>
+        <v>153000</v>
+      </c>
       <c r="L285" s="3"/>
       <c r="M285" s="3"/>
       <c r="N285" s="3"/>
@@ -13514,11 +14375,11 @@
         <v>1265000</v>
       </c>
       <c r="D286" s="4">
-        <f t="shared" si="8"/>
-        <v>253000</v>
+        <f t="shared" si="12"/>
+        <v>210833.33333333326</v>
       </c>
       <c r="E286" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON LQ 2170 24 aghi, 136 col. 440 cps</v>
       </c>
       <c r="F286" s="3"/>
@@ -13526,7 +14387,10 @@
       <c r="H286" s="3"/>
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
-      <c r="K286" s="3"/>
+      <c r="K286" s="21">
+        <f t="shared" si="14"/>
+        <v>210833.33333333334</v>
+      </c>
       <c r="L286" s="3"/>
       <c r="M286" s="3"/>
       <c r="N286" s="3"/>
@@ -13554,11 +14418,11 @@
         <v>256000</v>
       </c>
       <c r="D287" s="4">
-        <f t="shared" si="8"/>
-        <v>51200</v>
+        <f t="shared" si="12"/>
+        <v>42666.666666666657</v>
       </c>
       <c r="E287" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON STYLUS 300COLOR Ink Jet A4,1ppm col.</v>
       </c>
       <c r="F287" s="3"/>
@@ -13566,7 +14430,10 @@
       <c r="H287" s="3"/>
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
-      <c r="K287" s="3"/>
+      <c r="K287" s="21">
+        <f t="shared" si="14"/>
+        <v>42666.666666666672</v>
+      </c>
       <c r="L287" s="3"/>
       <c r="M287" s="3"/>
       <c r="N287" s="3"/>
@@ -13594,11 +14461,11 @@
         <v>371000</v>
       </c>
       <c r="D288" s="4">
-        <f t="shared" si="8"/>
-        <v>74200</v>
+        <f t="shared" si="12"/>
+        <v>61833.333333333314</v>
       </c>
       <c r="E288" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON STYLUS 400COLOR Ink Jet A4,3ppm col.</v>
       </c>
       <c r="F288" s="3"/>
@@ -13606,7 +14473,10 @@
       <c r="H288" s="3"/>
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
-      <c r="K288" s="3"/>
+      <c r="K288" s="21">
+        <f t="shared" si="14"/>
+        <v>61833.333333333336</v>
+      </c>
       <c r="L288" s="3"/>
       <c r="M288" s="3"/>
       <c r="N288" s="3"/>
@@ -13634,11 +14504,11 @@
         <v>457000</v>
       </c>
       <c r="D289" s="4">
-        <f t="shared" si="8"/>
-        <v>91400</v>
+        <f t="shared" si="12"/>
+        <v>76166.666666666628</v>
       </c>
       <c r="E289" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON STYLUS 600COLOR Ink Jet A4,4ppm col.</v>
       </c>
       <c r="F289" s="3"/>
@@ -13646,7 +14516,10 @@
       <c r="H289" s="3"/>
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
-      <c r="K289" s="3"/>
+      <c r="K289" s="21">
+        <f t="shared" si="14"/>
+        <v>76166.666666666672</v>
+      </c>
       <c r="L289" s="3"/>
       <c r="M289" s="3"/>
       <c r="N289" s="3"/>
@@ -13674,11 +14547,11 @@
         <v>642000</v>
       </c>
       <c r="D290" s="4">
-        <f t="shared" si="8"/>
-        <v>128400</v>
+        <f t="shared" si="12"/>
+        <v>107000</v>
       </c>
       <c r="E290" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON STYLUS 800COLOR Ink Jet A4,7ppm col.</v>
       </c>
       <c r="F290" s="3"/>
@@ -13686,7 +14559,10 @@
       <c r="H290" s="3"/>
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
-      <c r="K290" s="3"/>
+      <c r="K290" s="21">
+        <f t="shared" si="14"/>
+        <v>107000</v>
+      </c>
       <c r="L290" s="3"/>
       <c r="M290" s="3"/>
       <c r="N290" s="3"/>
@@ -13714,11 +14590,11 @@
         <v>1571000</v>
       </c>
       <c r="D291" s="4">
-        <f t="shared" si="8"/>
-        <v>314200</v>
+        <f t="shared" si="12"/>
+        <v>261833.33333333326</v>
       </c>
       <c r="E291" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON STYLUS 1520COLOR Ink Jet A2,800cps draft</v>
       </c>
       <c r="F291" s="3"/>
@@ -13726,7 +14602,10 @@
       <c r="H291" s="3"/>
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
-      <c r="K291" s="3"/>
+      <c r="K291" s="21">
+        <f t="shared" si="14"/>
+        <v>261833.33333333334</v>
+      </c>
       <c r="L291" s="3"/>
       <c r="M291" s="3"/>
       <c r="N291" s="3"/>
@@ -13754,11 +14633,11 @@
         <v>756000</v>
       </c>
       <c r="D292" s="4">
-        <f t="shared" si="8"/>
-        <v>151200</v>
+        <f t="shared" si="12"/>
+        <v>126000</v>
       </c>
       <c r="E292" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON STYLUS 1000 Ink Jet A3,250cps draft</v>
       </c>
       <c r="F292" s="3"/>
@@ -13766,7 +14645,10 @@
       <c r="H292" s="3"/>
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
-      <c r="K292" s="3"/>
+      <c r="K292" s="21">
+        <f t="shared" si="14"/>
+        <v>126000</v>
+      </c>
       <c r="L292" s="3"/>
       <c r="M292" s="3"/>
       <c r="N292" s="3"/>
@@ -13794,11 +14676,11 @@
         <v>1571000</v>
       </c>
       <c r="D293" s="4">
-        <f t="shared" si="8"/>
-        <v>314200</v>
+        <f t="shared" si="12"/>
+        <v>261833.33333333326</v>
       </c>
       <c r="E293" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP.EPSON STYLUS PRO XL+ Ink Jet A4/A3</v>
       </c>
       <c r="F293" s="3"/>
@@ -13806,7 +14688,10 @@
       <c r="H293" s="3"/>
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
-      <c r="K293" s="3"/>
+      <c r="K293" s="21">
+        <f t="shared" si="14"/>
+        <v>261833.33333333334</v>
+      </c>
       <c r="L293" s="3"/>
       <c r="M293" s="3"/>
       <c r="N293" s="3"/>
@@ -13834,11 +14719,11 @@
         <v>2716000</v>
       </c>
       <c r="D294" s="4">
-        <f t="shared" si="8"/>
-        <v>543200</v>
+        <f t="shared" si="12"/>
+        <v>452666.66666666651</v>
       </c>
       <c r="E294" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">STAMP.EPSON STYLUS  3000 Ink Jet A2 800cpc 1440*720 dpi </v>
       </c>
       <c r="F294" s="3"/>
@@ -13846,7 +14731,10 @@
       <c r="H294" s="3"/>
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
-      <c r="K294" s="3"/>
+      <c r="K294" s="21">
+        <f t="shared" si="14"/>
+        <v>452666.66666666669</v>
+      </c>
       <c r="L294" s="3"/>
       <c r="M294" s="3"/>
       <c r="N294" s="3"/>
@@ -13874,11 +14762,11 @@
         <v>640000</v>
       </c>
       <c r="D295" s="4">
-        <f t="shared" si="8"/>
-        <v>128000</v>
+        <f t="shared" si="12"/>
+        <v>106666.66666666663</v>
       </c>
       <c r="E295" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">STAMP.EPSON STYLUS PHOTO Ink Jet A4 6 colori 2ppm </v>
       </c>
       <c r="F295" s="3"/>
@@ -13886,7 +14774,10 @@
       <c r="H295" s="3"/>
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
-      <c r="K295" s="3"/>
+      <c r="K295" s="21">
+        <f t="shared" si="14"/>
+        <v>106666.66666666667</v>
+      </c>
       <c r="L295" s="3"/>
       <c r="M295" s="3"/>
       <c r="N295" s="3"/>
@@ -13914,11 +14805,11 @@
         <v>255000</v>
       </c>
       <c r="D296" s="4">
-        <f t="shared" si="8"/>
-        <v>51000</v>
+        <f t="shared" si="12"/>
+        <v>42500</v>
       </c>
       <c r="E296" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. CANON BJ-250 COLOR Ink Jet A4, 1ppm col</v>
       </c>
       <c r="F296" s="3"/>
@@ -13926,7 +14817,10 @@
       <c r="H296" s="3"/>
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
-      <c r="K296" s="3"/>
+      <c r="K296" s="21">
+        <f t="shared" si="14"/>
+        <v>42500</v>
+      </c>
       <c r="L296" s="3"/>
       <c r="M296" s="3"/>
       <c r="N296" s="3"/>
@@ -13954,11 +14848,11 @@
         <v>413000</v>
       </c>
       <c r="D297" s="4">
-        <f t="shared" si="8"/>
-        <v>82600</v>
+        <f t="shared" si="12"/>
+        <v>68833.333333333314</v>
       </c>
       <c r="E297" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. CANON BJC-80 COLOR Ink jet A4, 2ppm col.</v>
       </c>
       <c r="F297" s="3"/>
@@ -13966,7 +14860,10 @@
       <c r="H297" s="3"/>
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
-      <c r="K297" s="3"/>
+      <c r="K297" s="21">
+        <f t="shared" si="14"/>
+        <v>68833.333333333343</v>
+      </c>
       <c r="L297" s="3"/>
       <c r="M297" s="3"/>
       <c r="N297" s="3"/>
@@ -13994,11 +14891,11 @@
         <v>361000</v>
       </c>
       <c r="D298" s="4">
-        <f t="shared" si="8"/>
-        <v>72200</v>
+        <f t="shared" si="12"/>
+        <v>60166.666666666628</v>
       </c>
       <c r="E298" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. CANON BJC-4300 COLOR Ink Jet A4, 1ppm col.</v>
       </c>
       <c r="F298" s="3"/>
@@ -14006,7 +14903,10 @@
       <c r="H298" s="3"/>
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
-      <c r="K298" s="3"/>
+      <c r="K298" s="21">
+        <f t="shared" si="14"/>
+        <v>60166.666666666672</v>
+      </c>
       <c r="L298" s="3"/>
       <c r="M298" s="3"/>
       <c r="N298" s="3"/>
@@ -14034,11 +14934,11 @@
         <v>544000</v>
       </c>
       <c r="D299" s="4">
-        <f t="shared" si="8"/>
-        <v>108800</v>
+        <f t="shared" si="12"/>
+        <v>90666.666666666628</v>
       </c>
       <c r="E299" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. CANON BJC-4550 COLOR Ink Jet A4/A3, 1 ppm</v>
       </c>
       <c r="F299" s="3"/>
@@ -14046,7 +14946,10 @@
       <c r="H299" s="3"/>
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
-      <c r="K299" s="3"/>
+      <c r="K299" s="21">
+        <f t="shared" si="14"/>
+        <v>90666.666666666672</v>
+      </c>
       <c r="L299" s="3"/>
       <c r="M299" s="3"/>
       <c r="N299" s="3"/>
@@ -14074,11 +14977,11 @@
         <v>678000</v>
       </c>
       <c r="D300" s="4">
-        <f t="shared" si="8"/>
-        <v>135600</v>
+        <f t="shared" si="12"/>
+        <v>113000</v>
       </c>
       <c r="E300" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. CANON BJC-4650 COLOR Ink Jet A4/A3, 4,5 ppm</v>
       </c>
       <c r="F300" s="3"/>
@@ -14086,7 +14989,10 @@
       <c r="H300" s="3"/>
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
-      <c r="K300" s="3"/>
+      <c r="K300" s="21">
+        <f t="shared" si="14"/>
+        <v>113000</v>
+      </c>
       <c r="L300" s="3"/>
       <c r="M300" s="3"/>
       <c r="N300" s="3"/>
@@ -14114,11 +15020,11 @@
         <v>1054000</v>
       </c>
       <c r="D301" s="4">
-        <f t="shared" si="8"/>
-        <v>210800</v>
+        <f t="shared" si="12"/>
+        <v>175666.66666666663</v>
       </c>
       <c r="E301" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. CANON BJC-5500 COLOR Ink Jet A3/A2 694cps</v>
       </c>
       <c r="F301" s="3"/>
@@ -14126,7 +15032,10 @@
       <c r="H301" s="3"/>
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
-      <c r="K301" s="3"/>
+      <c r="K301" s="21">
+        <f t="shared" si="14"/>
+        <v>175666.66666666669</v>
+      </c>
       <c r="L301" s="3"/>
       <c r="M301" s="3"/>
       <c r="N301" s="3"/>
@@ -14154,11 +15063,11 @@
         <v>482000</v>
       </c>
       <c r="D302" s="4">
-        <f t="shared" si="8"/>
-        <v>96400</v>
+        <f t="shared" si="12"/>
+        <v>80333.333333333314</v>
       </c>
       <c r="E302" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. CANON BJC-620 COLOR Ink Jet A4, 300cps</v>
       </c>
       <c r="F302" s="3"/>
@@ -14166,7 +15075,10 @@
       <c r="H302" s="3"/>
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
-      <c r="K302" s="3"/>
+      <c r="K302" s="21">
+        <f t="shared" si="14"/>
+        <v>80333.333333333343</v>
+      </c>
       <c r="L302" s="3"/>
       <c r="M302" s="3"/>
       <c r="N302" s="3"/>
@@ -14194,11 +15106,11 @@
         <v>722000</v>
       </c>
       <c r="D303" s="4">
-        <f t="shared" si="8"/>
-        <v>144400</v>
+        <f t="shared" si="12"/>
+        <v>120333.33333333326</v>
       </c>
       <c r="E303" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. CANON BJC-7000 COLOR Ink Jet A4,4,5ppm, 1200x600dpi</v>
       </c>
       <c r="F303" s="3"/>
@@ -14206,7 +15118,10 @@
       <c r="H303" s="3"/>
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
-      <c r="K303" s="3"/>
+      <c r="K303" s="21">
+        <f t="shared" si="14"/>
+        <v>120333.33333333334</v>
+      </c>
       <c r="L303" s="3"/>
       <c r="M303" s="3"/>
       <c r="N303" s="3"/>
@@ -14234,11 +15149,11 @@
         <v>269000</v>
       </c>
       <c r="D304" s="4">
-        <f t="shared" si="8"/>
-        <v>53800</v>
+        <f t="shared" si="12"/>
+        <v>44833.333333333314</v>
       </c>
       <c r="E304" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. HP 400L Ink Jet A4, 3 ppm col.</v>
       </c>
       <c r="F304" s="3"/>
@@ -14246,7 +15161,10 @@
       <c r="H304" s="3"/>
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
-      <c r="K304" s="3"/>
+      <c r="K304" s="21">
+        <f t="shared" si="14"/>
+        <v>44833.333333333336</v>
+      </c>
       <c r="L304" s="3"/>
       <c r="M304" s="3"/>
       <c r="N304" s="3"/>
@@ -14274,11 +15192,11 @@
         <v>371000</v>
       </c>
       <c r="D305" s="4">
-        <f t="shared" si="8"/>
-        <v>74200</v>
+        <f t="shared" si="12"/>
+        <v>61833.333333333314</v>
       </c>
       <c r="E305" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. HP 670 Ink Jet A4, 3 ppm col.</v>
       </c>
       <c r="F305" s="3"/>
@@ -14286,7 +15204,10 @@
       <c r="H305" s="3"/>
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
-      <c r="K305" s="3"/>
+      <c r="K305" s="21">
+        <f t="shared" si="14"/>
+        <v>61833.333333333336</v>
+      </c>
       <c r="L305" s="3"/>
       <c r="M305" s="3"/>
       <c r="N305" s="3"/>
@@ -14314,11 +15235,11 @@
         <v>462000</v>
       </c>
       <c r="D306" s="4">
-        <f t="shared" si="8"/>
-        <v>92400</v>
+        <f t="shared" si="12"/>
+        <v>77000</v>
       </c>
       <c r="E306" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. HP 690+ Ink Jet A4,  5 ppm col.</v>
       </c>
       <c r="F306" s="3"/>
@@ -14326,7 +15247,10 @@
       <c r="H306" s="3"/>
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
-      <c r="K306" s="3"/>
+      <c r="K306" s="21">
+        <f t="shared" si="14"/>
+        <v>77000</v>
+      </c>
       <c r="L306" s="3"/>
       <c r="M306" s="3"/>
       <c r="N306" s="3"/>
@@ -14354,11 +15278,11 @@
         <v>541000</v>
       </c>
       <c r="D307" s="4">
-        <f t="shared" si="8"/>
-        <v>108200</v>
+        <f t="shared" si="12"/>
+        <v>90166.666666666628</v>
       </c>
       <c r="E307" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. HP 720C Ink Jet A4,  7 ppm col.</v>
       </c>
       <c r="F307" s="3"/>
@@ -14366,7 +15290,10 @@
       <c r="H307" s="3"/>
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
-      <c r="K307" s="3"/>
+      <c r="K307" s="21">
+        <f t="shared" si="14"/>
+        <v>90166.666666666672</v>
+      </c>
       <c r="L307" s="3"/>
       <c r="M307" s="3"/>
       <c r="N307" s="3"/>
@@ -14394,11 +15321,11 @@
         <v>648000</v>
       </c>
       <c r="D308" s="4">
-        <f t="shared" si="8"/>
-        <v>129600</v>
+        <f t="shared" si="12"/>
+        <v>108000</v>
       </c>
       <c r="E308" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. HP 870 CXI Ink Jet A4,  8 ppm col.</v>
       </c>
       <c r="F308" s="3"/>
@@ -14406,7 +15333,10 @@
       <c r="H308" s="3"/>
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
-      <c r="K308" s="3"/>
+      <c r="K308" s="21">
+        <f t="shared" si="14"/>
+        <v>108000</v>
+      </c>
       <c r="L308" s="3"/>
       <c r="M308" s="3"/>
       <c r="N308" s="3"/>
@@ -14434,11 +15364,11 @@
         <v>644000</v>
       </c>
       <c r="D309" s="4">
-        <f t="shared" si="8"/>
-        <v>128800</v>
+        <f t="shared" si="12"/>
+        <v>107333.33333333326</v>
       </c>
       <c r="E309" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. HP 890C Ink Jet A4,  9 ppm col.</v>
       </c>
       <c r="F309" s="3"/>
@@ -14446,7 +15376,10 @@
       <c r="H309" s="3"/>
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
-      <c r="K309" s="3"/>
+      <c r="K309" s="21">
+        <f t="shared" si="14"/>
+        <v>107333.33333333334</v>
+      </c>
       <c r="L309" s="3"/>
       <c r="M309" s="3"/>
       <c r="N309" s="3"/>
@@ -14474,11 +15407,11 @@
         <v>902000</v>
       </c>
       <c r="D310" s="4">
-        <f t="shared" si="8"/>
-        <v>180400</v>
+        <f t="shared" si="12"/>
+        <v>150333.33333333326</v>
       </c>
       <c r="E310" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. HP 1100C Ink Jet A3/A4,  6 ppm col., 2Mb</v>
       </c>
       <c r="F310" s="3"/>
@@ -14486,7 +15419,10 @@
       <c r="H310" s="3"/>
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
-      <c r="K310" s="3"/>
+      <c r="K310" s="21">
+        <f t="shared" si="14"/>
+        <v>150333.33333333334</v>
+      </c>
       <c r="L310" s="3"/>
       <c r="M310" s="3"/>
       <c r="N310" s="3"/>
@@ -14514,11 +15450,11 @@
         <v>722000</v>
       </c>
       <c r="D311" s="4">
-        <f t="shared" si="8"/>
-        <v>144400</v>
+        <f t="shared" si="12"/>
+        <v>120333.33333333326</v>
       </c>
       <c r="E311" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. HP 6L Laser, A4 600dpi, 6ppm</v>
       </c>
       <c r="F311" s="3"/>
@@ -14526,7 +15462,10 @@
       <c r="H311" s="3"/>
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
-      <c r="K311" s="3"/>
+      <c r="K311" s="21">
+        <f t="shared" si="14"/>
+        <v>120333.33333333334</v>
+      </c>
       <c r="L311" s="3"/>
       <c r="M311" s="3"/>
       <c r="N311" s="3"/>
@@ -14554,11 +15493,11 @@
         <v>1457000</v>
       </c>
       <c r="D312" s="4">
-        <f t="shared" si="8"/>
-        <v>291400</v>
+        <f t="shared" si="12"/>
+        <v>242833.33333333326</v>
       </c>
       <c r="E312" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. HP 6P Laser, A4 600dpi, 6ppm</v>
       </c>
       <c r="F312" s="3"/>
@@ -14566,7 +15505,10 @@
       <c r="H312" s="3"/>
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
-      <c r="K312" s="3"/>
+      <c r="K312" s="21">
+        <f t="shared" si="14"/>
+        <v>242833.33333333334</v>
+      </c>
       <c r="L312" s="3"/>
       <c r="M312" s="3"/>
       <c r="N312" s="3"/>
@@ -14594,11 +15536,11 @@
         <v>1786000</v>
       </c>
       <c r="D313" s="4">
-        <f t="shared" si="8"/>
-        <v>357200</v>
+        <f t="shared" si="12"/>
+        <v>297666.66666666651</v>
       </c>
       <c r="E313" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>STAMP. HP 6MP Laser, A4 600dpi, 8ppm, 3Mb</v>
       </c>
       <c r="F313" s="3"/>
@@ -14606,7 +15548,10 @@
       <c r="H313" s="3"/>
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
-      <c r="K313" s="3"/>
+      <c r="K313" s="21">
+        <f t="shared" si="14"/>
+        <v>297666.66666666669</v>
+      </c>
       <c r="L313" s="3"/>
       <c r="M313" s="3"/>
       <c r="N313" s="3"/>
@@ -14630,11 +15575,11 @@
       <c r="B314" s="3"/>
       <c r="C314" s="4"/>
       <c r="D314" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E314" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">CABINATI  </v>
       </c>
       <c r="F314" s="3"/>
@@ -14642,7 +15587,10 @@
       <c r="H314" s="3"/>
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
-      <c r="K314" s="3"/>
+      <c r="K314" s="21">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="L314" s="3"/>
       <c r="M314" s="3"/>
       <c r="N314" s="3"/>
@@ -14670,11 +15618,11 @@
         <v>85000</v>
       </c>
       <c r="D315" s="4">
-        <f t="shared" si="8"/>
-        <v>17000</v>
+        <f t="shared" si="12"/>
+        <v>14166.666666666657</v>
       </c>
       <c r="E315" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>CASE DESKTOP   CE CK 131-6 P/S 200W</v>
       </c>
       <c r="F315" s="3"/>
@@ -14682,7 +15630,10 @@
       <c r="H315" s="3"/>
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
-      <c r="K315" s="3"/>
+      <c r="K315" s="21">
+        <f t="shared" si="14"/>
+        <v>14166.666666666668</v>
+      </c>
       <c r="L315" s="3"/>
       <c r="M315" s="3"/>
       <c r="N315" s="3"/>
@@ -14710,11 +15661,11 @@
         <v>84000</v>
       </c>
       <c r="D316" s="4">
-        <f t="shared" si="8"/>
-        <v>16800</v>
+        <f t="shared" si="12"/>
+        <v>14000</v>
       </c>
       <c r="E316" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>CASE MINITOWER CE CK 136-1 P/S 200W</v>
       </c>
       <c r="F316" s="3"/>
@@ -14722,7 +15673,10 @@
       <c r="H316" s="3"/>
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
-      <c r="K316" s="3"/>
+      <c r="K316" s="21">
+        <f t="shared" si="14"/>
+        <v>14000</v>
+      </c>
       <c r="L316" s="3"/>
       <c r="M316" s="3"/>
       <c r="N316" s="3"/>
@@ -14750,11 +15704,11 @@
         <v>115000</v>
       </c>
       <c r="D317" s="4">
-        <f t="shared" si="8"/>
-        <v>23000</v>
+        <f t="shared" si="12"/>
+        <v>19166.666666666657</v>
       </c>
       <c r="E317" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">CASE MIDITOWER CE CK 135-1 P/S 230W </v>
       </c>
       <c r="F317" s="3"/>
@@ -14762,7 +15716,10 @@
       <c r="H317" s="3"/>
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
-      <c r="K317" s="3"/>
+      <c r="K317" s="21">
+        <f t="shared" si="14"/>
+        <v>19166.666666666668</v>
+      </c>
       <c r="L317" s="3"/>
       <c r="M317" s="3"/>
       <c r="N317" s="3"/>
@@ -14790,11 +15747,11 @@
         <v>152000</v>
       </c>
       <c r="D318" s="4">
-        <f t="shared" si="8"/>
-        <v>30400</v>
+        <f t="shared" si="12"/>
+        <v>25333.333333333328</v>
       </c>
       <c r="E318" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">CASE BIG TOWER CE   CK139-1 P/S 230W </v>
       </c>
       <c r="F318" s="3"/>
@@ -14802,7 +15759,10 @@
       <c r="H318" s="3"/>
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
-      <c r="K318" s="3"/>
+      <c r="K318" s="21">
+        <f t="shared" si="14"/>
+        <v>25333.333333333336</v>
+      </c>
       <c r="L318" s="3"/>
       <c r="M318" s="3"/>
       <c r="N318" s="3"/>
@@ -14830,11 +15790,11 @@
         <v>82000</v>
       </c>
       <c r="D319" s="4">
-        <f t="shared" si="8"/>
-        <v>16400</v>
+        <f t="shared" si="12"/>
+        <v>13666.666666666657</v>
       </c>
       <c r="E319" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>CASE DESKTOP CE CK 131-8 P/S 200W</v>
       </c>
       <c r="F319" s="3"/>
@@ -14842,7 +15802,10 @@
       <c r="H319" s="3"/>
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
-      <c r="K319" s="3"/>
+      <c r="K319" s="21">
+        <f t="shared" si="14"/>
+        <v>13666.666666666668</v>
+      </c>
       <c r="L319" s="3"/>
       <c r="M319" s="3"/>
       <c r="N319" s="3"/>
@@ -14870,11 +15833,11 @@
         <v>84000</v>
       </c>
       <c r="D320" s="4">
-        <f t="shared" si="8"/>
-        <v>16800</v>
+        <f t="shared" si="12"/>
+        <v>14000</v>
       </c>
       <c r="E320" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>CASE SUB-MIDITOWER CE  CK 132-3 P/S 200W</v>
       </c>
       <c r="F320" s="3"/>
@@ -14882,7 +15845,10 @@
       <c r="H320" s="3"/>
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
-      <c r="K320" s="3"/>
+      <c r="K320" s="21">
+        <f t="shared" si="14"/>
+        <v>14000</v>
+      </c>
       <c r="L320" s="3"/>
       <c r="M320" s="3"/>
       <c r="N320" s="3"/>
@@ -14910,11 +15876,11 @@
         <v>115000</v>
       </c>
       <c r="D321" s="4">
-        <f t="shared" si="8"/>
-        <v>23000</v>
+        <f t="shared" si="12"/>
+        <v>19166.666666666657</v>
       </c>
       <c r="E321" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>CASE  MIDITOWER CE  CK 135-2 P/S 230W</v>
       </c>
       <c r="F321" s="3"/>
@@ -14922,7 +15888,10 @@
       <c r="H321" s="3"/>
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
-      <c r="K321" s="3"/>
+      <c r="K321" s="21">
+        <f t="shared" si="14"/>
+        <v>19166.666666666668</v>
+      </c>
       <c r="L321" s="3"/>
       <c r="M321" s="3"/>
       <c r="N321" s="3"/>
@@ -14950,11 +15919,11 @@
         <v>153000</v>
       </c>
       <c r="D322" s="4">
-        <f t="shared" si="8"/>
-        <v>30600</v>
+        <f t="shared" si="12"/>
+        <v>25500</v>
       </c>
       <c r="E322" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>CASE TOWER CE CK 139-2 P/S 230W</v>
       </c>
       <c r="F322" s="3"/>
@@ -14962,7 +15931,10 @@
       <c r="H322" s="3"/>
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
-      <c r="K322" s="3"/>
+      <c r="K322" s="21">
+        <f t="shared" si="14"/>
+        <v>25500</v>
+      </c>
       <c r="L322" s="3"/>
       <c r="M322" s="3"/>
       <c r="N322" s="3"/>
@@ -14990,11 +15962,11 @@
         <v>80000</v>
       </c>
       <c r="D323" s="4">
-        <f t="shared" ref="D323:D337" si="10">C323*$G$2</f>
-        <v>16000</v>
+        <f t="shared" ref="D323:D337" si="15">C323-(C323/(1+($G$2)))</f>
+        <v>13333.333333333328</v>
       </c>
       <c r="E323" s="3" t="str">
-        <f t="shared" ref="E323:E337" si="11">_xlfn.CONCAT(A323," ",B323)</f>
+        <f t="shared" ref="E323:E337" si="16">_xlfn.CONCAT(A323," ",B323)</f>
         <v>CASE MIDITOWER BC VIP 432 P/S 230W</v>
       </c>
       <c r="F323" s="3"/>
@@ -15002,7 +15974,10 @@
       <c r="H323" s="3"/>
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
-      <c r="K323" s="3"/>
+      <c r="K323" s="21">
+        <f t="shared" ref="K323:K337" si="17">(C323*$G$2)/$H$2</f>
+        <v>13333.333333333334</v>
+      </c>
       <c r="L323" s="3"/>
       <c r="M323" s="3"/>
       <c r="N323" s="3"/>
@@ -15030,11 +16005,11 @@
         <v>102000</v>
       </c>
       <c r="D324" s="4">
-        <f t="shared" si="10"/>
-        <v>20400</v>
+        <f t="shared" si="15"/>
+        <v>17000</v>
       </c>
       <c r="E324" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>CASE TOWER BC VIP 730 P/S 230W</v>
       </c>
       <c r="F324" s="3"/>
@@ -15042,7 +16017,10 @@
       <c r="H324" s="3"/>
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
-      <c r="K324" s="3"/>
+      <c r="K324" s="21">
+        <f t="shared" si="17"/>
+        <v>17000</v>
+      </c>
       <c r="L324" s="3"/>
       <c r="M324" s="3"/>
       <c r="N324" s="3"/>
@@ -15066,11 +16044,11 @@
       <c r="B325" s="3"/>
       <c r="C325" s="4"/>
       <c r="D325" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E325" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">GRUPPI DI CONTINUITA' </v>
       </c>
       <c r="F325" s="3"/>
@@ -15078,7 +16056,10 @@
       <c r="H325" s="3"/>
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
-      <c r="K325" s="3"/>
+      <c r="K325" s="21">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="L325" s="3"/>
       <c r="M325" s="3"/>
       <c r="N325" s="3"/>
@@ -15106,11 +16087,11 @@
         <v>198000</v>
       </c>
       <c r="D326" s="4">
-        <f t="shared" si="10"/>
-        <v>39600</v>
+        <f t="shared" si="15"/>
+        <v>33000</v>
       </c>
       <c r="E326" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.REVOLUTION E300  STAND- BY</v>
       </c>
       <c r="F326" s="3"/>
@@ -15118,7 +16099,10 @@
       <c r="H326" s="3"/>
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
-      <c r="K326" s="3"/>
+      <c r="K326" s="21">
+        <f t="shared" si="17"/>
+        <v>33000</v>
+      </c>
       <c r="L326" s="3"/>
       <c r="M326" s="3"/>
       <c r="N326" s="3"/>
@@ -15146,11 +16130,11 @@
         <v>233000</v>
       </c>
       <c r="D327" s="4">
-        <f t="shared" si="10"/>
-        <v>46600</v>
+        <f t="shared" si="15"/>
+        <v>38833.333333333314</v>
       </c>
       <c r="E327" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.REVOLUTION F450 STAND- BY</v>
       </c>
       <c r="F327" s="3"/>
@@ -15158,7 +16142,10 @@
       <c r="H327" s="3"/>
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
-      <c r="K327" s="3"/>
+      <c r="K327" s="21">
+        <f t="shared" si="17"/>
+        <v>38833.333333333336</v>
+      </c>
       <c r="L327" s="3"/>
       <c r="M327" s="3"/>
       <c r="N327" s="3"/>
@@ -15186,11 +16173,11 @@
         <v>279000</v>
       </c>
       <c r="D328" s="4">
-        <f t="shared" si="10"/>
-        <v>55800</v>
+        <f t="shared" si="15"/>
+        <v>46500</v>
       </c>
       <c r="E328" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.REVOLUTION L600 STAND- BY</v>
       </c>
       <c r="F328" s="3"/>
@@ -15198,7 +16185,10 @@
       <c r="H328" s="3"/>
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
-      <c r="K328" s="3"/>
+      <c r="K328" s="21">
+        <f t="shared" si="17"/>
+        <v>46500</v>
+      </c>
       <c r="L328" s="3"/>
       <c r="M328" s="3"/>
       <c r="N328" s="3"/>
@@ -15226,11 +16216,11 @@
         <v>298000</v>
       </c>
       <c r="D329" s="4">
-        <f t="shared" si="10"/>
-        <v>59600</v>
+        <f t="shared" si="15"/>
+        <v>49666.666666666657</v>
       </c>
       <c r="E329" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.POWER PRO 600 LINE INTERACTIVE</v>
       </c>
       <c r="F329" s="3"/>
@@ -15238,7 +16228,10 @@
       <c r="H329" s="3"/>
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
-      <c r="K329" s="3"/>
+      <c r="K329" s="21">
+        <f t="shared" si="17"/>
+        <v>49666.666666666672</v>
+      </c>
       <c r="L329" s="3"/>
       <c r="M329" s="3"/>
       <c r="N329" s="3"/>
@@ -15266,11 +16259,11 @@
         <v>478000</v>
       </c>
       <c r="D330" s="4">
-        <f t="shared" si="10"/>
-        <v>95600</v>
+        <f t="shared" si="15"/>
+        <v>79666.666666666628</v>
       </c>
       <c r="E330" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.POWER PRO 750 LINE INTERACTIVE</v>
       </c>
       <c r="F330" s="3"/>
@@ -15278,7 +16271,10 @@
       <c r="H330" s="3"/>
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
-      <c r="K330" s="3"/>
+      <c r="K330" s="21">
+        <f t="shared" si="17"/>
+        <v>79666.666666666672</v>
+      </c>
       <c r="L330" s="3"/>
       <c r="M330" s="3"/>
       <c r="N330" s="3"/>
@@ -15306,11 +16302,11 @@
         <v>626000</v>
       </c>
       <c r="D331" s="4">
-        <f t="shared" si="10"/>
-        <v>125200</v>
+        <f t="shared" si="15"/>
+        <v>104333.33333333331</v>
       </c>
       <c r="E331" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.POWER PRO 900 LINE INTERACTIVE</v>
       </c>
       <c r="F331" s="3"/>
@@ -15318,7 +16314,10 @@
       <c r="H331" s="3"/>
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
-      <c r="K331" s="3"/>
+      <c r="K331" s="21">
+        <f t="shared" si="17"/>
+        <v>104333.33333333334</v>
+      </c>
       <c r="L331" s="3"/>
       <c r="M331" s="3"/>
       <c r="N331" s="3"/>
@@ -15346,11 +16345,11 @@
         <v>757000</v>
       </c>
       <c r="D332" s="4">
-        <f t="shared" si="10"/>
-        <v>151400</v>
+        <f t="shared" si="15"/>
+        <v>126166.66666666663</v>
       </c>
       <c r="E332" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.POWER PRO 1000 LINE INTERACTIVE</v>
       </c>
       <c r="F332" s="3"/>
@@ -15358,7 +16357,10 @@
       <c r="H332" s="3"/>
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
-      <c r="K332" s="3"/>
+      <c r="K332" s="21">
+        <f t="shared" si="17"/>
+        <v>126166.66666666667</v>
+      </c>
       <c r="L332" s="3"/>
       <c r="M332" s="3"/>
       <c r="N332" s="3"/>
@@ -15386,11 +16388,11 @@
         <v>1128000</v>
       </c>
       <c r="D333" s="4">
-        <f t="shared" si="10"/>
-        <v>225600</v>
+        <f t="shared" si="15"/>
+        <v>188000</v>
       </c>
       <c r="E333" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.POWER PRO 1600 LINE INTERACTIVE</v>
       </c>
       <c r="F333" s="3"/>
@@ -15398,7 +16400,10 @@
       <c r="H333" s="3"/>
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
-      <c r="K333" s="3"/>
+      <c r="K333" s="21">
+        <f t="shared" si="17"/>
+        <v>188000</v>
+      </c>
       <c r="L333" s="3"/>
       <c r="M333" s="3"/>
       <c r="N333" s="3"/>
@@ -15426,11 +16431,11 @@
         <v>1527000</v>
       </c>
       <c r="D334" s="4">
-        <f t="shared" si="10"/>
-        <v>305400</v>
+        <f t="shared" si="15"/>
+        <v>254500</v>
       </c>
       <c r="E334" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.POWER PRO 2400 LINE INTERACTIVE</v>
       </c>
       <c r="F334" s="3"/>
@@ -15438,7 +16443,10 @@
       <c r="H334" s="3"/>
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
-      <c r="K334" s="3"/>
+      <c r="K334" s="21">
+        <f t="shared" si="17"/>
+        <v>254500</v>
+      </c>
       <c r="L334" s="3"/>
       <c r="M334" s="3"/>
       <c r="N334" s="3"/>
@@ -15466,11 +16474,11 @@
         <v>4134000</v>
       </c>
       <c r="D335" s="4">
-        <f t="shared" si="10"/>
-        <v>826800</v>
+        <f t="shared" si="15"/>
+        <v>689000</v>
       </c>
       <c r="E335" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.POWERSAVE 4000 ON-LINE</v>
       </c>
       <c r="F335" s="3"/>
@@ -15478,7 +16486,10 @@
       <c r="H335" s="3"/>
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
-      <c r="K335" s="3"/>
+      <c r="K335" s="21">
+        <f t="shared" si="17"/>
+        <v>689000</v>
+      </c>
       <c r="L335" s="3"/>
       <c r="M335" s="3"/>
       <c r="N335" s="3"/>
@@ -15506,11 +16517,11 @@
         <v>6850000</v>
       </c>
       <c r="D336" s="4">
-        <f t="shared" si="10"/>
-        <v>1370000</v>
+        <f t="shared" si="15"/>
+        <v>1141666.666666666</v>
       </c>
       <c r="E336" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.POWERSAVE 7500 ON-LINE</v>
       </c>
       <c r="F336" s="3"/>
@@ -15518,7 +16529,10 @@
       <c r="H336" s="3"/>
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
-      <c r="K336" s="3"/>
+      <c r="K336" s="21">
+        <f t="shared" si="17"/>
+        <v>1141666.6666666667</v>
+      </c>
       <c r="L336" s="3"/>
       <c r="M336" s="3"/>
       <c r="N336" s="3"/>
@@ -15546,11 +16560,11 @@
         <v>11712000</v>
       </c>
       <c r="D337" s="4">
-        <f t="shared" si="10"/>
-        <v>2342400</v>
+        <f t="shared" si="15"/>
+        <v>1952000</v>
       </c>
       <c r="E337" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>GR.CONT.POWERSAVE 12500 ON-LINE</v>
       </c>
       <c r="F337" s="3"/>
@@ -15558,7 +16572,10 @@
       <c r="H337" s="3"/>
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
-      <c r="K337" s="3"/>
+      <c r="K337" s="21">
+        <f t="shared" si="17"/>
+        <v>1952000</v>
+      </c>
       <c r="L337" s="3"/>
       <c r="M337" s="3"/>
       <c r="N337" s="3"/>

--- a/ESERCIZIO_M2-1-1_dati.xlsx
+++ b/ESERCIZIO_M2-1-1_dati.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giancarloortolani/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giancarloortolani/Documents/GitHub/DataAnalyst_2026_G_Ortolani/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E3E98A4-C39D-CC4D-9307-8424883A9E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{D5D7D734-0C47-FB4C-9A07-27B71B2090C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assoluti_Iva" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,19 @@
   <definedNames>
     <definedName name="ACCES">Assoluti_Iva!$A$193:$C$227</definedName>
     <definedName name="CAB">Assoluti_Iva!$A$315:$C$324</definedName>
+    <definedName name="categoria">Fatture!$C$2:$C$150</definedName>
     <definedName name="CDROM">Assoluti_Iva!$A$108:$C$115</definedName>
+    <definedName name="cliente">Fatture!$B$2:$B$150</definedName>
     <definedName name="Codice">#REF!</definedName>
     <definedName name="CONT">Assoluti_Iva!$A$326:$C$337</definedName>
     <definedName name="CPU">Assoluti_Iva!$A$163:$C$183</definedName>
     <definedName name="DANIELE">#REF!</definedName>
     <definedName name="DATI">Assoluti_Iva!$A$1:$C$337</definedName>
+    <definedName name="esiti">Giudizio!$G$2:$H$5</definedName>
     <definedName name="HD">Assoluti_Iva!$A$79:$C$102</definedName>
     <definedName name="IMPO">#REF!</definedName>
     <definedName name="IMPORTO">#REF!</definedName>
+    <definedName name="importo_fattura">Fatture!$D$2:$D$150</definedName>
     <definedName name="IO_B">Assoluti_Iva!$A$63:$C$77</definedName>
     <definedName name="IVATOT">Assoluti_Iva!$G$1</definedName>
     <definedName name="MAIN_B">Assoluti_Iva!$A$20:$C$35</definedName>
@@ -39,19 +43,25 @@
     <definedName name="MODEM">Assoluti_Iva!$A$133:$C$149</definedName>
     <definedName name="MON">Assoluti_Iva!$A$2:$C$15</definedName>
     <definedName name="MONLCD">Assoluti_Iva!$A$17:$C$18</definedName>
+    <definedName name="nome">Giudizio!$A$2:$A$10</definedName>
+    <definedName name="punteggio">Giudizio!$B$2:$B$10</definedName>
     <definedName name="SOFT">Assoluti_Iva!$A$229:$C$278</definedName>
+    <definedName name="spese_di_spedizione">Fatture!$E$2:$E$150</definedName>
     <definedName name="STAMP">Assoluti_Iva!$A$280:$C$313</definedName>
     <definedName name="TAST">Assoluti_Iva!$A$185:$C$191</definedName>
     <definedName name="VIDEO_B">Assoluti_Iva!$A$37:$C$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -2008,9 +2018,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Column3" dataDxfId="0">
-      <calculatedColumnFormula>_xludf.VLOOKUP(B1,$G$2:$H$5,2)</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Column3" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Giudizio-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -35136,7 +35144,7 @@
         <v>40</v>
       </c>
       <c r="C2" s="6" t="str">
-        <f>VLOOKUP(B2,$G$2:$H$5,2,FALSE)</f>
+        <f>VLOOKUP(B2,esiti,2,FALSE)</f>
         <v>sufficiente</v>
       </c>
       <c r="D2" s="7"/>
@@ -35175,7 +35183,7 @@
         <v>60</v>
       </c>
       <c r="C3" s="6" t="str">
-        <f t="shared" ref="C3:C8" si="0">VLOOKUP(B3,$G$2:$H$5,2,FALSE)</f>
+        <f>VLOOKUP(B3,esiti,2,FALSE)</f>
         <v>discreto</v>
       </c>
       <c r="E3" s="7"/>
@@ -35213,7 +35221,7 @@
         <v>60</v>
       </c>
       <c r="C4" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(B4,esiti,2,FALSE)</f>
         <v>discreto</v>
       </c>
       <c r="E4" s="7"/>
@@ -35251,7 +35259,7 @@
         <v>40</v>
       </c>
       <c r="C5" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(B5,esiti,2,FALSE)</f>
         <v>sufficiente</v>
       </c>
       <c r="E5" s="7"/>
@@ -35289,7 +35297,7 @@
         <v>70</v>
       </c>
       <c r="C6" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(B6,esiti,2,FALSE)</f>
         <v>buono</v>
       </c>
       <c r="E6" s="7"/>
@@ -35323,7 +35331,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(B7,esiti,2,FALSE)</f>
         <v>respinto</v>
       </c>
       <c r="E7" s="7"/>
@@ -35357,7 +35365,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(B8,esiti,2,FALSE)</f>
         <v>respinto</v>
       </c>
       <c r="E8" s="7"/>
@@ -63038,7 +63046,7 @@
         <v>499</v>
       </c>
       <c r="H2">
-        <f>COUNTIF($C$2:$C$80,G2)</f>
+        <f>COUNTIF(categoria,G2)</f>
         <v>11</v>
       </c>
     </row>
@@ -63062,7 +63070,7 @@
         <v>558</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H4" si="0">COUNTIF($C$2:$C$80,G3)</f>
+        <f>COUNTIF(categoria,G3)</f>
         <v>5</v>
       </c>
     </row>
@@ -63086,7 +63094,7 @@
         <v>506</v>
       </c>
       <c r="H4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(categoria,G4)</f>
         <v>4</v>
       </c>
     </row>
@@ -63110,7 +63118,7 @@
         <v>547</v>
       </c>
       <c r="H5">
-        <f>COUNTIF($C$2:$C$80,G5)</f>
+        <f>COUNTIF(categoria,G5)</f>
         <v>4</v>
       </c>
     </row>
@@ -63206,7 +63214,7 @@
         <v>501</v>
       </c>
       <c r="H10">
-        <f>COUNTIF($B$2:$B$80,G10)</f>
+        <f>COUNTIF(cliente,G10)</f>
         <v>2</v>
       </c>
     </row>
@@ -63230,7 +63238,7 @@
         <v>507</v>
       </c>
       <c r="H11">
-        <f t="shared" ref="H11:H16" si="1">COUNTIF($B$2:$B$80,G11)</f>
+        <f>COUNTIF(cliente,G11)</f>
         <v>1</v>
       </c>
     </row>
@@ -63254,7 +63262,7 @@
         <v>509</v>
       </c>
       <c r="H12">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(cliente,G12)</f>
         <v>1</v>
       </c>
     </row>
@@ -63278,7 +63286,7 @@
         <v>511</v>
       </c>
       <c r="H13">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(cliente,G13)</f>
         <v>1</v>
       </c>
     </row>
@@ -63302,7 +63310,7 @@
         <v>525</v>
       </c>
       <c r="H14">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(cliente,G14)</f>
         <v>4</v>
       </c>
     </row>
@@ -63326,7 +63334,7 @@
         <v>528</v>
       </c>
       <c r="H15">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(cliente,G15)</f>
         <v>2</v>
       </c>
     </row>
@@ -63350,7 +63358,7 @@
         <v>529</v>
       </c>
       <c r="H16">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(cliente,G16)</f>
         <v>1</v>
       </c>
     </row>
@@ -63446,7 +63454,7 @@
         <v>499</v>
       </c>
       <c r="H21" s="20">
-        <f>SUMIF($C$2:$C$80,G21,$D$2:$D$80)</f>
+        <f>SUMIF(categoria,G21,importo_fattura)</f>
         <v>611780</v>
       </c>
     </row>
@@ -63470,7 +63478,7 @@
         <v>558</v>
       </c>
       <c r="H22" s="20">
-        <f t="shared" ref="H22:H24" si="2">SUMIF($C$2:$C$80,G22,$D$2:$D$80)</f>
+        <f>SUMIF(categoria,G22,importo_fattura)</f>
         <v>30860</v>
       </c>
     </row>
@@ -63494,7 +63502,7 @@
         <v>506</v>
       </c>
       <c r="H23" s="20">
-        <f t="shared" si="2"/>
+        <f>SUMIF(categoria,G23,importo_fattura)</f>
         <v>54000</v>
       </c>
     </row>
@@ -63518,7 +63526,7 @@
         <v>547</v>
       </c>
       <c r="H24" s="20">
-        <f t="shared" si="2"/>
+        <f>SUMIF(categoria,G24,importo_fattura)</f>
         <v>6765600</v>
       </c>
     </row>
@@ -63593,7 +63601,7 @@
         <v>501</v>
       </c>
       <c r="H28" s="20">
-        <f>SUMIF($B$2:$B$80,G28,$D$2:$D$80)</f>
+        <f>SUMIF(cliente,G28,importo_fattura)</f>
         <v>73450</v>
       </c>
     </row>
@@ -63617,7 +63625,7 @@
         <v>507</v>
       </c>
       <c r="H29" s="20">
-        <f t="shared" ref="H29:H34" si="3">SUMIF($B$2:$B$80,G29,$D$2:$D$80)</f>
+        <f>SUMIF(cliente,G29,importo_fattura)</f>
         <v>50800</v>
       </c>
     </row>
@@ -63641,7 +63649,7 @@
         <v>509</v>
       </c>
       <c r="H30" s="20">
-        <f t="shared" si="3"/>
+        <f>SUMIF(cliente,G30,importo_fattura)</f>
         <v>98450</v>
       </c>
     </row>
@@ -63665,7 +63673,7 @@
         <v>511</v>
       </c>
       <c r="H31" s="20">
-        <f t="shared" si="3"/>
+        <f>SUMIF(cliente,G31,importo_fattura)</f>
         <v>7950</v>
       </c>
     </row>
@@ -63689,7 +63697,7 @@
         <v>525</v>
       </c>
       <c r="H32" s="20">
-        <f t="shared" si="3"/>
+        <f>SUMIF(cliente,G32,importo_fattura)</f>
         <v>283000</v>
       </c>
     </row>
@@ -63713,7 +63721,7 @@
         <v>528</v>
       </c>
       <c r="H33" s="20">
-        <f t="shared" si="3"/>
+        <f>SUMIF(cliente,G33,importo_fattura)</f>
         <v>107700</v>
       </c>
     </row>
@@ -63737,7 +63745,7 @@
         <v>529</v>
       </c>
       <c r="H34" s="20">
-        <f t="shared" si="3"/>
+        <f>SUMIF(cliente,G34,importo_fattura)</f>
         <v>27270</v>
       </c>
     </row>
